--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -458,7 +458,7 @@
         <v>1.698676514770144</v>
       </c>
       <c r="C2" t="n">
-        <v>43.20759758426878</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>0.99</v>
@@ -472,7 +472,7 @@
         <v>0.5576178793366848</v>
       </c>
       <c r="C3" t="n">
-        <v>43.38585708536767</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>0.99</v>
@@ -486,7 +486,7 @@
         <v>1.124554743302174</v>
       </c>
       <c r="C4" t="n">
-        <v>27.45266138292878</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>0.9999</v>
@@ -500,7 +500,7 @@
         <v>1.621772775239417</v>
       </c>
       <c r="C5" t="n">
-        <v>36.68641219189514</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
         <v>0.9</v>
@@ -514,7 +514,7 @@
         <v>1.276891453942786</v>
       </c>
       <c r="C6" t="n">
-        <v>96.38144878048971</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>0.999</v>
@@ -528,7 +528,7 @@
         <v>0.9167562239484524</v>
       </c>
       <c r="C7" t="n">
-        <v>55.13073435377007</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
         <v>0.99</v>
@@ -542,7 +542,7 @@
         <v>1.125732881805666</v>
       </c>
       <c r="C8" t="n">
-        <v>75.08959796972462</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
         <v>0.9</v>
@@ -556,7 +556,7 @@
         <v>0.8637911872546682</v>
       </c>
       <c r="C9" t="n">
-        <v>48.2333066780183</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>0.9999</v>
@@ -570,7 +570,7 @@
         <v>1.318929248634284</v>
       </c>
       <c r="C10" t="n">
-        <v>51.39147289948201</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
         <v>0.9</v>
@@ -584,7 +584,7 @@
         <v>1.163224041631707</v>
       </c>
       <c r="C11" t="n">
-        <v>57.81777252679737</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>0.999</v>
@@ -598,7 +598,7 @@
         <v>0.6171149990192427</v>
       </c>
       <c r="C12" t="n">
-        <v>60.20629815197702</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>0.9999</v>
@@ -612,7 +612,7 @@
         <v>1.588839589559654</v>
       </c>
       <c r="C13" t="n">
-        <v>43.57610747977117</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
         <v>0.999</v>
@@ -626,7 +626,7 @@
         <v>1.04376917576841</v>
       </c>
       <c r="C14" t="n">
-        <v>77.9882468342083</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
         <v>0.999</v>
@@ -640,7 +640,7 @@
         <v>0.6063815335163489</v>
       </c>
       <c r="C15" t="n">
-        <v>24.09392907131769</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
         <v>0.9</v>
@@ -654,7 +654,7 @@
         <v>0.5239759095260945</v>
       </c>
       <c r="C16" t="n">
-        <v>51.3555073720406</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0.999</v>
@@ -668,7 +668,7 @@
         <v>0.7325500786327677</v>
       </c>
       <c r="C17" t="n">
-        <v>53.78844418250332</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>0.99</v>
@@ -682,7 +682,7 @@
         <v>1.500998025568986</v>
       </c>
       <c r="C18" t="n">
-        <v>49.05952338269637</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
         <v>0.99</v>
@@ -696,7 +696,7 @@
         <v>1.865713256096655</v>
       </c>
       <c r="C19" t="n">
-        <v>21.31368435641481</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
         <v>0.9</v>
@@ -710,7 +710,7 @@
         <v>1.617948301587924</v>
       </c>
       <c r="C20" t="n">
-        <v>56.52668008097017</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
         <v>0.9</v>
@@ -724,7 +724,7 @@
         <v>1.091914683287179</v>
       </c>
       <c r="C21" t="n">
-        <v>44.30025813913874</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
         <v>0.9999</v>
@@ -738,7 +738,7 @@
         <v>0.748173281639764</v>
       </c>
       <c r="C22" t="n">
-        <v>45.50457887351563</v>
+        <v>36</v>
       </c>
       <c r="D22" t="n">
         <v>0.9</v>
@@ -752,7 +752,7 @@
         <v>0.7023530680965311</v>
       </c>
       <c r="C23" t="n">
-        <v>55.02309588376541</v>
+        <v>44</v>
       </c>
       <c r="D23" t="n">
         <v>0.9</v>
@@ -766,7 +766,7 @@
         <v>1.28250873570704</v>
       </c>
       <c r="C24" t="n">
-        <v>52.18369220269612</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
         <v>0.99</v>
@@ -780,7 +780,7 @@
         <v>0.5207435482617606</v>
       </c>
       <c r="C25" t="n">
-        <v>64.1433465628119</v>
+        <v>39</v>
       </c>
       <c r="D25" t="n">
         <v>0.9</v>
@@ -794,7 +794,7 @@
         <v>1.768814210603876</v>
       </c>
       <c r="C26" t="n">
-        <v>38.7105271323888</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
         <v>0.9999</v>
@@ -808,7 +808,7 @@
         <v>1.933374127727371</v>
       </c>
       <c r="C27" t="n">
-        <v>47.15513362837858</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
         <v>0.9999</v>
@@ -822,7 +822,7 @@
         <v>1.848292124784682</v>
       </c>
       <c r="C28" t="n">
-        <v>74.63638949869004</v>
+        <v>41</v>
       </c>
       <c r="D28" t="n">
         <v>0.99</v>
@@ -836,7 +836,7 @@
         <v>0.8606761119609709</v>
       </c>
       <c r="C29" t="n">
-        <v>26.42818394017014</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
         <v>0.9</v>
@@ -850,7 +850,7 @@
         <v>1.435199088265653</v>
       </c>
       <c r="C30" t="n">
-        <v>37.81454435248695</v>
+        <v>34</v>
       </c>
       <c r="D30" t="n">
         <v>0.99</v>
@@ -864,7 +864,7 @@
         <v>1.200674143791567</v>
       </c>
       <c r="C31" t="n">
-        <v>11.55327504852977</v>
+        <v>32</v>
       </c>
       <c r="D31" t="n">
         <v>0.9999</v>
@@ -878,7 +878,7 @@
         <v>1.306239562439592</v>
       </c>
       <c r="C32" t="n">
-        <v>52.04782177376918</v>
+        <v>32</v>
       </c>
       <c r="D32" t="n">
         <v>0.999</v>
@@ -892,7 +892,7 @@
         <v>1.414121526506614</v>
       </c>
       <c r="C33" t="n">
-        <v>27.00002451712456</v>
+        <v>40</v>
       </c>
       <c r="D33" t="n">
         <v>0.999</v>
@@ -906,7 +906,7 @@
         <v>1.503259754869743</v>
       </c>
       <c r="C34" t="n">
-        <v>69.05176475181942</v>
+        <v>25</v>
       </c>
       <c r="D34" t="n">
         <v>0.99</v>
@@ -920,7 +920,7 @@
         <v>1.526822826982247</v>
       </c>
       <c r="C35" t="n">
-        <v>72.93728062802091</v>
+        <v>17</v>
       </c>
       <c r="D35" t="n">
         <v>0.9999</v>
@@ -934,7 +934,7 @@
         <v>0.5684495858010306</v>
       </c>
       <c r="C36" t="n">
-        <v>94.1892514143386</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>0.99</v>
@@ -948,7 +948,7 @@
         <v>1.179773715471355</v>
       </c>
       <c r="C37" t="n">
-        <v>50.74555317850584</v>
+        <v>16</v>
       </c>
       <c r="D37" t="n">
         <v>0.99</v>
@@ -962,7 +962,7 @@
         <v>1.298240201487501</v>
       </c>
       <c r="C38" t="n">
-        <v>72.87509432348376</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
         <v>0.999</v>
@@ -976,7 +976,7 @@
         <v>1.503696463389796</v>
       </c>
       <c r="C39" t="n">
-        <v>64.11347570332134</v>
+        <v>15</v>
       </c>
       <c r="D39" t="n">
         <v>0.99</v>
@@ -990,7 +990,7 @@
         <v>1.523658305587413</v>
       </c>
       <c r="C40" t="n">
-        <v>49.4848747688195</v>
+        <v>21</v>
       </c>
       <c r="D40" t="n">
         <v>0.9999</v>
@@ -1004,7 +1004,7 @@
         <v>1.223691777270608</v>
       </c>
       <c r="C41" t="n">
-        <v>40.61149836178698</v>
+        <v>44</v>
       </c>
       <c r="D41" t="n">
         <v>0.9</v>
@@ -1018,7 +1018,7 @@
         <v>1.034141742643207</v>
       </c>
       <c r="C42" t="n">
-        <v>55.49633659048928</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
         <v>0.999</v>
@@ -1032,7 +1032,7 @@
         <v>0.8226734334855148</v>
       </c>
       <c r="C43" t="n">
-        <v>50.21304384090709</v>
+        <v>25</v>
       </c>
       <c r="D43" t="n">
         <v>0.99</v>
@@ -1046,7 +1046,7 @@
         <v>0.800146381586586</v>
       </c>
       <c r="C44" t="n">
-        <v>80.28697150155216</v>
+        <v>16</v>
       </c>
       <c r="D44" t="n">
         <v>0.99</v>
@@ -1060,7 +1060,7 @@
         <v>1.340370064244808</v>
       </c>
       <c r="C45" t="n">
-        <v>79.73797000587803</v>
+        <v>41</v>
       </c>
       <c r="D45" t="n">
         <v>0.99</v>
@@ -1074,7 +1074,7 @@
         <v>1.15931108163272</v>
       </c>
       <c r="C46" t="n">
-        <v>27.99943562898938</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>0.9</v>
@@ -1088,7 +1088,7 @@
         <v>1.358026998454297</v>
       </c>
       <c r="C47" t="n">
-        <v>47.63495712009154</v>
+        <v>41</v>
       </c>
       <c r="D47" t="n">
         <v>0.9999</v>
@@ -1102,7 +1102,7 @@
         <v>0.7465153865434618</v>
       </c>
       <c r="C48" t="n">
-        <v>69.4777732317263</v>
+        <v>48</v>
       </c>
       <c r="D48" t="n">
         <v>0.9</v>
@@ -1116,7 +1116,7 @@
         <v>1.929676563507516</v>
       </c>
       <c r="C49" t="n">
-        <v>18.78144905959988</v>
+        <v>22</v>
       </c>
       <c r="D49" t="n">
         <v>0.999</v>
@@ -1130,7 +1130,7 @@
         <v>1.698174978067605</v>
       </c>
       <c r="C50" t="n">
-        <v>62.45478263683285</v>
+        <v>33</v>
       </c>
       <c r="D50" t="n">
         <v>0.9</v>
@@ -1144,7 +1144,7 @@
         <v>1.415739889683047</v>
       </c>
       <c r="C51" t="n">
-        <v>41.17089163372808</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
         <v>0.999</v>
@@ -1158,7 +1158,7 @@
         <v>1.831453901303101</v>
       </c>
       <c r="C52" t="n">
-        <v>36.20911811232581</v>
+        <v>24</v>
       </c>
       <c r="D52" t="n">
         <v>0.999</v>
@@ -1172,7 +1172,7 @@
         <v>1.969558271783297</v>
       </c>
       <c r="C53" t="n">
-        <v>53.36755021048462</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
         <v>0.99</v>
@@ -1186,7 +1186,7 @@
         <v>1.030740342586972</v>
       </c>
       <c r="C54" t="n">
-        <v>86.68081948680488</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>0.9</v>
@@ -1200,7 +1200,7 @@
         <v>1.040929756161986</v>
       </c>
       <c r="C55" t="n">
-        <v>66.87614279594948</v>
+        <v>30</v>
       </c>
       <c r="D55" t="n">
         <v>0.999</v>
@@ -1214,7 +1214,7 @@
         <v>1.816948765493561</v>
       </c>
       <c r="C56" t="n">
-        <v>68.89653597946707</v>
+        <v>27</v>
       </c>
       <c r="D56" t="n">
         <v>0.99</v>
@@ -1228,7 +1228,7 @@
         <v>1.052073422806038</v>
       </c>
       <c r="C57" t="n">
-        <v>61.69922395929176</v>
+        <v>42</v>
       </c>
       <c r="D57" t="n">
         <v>0.99</v>
@@ -1242,7 +1242,7 @@
         <v>0.9040033107181582</v>
       </c>
       <c r="C58" t="n">
-        <v>54.15504567529959</v>
+        <v>15</v>
       </c>
       <c r="D58" t="n">
         <v>0.99</v>
@@ -1256,7 +1256,7 @@
         <v>0.9928927498253965</v>
       </c>
       <c r="C59" t="n">
-        <v>59.19308713179974</v>
+        <v>24</v>
       </c>
       <c r="D59" t="n">
         <v>0.99</v>
@@ -1270,7 +1270,7 @@
         <v>1.509078210389081</v>
       </c>
       <c r="C60" t="n">
-        <v>46.60421690982366</v>
+        <v>35</v>
       </c>
       <c r="D60" t="n">
         <v>0.9</v>
@@ -1284,7 +1284,7 @@
         <v>0.9862916350858244</v>
       </c>
       <c r="C61" t="n">
-        <v>57.55358370680607</v>
+        <v>23</v>
       </c>
       <c r="D61" t="n">
         <v>0.999</v>
@@ -1298,7 +1298,7 @@
         <v>1.141375014735014</v>
       </c>
       <c r="C62" t="n">
-        <v>52.07487047590578</v>
+        <v>45</v>
       </c>
       <c r="D62" t="n">
         <v>0.9999</v>
@@ -1312,7 +1312,7 @@
         <v>1.906647222467766</v>
       </c>
       <c r="C63" t="n">
-        <v>95.27992184950708</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
         <v>0.999</v>
@@ -1326,7 +1326,7 @@
         <v>0.9521172516558767</v>
       </c>
       <c r="C64" t="n">
-        <v>69.17246069561165</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
         <v>0.999</v>
@@ -1340,7 +1340,7 @@
         <v>0.8558423325051934</v>
       </c>
       <c r="C65" t="n">
-        <v>41.08058693360758</v>
+        <v>13</v>
       </c>
       <c r="D65" t="n">
         <v>0.99</v>
@@ -1354,7 +1354,7 @@
         <v>1.298123485843432</v>
       </c>
       <c r="C66" t="n">
-        <v>43.59202073570907</v>
+        <v>44</v>
       </c>
       <c r="D66" t="n">
         <v>0.99</v>
@@ -1368,7 +1368,7 @@
         <v>0.5713564090935292</v>
       </c>
       <c r="C67" t="n">
-        <v>44.53644711143514</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
         <v>0.99</v>
@@ -1382,7 +1382,7 @@
         <v>1.972597559710513</v>
       </c>
       <c r="C68" t="n">
-        <v>51.41579418547523</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
         <v>0.99</v>
@@ -1396,7 +1396,7 @@
         <v>1.430863916596355</v>
       </c>
       <c r="C69" t="n">
-        <v>34.08151122908987</v>
+        <v>18</v>
       </c>
       <c r="D69" t="n">
         <v>0.99</v>
@@ -1410,7 +1410,7 @@
         <v>1.146633986672343</v>
       </c>
       <c r="C70" t="n">
-        <v>54.65872410671282</v>
+        <v>15</v>
       </c>
       <c r="D70" t="n">
         <v>0.999</v>
@@ -1424,7 +1424,7 @@
         <v>1.816066291939203</v>
       </c>
       <c r="C71" t="n">
-        <v>66.48692590821491</v>
+        <v>26</v>
       </c>
       <c r="D71" t="n">
         <v>0.9999</v>
@@ -1438,7 +1438,7 @@
         <v>1.161652003910522</v>
       </c>
       <c r="C72" t="n">
-        <v>57.19324236092296</v>
+        <v>27</v>
       </c>
       <c r="D72" t="n">
         <v>0.9999</v>
@@ -1452,7 +1452,7 @@
         <v>0.5855852471050556</v>
       </c>
       <c r="C73" t="n">
-        <v>68.84173796027147</v>
+        <v>13</v>
       </c>
       <c r="D73" t="n">
         <v>0.999</v>
@@ -1466,7 +1466,7 @@
         <v>0.8087874084133323</v>
       </c>
       <c r="C74" t="n">
-        <v>54.13583146373279</v>
+        <v>20</v>
       </c>
       <c r="D74" t="n">
         <v>0.9999</v>
@@ -1480,7 +1480,7 @@
         <v>1.865168923911332</v>
       </c>
       <c r="C75" t="n">
-        <v>8.567289588645963</v>
+        <v>12</v>
       </c>
       <c r="D75" t="n">
         <v>0.9</v>
@@ -1494,7 +1494,7 @@
         <v>1.817678962718627</v>
       </c>
       <c r="C76" t="n">
-        <v>54.75334241138257</v>
+        <v>22</v>
       </c>
       <c r="D76" t="n">
         <v>0.999</v>
@@ -1508,7 +1508,7 @@
         <v>0.9642914675406724</v>
       </c>
       <c r="C77" t="n">
-        <v>52.81015271563107</v>
+        <v>15</v>
       </c>
       <c r="D77" t="n">
         <v>0.9999</v>
@@ -1522,7 +1522,7 @@
         <v>1.224190745013748</v>
       </c>
       <c r="C78" t="n">
-        <v>52.46396296696184</v>
+        <v>38</v>
       </c>
       <c r="D78" t="n">
         <v>0.9999</v>
@@ -1536,7 +1536,7 @@
         <v>1.132653855499087</v>
       </c>
       <c r="C79" t="n">
-        <v>58.79872928260366</v>
+        <v>11</v>
       </c>
       <c r="D79" t="n">
         <v>0.99</v>
@@ -1550,7 +1550,7 @@
         <v>1.441694714052209</v>
       </c>
       <c r="C80" t="n">
-        <v>18.72022139376082</v>
+        <v>50</v>
       </c>
       <c r="D80" t="n">
         <v>0.9</v>
@@ -1564,7 +1564,7 @@
         <v>0.888431824966925</v>
       </c>
       <c r="C81" t="n">
-        <v>43.90867391329789</v>
+        <v>20</v>
       </c>
       <c r="D81" t="n">
         <v>0.9999</v>
@@ -1578,7 +1578,7 @@
         <v>1.150241061134162</v>
       </c>
       <c r="C82" t="n">
-        <v>53.5985932196014</v>
+        <v>37</v>
       </c>
       <c r="D82" t="n">
         <v>0.99</v>
@@ -1592,7 +1592,7 @@
         <v>1.124274331781209</v>
       </c>
       <c r="C83" t="n">
-        <v>40.30209447778905</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
         <v>0.99</v>
@@ -1606,7 +1606,7 @@
         <v>1.377181285809777</v>
       </c>
       <c r="C84" t="n">
-        <v>85.36821865802962</v>
+        <v>23</v>
       </c>
       <c r="D84" t="n">
         <v>0.999</v>
@@ -1620,7 +1620,7 @@
         <v>1.831081137486251</v>
       </c>
       <c r="C85" t="n">
-        <v>43.99412372367888</v>
+        <v>31</v>
       </c>
       <c r="D85" t="n">
         <v>0.9</v>
@@ -1634,7 +1634,7 @@
         <v>0.9514393938419983</v>
       </c>
       <c r="C86" t="n">
-        <v>40.39145421141154</v>
+        <v>35</v>
       </c>
       <c r="D86" t="n">
         <v>0.9999</v>
@@ -1648,7 +1648,7 @@
         <v>1.205959700518656</v>
       </c>
       <c r="C87" t="n">
-        <v>43.14945744753425</v>
+        <v>42</v>
       </c>
       <c r="D87" t="n">
         <v>0.999</v>
@@ -1662,7 +1662,7 @@
         <v>1.624691639598191</v>
       </c>
       <c r="C88" t="n">
-        <v>62.8857262773269</v>
+        <v>29</v>
       </c>
       <c r="D88" t="n">
         <v>0.9999</v>
@@ -1676,7 +1676,7 @@
         <v>1.325552594384797</v>
       </c>
       <c r="C89" t="n">
-        <v>60.93974912167573</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
         <v>0.9999</v>
@@ -1690,7 +1690,7 @@
         <v>1.213340035311207</v>
       </c>
       <c r="C90" t="n">
-        <v>55.77546672427388</v>
+        <v>31</v>
       </c>
       <c r="D90" t="n">
         <v>0.9999</v>
@@ -1704,7 +1704,7 @@
         <v>1.534624620716951</v>
       </c>
       <c r="C91" t="n">
-        <v>68.77720052962201</v>
+        <v>16</v>
       </c>
       <c r="D91" t="n">
         <v>0.9</v>
@@ -1718,7 +1718,7 @@
         <v>1.997963898212609</v>
       </c>
       <c r="C92" t="n">
-        <v>51.18970735828495</v>
+        <v>13</v>
       </c>
       <c r="D92" t="n">
         <v>0.99</v>
@@ -1732,7 +1732,7 @@
         <v>1.566012214879641</v>
       </c>
       <c r="C93" t="n">
-        <v>69.84357131562507</v>
+        <v>29</v>
       </c>
       <c r="D93" t="n">
         <v>0.999</v>
@@ -1746,7 +1746,7 @@
         <v>1.903645965732959</v>
       </c>
       <c r="C94" t="n">
-        <v>48.4711112188855</v>
+        <v>42</v>
       </c>
       <c r="D94" t="n">
         <v>0.999</v>
@@ -1760,7 +1760,7 @@
         <v>1.245133191583559</v>
       </c>
       <c r="C95" t="n">
-        <v>38.38517172536942</v>
+        <v>49</v>
       </c>
       <c r="D95" t="n">
         <v>0.999</v>
@@ -1774,7 +1774,7 @@
         <v>1.017116826713074</v>
       </c>
       <c r="C96" t="n">
-        <v>98.94416185326097</v>
+        <v>46</v>
       </c>
       <c r="D96" t="n">
         <v>0.9999</v>
@@ -1788,7 +1788,7 @@
         <v>1.827822917119495</v>
       </c>
       <c r="C97" t="n">
-        <v>25.68209333658137</v>
+        <v>50</v>
       </c>
       <c r="D97" t="n">
         <v>0.9</v>
@@ -1802,7 +1802,7 @@
         <v>1.012730868611788</v>
       </c>
       <c r="C98" t="n">
-        <v>30.58917014906865</v>
+        <v>17</v>
       </c>
       <c r="D98" t="n">
         <v>0.999</v>
@@ -1816,7 +1816,7 @@
         <v>1.883181775512212</v>
       </c>
       <c r="C99" t="n">
-        <v>55.4789924474909</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
         <v>0.9999</v>
@@ -1830,7 +1830,7 @@
         <v>1.418292648812512</v>
       </c>
       <c r="C100" t="n">
-        <v>25.94949736168169</v>
+        <v>49</v>
       </c>
       <c r="D100" t="n">
         <v>0.9</v>
@@ -1844,7 +1844,7 @@
         <v>0.9170233886763599</v>
       </c>
       <c r="C101" t="n">
-        <v>59.33338891114646</v>
+        <v>14</v>
       </c>
       <c r="D101" t="n">
         <v>0.9999</v>
@@ -1858,7 +1858,7 @@
         <v>0.9537779466483038</v>
       </c>
       <c r="C102" t="n">
-        <v>74.75354707657456</v>
+        <v>37</v>
       </c>
       <c r="D102" t="n">
         <v>0.9</v>
@@ -1872,7 +1872,7 @@
         <v>1.577314399725761</v>
       </c>
       <c r="C103" t="n">
-        <v>38.10131030109781</v>
+        <v>31</v>
       </c>
       <c r="D103" t="n">
         <v>0.9</v>
@@ -1886,7 +1886,7 @@
         <v>0.8845538199395837</v>
       </c>
       <c r="C104" t="n">
-        <v>59.09064323171441</v>
+        <v>49</v>
       </c>
       <c r="D104" t="n">
         <v>0.99</v>
@@ -1900,7 +1900,7 @@
         <v>1.986382241334534</v>
       </c>
       <c r="C105" t="n">
-        <v>45.76409327869553</v>
+        <v>37</v>
       </c>
       <c r="D105" t="n">
         <v>0.9999</v>
@@ -1914,7 +1914,7 @@
         <v>1.917266514357731</v>
       </c>
       <c r="C106" t="n">
-        <v>47.79058529410705</v>
+        <v>27</v>
       </c>
       <c r="D106" t="n">
         <v>0.9999</v>
@@ -1928,7 +1928,7 @@
         <v>0.9772057199456969</v>
       </c>
       <c r="C107" t="n">
-        <v>54.99188807458597</v>
+        <v>20</v>
       </c>
       <c r="D107" t="n">
         <v>0.9</v>
@@ -1942,7 +1942,7 @@
         <v>0.8832316178677049</v>
       </c>
       <c r="C108" t="n">
-        <v>55.97322148583545</v>
+        <v>48</v>
       </c>
       <c r="D108" t="n">
         <v>0.9</v>
@@ -1956,7 +1956,7 @@
         <v>1.475667183557569</v>
       </c>
       <c r="C109" t="n">
-        <v>54.07640908246629</v>
+        <v>35</v>
       </c>
       <c r="D109" t="n">
         <v>0.9999</v>
@@ -1970,7 +1970,7 @@
         <v>1.193530399564723</v>
       </c>
       <c r="C110" t="n">
-        <v>77.2673948909937</v>
+        <v>20</v>
       </c>
       <c r="D110" t="n">
         <v>0.9</v>
@@ -1984,7 +1984,7 @@
         <v>1.526682248403668</v>
       </c>
       <c r="C111" t="n">
-        <v>12.33299322717335</v>
+        <v>22</v>
       </c>
       <c r="D111" t="n">
         <v>0.9999</v>
@@ -1998,7 +1998,7 @@
         <v>1.99592970650501</v>
       </c>
       <c r="C112" t="n">
-        <v>32.10974931541395</v>
+        <v>50</v>
       </c>
       <c r="D112" t="n">
         <v>0.999</v>
@@ -2012,7 +2012,7 @@
         <v>0.5265638021424695</v>
       </c>
       <c r="C113" t="n">
-        <v>67.73622975761094</v>
+        <v>29</v>
       </c>
       <c r="D113" t="n">
         <v>0.9999</v>
@@ -2026,7 +2026,7 @@
         <v>0.5161931264924058</v>
       </c>
       <c r="C114" t="n">
-        <v>66.40356718027326</v>
+        <v>50</v>
       </c>
       <c r="D114" t="n">
         <v>0.99</v>
@@ -2040,7 +2040,7 @@
         <v>1.967253588335947</v>
       </c>
       <c r="C115" t="n">
-        <v>31.78790631655901</v>
+        <v>22</v>
       </c>
       <c r="D115" t="n">
         <v>0.9999</v>
@@ -2054,7 +2054,7 @@
         <v>1.89615348425003</v>
       </c>
       <c r="C116" t="n">
-        <v>64.37726779703684</v>
+        <v>39</v>
       </c>
       <c r="D116" t="n">
         <v>0.9999</v>
@@ -2068,7 +2068,7 @@
         <v>0.6965759756239653</v>
       </c>
       <c r="C117" t="n">
-        <v>53.40776155781828</v>
+        <v>38</v>
       </c>
       <c r="D117" t="n">
         <v>0.9</v>
@@ -2082,7 +2082,7 @@
         <v>1.941117476679422</v>
       </c>
       <c r="C118" t="n">
-        <v>76.25004893712321</v>
+        <v>39</v>
       </c>
       <c r="D118" t="n">
         <v>0.99</v>
@@ -2096,7 +2096,7 @@
         <v>0.9390548602461679</v>
       </c>
       <c r="C119" t="n">
-        <v>72.66476000723722</v>
+        <v>16</v>
       </c>
       <c r="D119" t="n">
         <v>0.999</v>
@@ -2110,7 +2110,7 @@
         <v>1.005056755933833</v>
       </c>
       <c r="C120" t="n">
-        <v>55.47989910062199</v>
+        <v>50</v>
       </c>
       <c r="D120" t="n">
         <v>0.9999</v>
@@ -2124,7 +2124,7 @@
         <v>1.57653010894631</v>
       </c>
       <c r="C121" t="n">
-        <v>61.25705195827475</v>
+        <v>36</v>
       </c>
       <c r="D121" t="n">
         <v>0.9999</v>
@@ -2138,7 +2138,7 @@
         <v>1.138993162495187</v>
       </c>
       <c r="C122" t="n">
-        <v>33.63993991992791</v>
+        <v>31</v>
       </c>
       <c r="D122" t="n">
         <v>0.99</v>
@@ -2152,7 +2152,7 @@
         <v>1.210173278683276</v>
       </c>
       <c r="C123" t="n">
-        <v>37.77805304550698</v>
+        <v>23</v>
       </c>
       <c r="D123" t="n">
         <v>0.99</v>
@@ -2166,7 +2166,7 @@
         <v>1.590989166316217</v>
       </c>
       <c r="C124" t="n">
-        <v>61.57428809194288</v>
+        <v>29</v>
       </c>
       <c r="D124" t="n">
         <v>0.9</v>
@@ -2180,7 +2180,7 @@
         <v>0.6343737052454252</v>
       </c>
       <c r="C125" t="n">
-        <v>59.34728818910371</v>
+        <v>24</v>
       </c>
       <c r="D125" t="n">
         <v>0.9</v>
@@ -2194,7 +2194,7 @@
         <v>1.768735631079944</v>
       </c>
       <c r="C126" t="n">
-        <v>59.3527919898704</v>
+        <v>32</v>
       </c>
       <c r="D126" t="n">
         <v>0.999</v>
@@ -2208,7 +2208,7 @@
         <v>0.8723914376346985</v>
       </c>
       <c r="C127" t="n">
-        <v>47.89550907575663</v>
+        <v>40</v>
       </c>
       <c r="D127" t="n">
         <v>0.9999</v>
@@ -2222,7 +2222,7 @@
         <v>0.68677596232893</v>
       </c>
       <c r="C128" t="n">
-        <v>87.62819238440366</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
         <v>0.999</v>
@@ -2236,7 +2236,7 @@
         <v>1.920396836566512</v>
       </c>
       <c r="C129" t="n">
-        <v>60.22400849114594</v>
+        <v>38</v>
       </c>
       <c r="D129" t="n">
         <v>0.999</v>
@@ -2250,7 +2250,7 @@
         <v>1.909367759380076</v>
       </c>
       <c r="C130" t="n">
-        <v>55.5412462608636</v>
+        <v>40</v>
       </c>
       <c r="D130" t="n">
         <v>0.9999</v>
@@ -2264,7 +2264,7 @@
         <v>1.393498512084533</v>
       </c>
       <c r="C131" t="n">
-        <v>58.402427945288</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
         <v>0.9</v>
@@ -2278,7 +2278,7 @@
         <v>1.187596167398222</v>
       </c>
       <c r="C132" t="n">
-        <v>35.57338683031903</v>
+        <v>23</v>
       </c>
       <c r="D132" t="n">
         <v>0.999</v>
@@ -2292,7 +2292,7 @@
         <v>1.272934462939539</v>
       </c>
       <c r="C133" t="n">
-        <v>35.6998408361998</v>
+        <v>48</v>
       </c>
       <c r="D133" t="n">
         <v>0.99</v>
@@ -2306,7 +2306,7 @@
         <v>1.153128796728891</v>
       </c>
       <c r="C134" t="n">
-        <v>28.28236827025106</v>
+        <v>15</v>
       </c>
       <c r="D134" t="n">
         <v>0.99</v>
@@ -2320,7 +2320,7 @@
         <v>1.16045611412061</v>
       </c>
       <c r="C135" t="n">
-        <v>43.97417121229151</v>
+        <v>33</v>
       </c>
       <c r="D135" t="n">
         <v>0.9</v>
@@ -2334,7 +2334,7 @@
         <v>1.014730722566602</v>
       </c>
       <c r="C136" t="n">
-        <v>32.6642947372342</v>
+        <v>34</v>
       </c>
       <c r="D136" t="n">
         <v>0.999</v>
@@ -2348,7 +2348,7 @@
         <v>1.376458654732497</v>
       </c>
       <c r="C137" t="n">
-        <v>59.32849460019946</v>
+        <v>8</v>
       </c>
       <c r="D137" t="n">
         <v>0.999</v>
@@ -2362,7 +2362,7 @@
         <v>0.9158407099198769</v>
       </c>
       <c r="C138" t="n">
-        <v>53.79870291338703</v>
+        <v>37</v>
       </c>
       <c r="D138" t="n">
         <v>0.999</v>
@@ -2376,7 +2376,7 @@
         <v>1.161024498520936</v>
       </c>
       <c r="C139" t="n">
-        <v>51.07101703821254</v>
+        <v>26</v>
       </c>
       <c r="D139" t="n">
         <v>0.9</v>
@@ -2390,7 +2390,7 @@
         <v>0.5691682785320457</v>
       </c>
       <c r="C140" t="n">
-        <v>59.44097895331267</v>
+        <v>29</v>
       </c>
       <c r="D140" t="n">
         <v>0.999</v>
@@ -2404,7 +2404,7 @@
         <v>0.558185544582529</v>
       </c>
       <c r="C141" t="n">
-        <v>45.6646095015544</v>
+        <v>28</v>
       </c>
       <c r="D141" t="n">
         <v>0.9999</v>
@@ -2418,7 +2418,7 @@
         <v>1.067330561012164</v>
       </c>
       <c r="C142" t="n">
-        <v>47.02182939587593</v>
+        <v>35</v>
       </c>
       <c r="D142" t="n">
         <v>0.99</v>
@@ -2432,7 +2432,7 @@
         <v>1.879025263275386</v>
       </c>
       <c r="C143" t="n">
-        <v>56.52014523281619</v>
+        <v>5</v>
       </c>
       <c r="D143" t="n">
         <v>0.99</v>
@@ -2446,7 +2446,7 @@
         <v>1.425020254339325</v>
       </c>
       <c r="C144" t="n">
-        <v>18.64237593166486</v>
+        <v>21</v>
       </c>
       <c r="D144" t="n">
         <v>0.999</v>
@@ -2460,7 +2460,7 @@
         <v>1.372806673584253</v>
       </c>
       <c r="C145" t="n">
-        <v>41.60180208730131</v>
+        <v>38</v>
       </c>
       <c r="D145" t="n">
         <v>0.99</v>
@@ -2474,7 +2474,7 @@
         <v>0.8007931175918177</v>
       </c>
       <c r="C146" t="n">
-        <v>82.7650811433617</v>
+        <v>36</v>
       </c>
       <c r="D146" t="n">
         <v>0.9</v>
@@ -2488,7 +2488,7 @@
         <v>1.440880270175235</v>
       </c>
       <c r="C147" t="n">
-        <v>42.37732900086705</v>
+        <v>34</v>
       </c>
       <c r="D147" t="n">
         <v>0.999</v>
@@ -2502,7 +2502,7 @@
         <v>0.715362962414009</v>
       </c>
       <c r="C148" t="n">
-        <v>49.95398679298959</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
         <v>0.9</v>
@@ -2516,7 +2516,7 @@
         <v>1.560571204256596</v>
       </c>
       <c r="C149" t="n">
-        <v>38.18412672813696</v>
+        <v>36</v>
       </c>
       <c r="D149" t="n">
         <v>0.999</v>
@@ -2530,7 +2530,7 @@
         <v>1.846820848597533</v>
       </c>
       <c r="C150" t="n">
-        <v>51.8560884160152</v>
+        <v>34</v>
       </c>
       <c r="D150" t="n">
         <v>0.999</v>
@@ -2544,7 +2544,7 @@
         <v>0.8290130927646091</v>
       </c>
       <c r="C151" t="n">
-        <v>29.7875634683097</v>
+        <v>17</v>
       </c>
       <c r="D151" t="n">
         <v>0.9</v>
@@ -2558,7 +2558,7 @@
         <v>1.621975929178317</v>
       </c>
       <c r="C152" t="n">
-        <v>54.10473410883696</v>
+        <v>7</v>
       </c>
       <c r="D152" t="n">
         <v>0.99</v>
@@ -2572,7 +2572,7 @@
         <v>1.826859764671628</v>
       </c>
       <c r="C153" t="n">
-        <v>29.66099402171883</v>
+        <v>38</v>
       </c>
       <c r="D153" t="n">
         <v>0.99</v>
@@ -2586,7 +2586,7 @@
         <v>1.020755919076118</v>
       </c>
       <c r="C154" t="n">
-        <v>57.0871940191464</v>
+        <v>35</v>
       </c>
       <c r="D154" t="n">
         <v>0.999</v>
@@ -2600,7 +2600,7 @@
         <v>1.462888622687835</v>
       </c>
       <c r="C155" t="n">
-        <v>23.81428370738922</v>
+        <v>27</v>
       </c>
       <c r="D155" t="n">
         <v>0.9999</v>
@@ -2614,7 +2614,7 @@
         <v>0.7011151675491456</v>
       </c>
       <c r="C156" t="n">
-        <v>48.11775373375345</v>
+        <v>26</v>
       </c>
       <c r="D156" t="n">
         <v>0.999</v>
@@ -2628,7 +2628,7 @@
         <v>1.21156168911754</v>
       </c>
       <c r="C157" t="n">
-        <v>46.36413000420836</v>
+        <v>41</v>
       </c>
       <c r="D157" t="n">
         <v>0.99</v>
@@ -2642,7 +2642,7 @@
         <v>1.959051147849327</v>
       </c>
       <c r="C158" t="n">
-        <v>32.01678878891607</v>
+        <v>17</v>
       </c>
       <c r="D158" t="n">
         <v>0.999</v>
@@ -2656,7 +2656,7 @@
         <v>1.59819000355857</v>
       </c>
       <c r="C159" t="n">
-        <v>66.33555871283548</v>
+        <v>12</v>
       </c>
       <c r="D159" t="n">
         <v>0.9999</v>
@@ -2670,7 +2670,7 @@
         <v>1.029338817444233</v>
       </c>
       <c r="C160" t="n">
-        <v>40.86823229046978</v>
+        <v>15</v>
       </c>
       <c r="D160" t="n">
         <v>0.9999</v>
@@ -2684,7 +2684,7 @@
         <v>1.110467212912065</v>
       </c>
       <c r="C161" t="n">
-        <v>63.04176689852675</v>
+        <v>32</v>
       </c>
       <c r="D161" t="n">
         <v>0.9</v>
@@ -2698,7 +2698,7 @@
         <v>1.518168198151698</v>
       </c>
       <c r="C162" t="n">
-        <v>45.01544938245973</v>
+        <v>5</v>
       </c>
       <c r="D162" t="n">
         <v>0.9999</v>
@@ -2712,7 +2712,7 @@
         <v>0.6461838780613436</v>
       </c>
       <c r="C163" t="n">
-        <v>46.94076825568083</v>
+        <v>12</v>
       </c>
       <c r="D163" t="n">
         <v>0.99</v>
@@ -2726,7 +2726,7 @@
         <v>1.478815136842968</v>
       </c>
       <c r="C164" t="n">
-        <v>80.96459994383044</v>
+        <v>22</v>
       </c>
       <c r="D164" t="n">
         <v>0.9</v>
@@ -2740,7 +2740,7 @@
         <v>1.43791051418215</v>
       </c>
       <c r="C165" t="n">
-        <v>55.70445243448228</v>
+        <v>46</v>
       </c>
       <c r="D165" t="n">
         <v>0.999</v>
@@ -2754,7 +2754,7 @@
         <v>1.970451205844075</v>
       </c>
       <c r="C166" t="n">
-        <v>60.22060361378609</v>
+        <v>44</v>
       </c>
       <c r="D166" t="n">
         <v>0.99</v>
@@ -2768,7 +2768,7 @@
         <v>0.6165587144900581</v>
       </c>
       <c r="C167" t="n">
-        <v>35.52447847044257</v>
+        <v>50</v>
       </c>
       <c r="D167" t="n">
         <v>0.999</v>
@@ -2782,7 +2782,7 @@
         <v>1.777549109504937</v>
       </c>
       <c r="C168" t="n">
-        <v>74.83796044440696</v>
+        <v>43</v>
       </c>
       <c r="D168" t="n">
         <v>0.9999</v>
@@ -2796,7 +2796,7 @@
         <v>1.923435722078754</v>
       </c>
       <c r="C169" t="n">
-        <v>35.91062707574415</v>
+        <v>12</v>
       </c>
       <c r="D169" t="n">
         <v>0.999</v>
@@ -2810,7 +2810,7 @@
         <v>0.50410556434063</v>
       </c>
       <c r="C170" t="n">
-        <v>41.07876824153396</v>
+        <v>28</v>
       </c>
       <c r="D170" t="n">
         <v>0.9999</v>
@@ -2824,7 +2824,7 @@
         <v>0.682665623139759</v>
       </c>
       <c r="C171" t="n">
-        <v>27.83349922363659</v>
+        <v>20</v>
       </c>
       <c r="D171" t="n">
         <v>0.999</v>
@@ -2838,7 +2838,7 @@
         <v>1.013140134936704</v>
       </c>
       <c r="C172" t="n">
-        <v>10.60510472593611</v>
+        <v>14</v>
       </c>
       <c r="D172" t="n">
         <v>0.999</v>
@@ -2852,7 +2852,7 @@
         <v>1.827315687959412</v>
       </c>
       <c r="C173" t="n">
-        <v>56.57070459279413</v>
+        <v>43</v>
       </c>
       <c r="D173" t="n">
         <v>0.9999</v>
@@ -2866,7 +2866,7 @@
         <v>1.713205254747983</v>
       </c>
       <c r="C174" t="n">
-        <v>36.25296257009146</v>
+        <v>12</v>
       </c>
       <c r="D174" t="n">
         <v>0.9</v>
@@ -2880,7 +2880,7 @@
         <v>1.45624265265026</v>
       </c>
       <c r="C175" t="n">
-        <v>46.00948760840934</v>
+        <v>37</v>
       </c>
       <c r="D175" t="n">
         <v>0.9999</v>
@@ -2894,7 +2894,7 @@
         <v>0.5195565980853729</v>
       </c>
       <c r="C176" t="n">
-        <v>64.98581463610341</v>
+        <v>38</v>
       </c>
       <c r="D176" t="n">
         <v>0.9</v>
@@ -2908,7 +2908,7 @@
         <v>1.412912890468327</v>
       </c>
       <c r="C177" t="n">
-        <v>39.57041138402937</v>
+        <v>29</v>
       </c>
       <c r="D177" t="n">
         <v>0.99</v>
@@ -2922,7 +2922,7 @@
         <v>1.943389560641203</v>
       </c>
       <c r="C178" t="n">
-        <v>38.26119121400266</v>
+        <v>5</v>
       </c>
       <c r="D178" t="n">
         <v>0.9</v>
@@ -2936,7 +2936,7 @@
         <v>1.566008595031556</v>
       </c>
       <c r="C179" t="n">
-        <v>39.40324060927303</v>
+        <v>22</v>
       </c>
       <c r="D179" t="n">
         <v>0.9</v>
@@ -2950,7 +2950,7 @@
         <v>1.421481188363827</v>
       </c>
       <c r="C180" t="n">
-        <v>48.43212035316666</v>
+        <v>40</v>
       </c>
       <c r="D180" t="n">
         <v>0.99</v>
@@ -2964,7 +2964,7 @@
         <v>0.9661528785946254</v>
       </c>
       <c r="C181" t="n">
-        <v>96.49696595745532</v>
+        <v>32</v>
       </c>
       <c r="D181" t="n">
         <v>0.99</v>
@@ -2978,7 +2978,7 @@
         <v>1.016994233974312</v>
       </c>
       <c r="C182" t="n">
-        <v>41.70215136698815</v>
+        <v>33</v>
       </c>
       <c r="D182" t="n">
         <v>0.9</v>
@@ -2992,7 +2992,7 @@
         <v>1.289320399650121</v>
       </c>
       <c r="C183" t="n">
-        <v>68.45673375956804</v>
+        <v>21</v>
       </c>
       <c r="D183" t="n">
         <v>0.9</v>
@@ -3006,7 +3006,7 @@
         <v>0.8684840279545238</v>
       </c>
       <c r="C184" t="n">
-        <v>51.49323544861909</v>
+        <v>21</v>
       </c>
       <c r="D184" t="n">
         <v>0.999</v>
@@ -3020,7 +3020,7 @@
         <v>0.5233041138229977</v>
       </c>
       <c r="C185" t="n">
-        <v>59.34093572922665</v>
+        <v>18</v>
       </c>
       <c r="D185" t="n">
         <v>0.9999</v>
@@ -3034,7 +3034,7 @@
         <v>1.080886887873118</v>
       </c>
       <c r="C186" t="n">
-        <v>67.83919761244347</v>
+        <v>21</v>
       </c>
       <c r="D186" t="n">
         <v>0.9</v>
@@ -3048,7 +3048,7 @@
         <v>1.936002494005718</v>
       </c>
       <c r="C187" t="n">
-        <v>30.02472658904182</v>
+        <v>35</v>
       </c>
       <c r="D187" t="n">
         <v>0.9</v>
@@ -3062,7 +3062,7 @@
         <v>0.8823253989818636</v>
       </c>
       <c r="C188" t="n">
-        <v>50.53243129360188</v>
+        <v>10</v>
       </c>
       <c r="D188" t="n">
         <v>0.9999</v>
@@ -3076,7 +3076,7 @@
         <v>0.5888615131268994</v>
       </c>
       <c r="C189" t="n">
-        <v>37.10279117957653</v>
+        <v>13</v>
       </c>
       <c r="D189" t="n">
         <v>0.99</v>
@@ -3090,7 +3090,7 @@
         <v>1.493961165977075</v>
       </c>
       <c r="C190" t="n">
-        <v>84.60916806538907</v>
+        <v>23</v>
       </c>
       <c r="D190" t="n">
         <v>0.9</v>
@@ -3104,7 +3104,7 @@
         <v>1.846857262790149</v>
       </c>
       <c r="C191" t="n">
-        <v>51.33048636029659</v>
+        <v>19</v>
       </c>
       <c r="D191" t="n">
         <v>0.9999</v>
@@ -3118,7 +3118,7 @@
         <v>0.80785866874114</v>
       </c>
       <c r="C192" t="n">
-        <v>30.99292366373328</v>
+        <v>25</v>
       </c>
       <c r="D192" t="n">
         <v>0.9999</v>
@@ -3132,7 +3132,7 @@
         <v>1.550979765374794</v>
       </c>
       <c r="C193" t="n">
-        <v>30.96494662908491</v>
+        <v>13</v>
       </c>
       <c r="D193" t="n">
         <v>0.99</v>
@@ -3146,7 +3146,7 @@
         <v>1.038987919243236</v>
       </c>
       <c r="C194" t="n">
-        <v>58.23712976094647</v>
+        <v>9</v>
       </c>
       <c r="D194" t="n">
         <v>0.9</v>
@@ -3160,7 +3160,7 @@
         <v>1.264389791626048</v>
       </c>
       <c r="C195" t="n">
-        <v>30.91992531690555</v>
+        <v>46</v>
       </c>
       <c r="D195" t="n">
         <v>0.9</v>
@@ -3174,7 +3174,7 @@
         <v>0.7213409319196464</v>
       </c>
       <c r="C196" t="n">
-        <v>38.28294551366284</v>
+        <v>27</v>
       </c>
       <c r="D196" t="n">
         <v>0.99</v>
@@ -3188,7 +3188,7 @@
         <v>1.784902233608911</v>
       </c>
       <c r="C197" t="n">
-        <v>69.01566878980147</v>
+        <v>44</v>
       </c>
       <c r="D197" t="n">
         <v>0.999</v>
@@ -3202,7 +3202,7 @@
         <v>1.44872661437035</v>
       </c>
       <c r="C198" t="n">
-        <v>60.56783139759938</v>
+        <v>27</v>
       </c>
       <c r="D198" t="n">
         <v>0.999</v>
@@ -3216,7 +3216,7 @@
         <v>1.464910533836621</v>
       </c>
       <c r="C199" t="n">
-        <v>43.66447095291823</v>
+        <v>45</v>
       </c>
       <c r="D199" t="n">
         <v>0.9999</v>
@@ -3230,7 +3230,7 @@
         <v>1.879986701906027</v>
       </c>
       <c r="C200" t="n">
-        <v>85.42407309850805</v>
+        <v>22</v>
       </c>
       <c r="D200" t="n">
         <v>0.9</v>
@@ -3244,7 +3244,7 @@
         <v>1.258948347352817</v>
       </c>
       <c r="C201" t="n">
-        <v>40.37192940527918</v>
+        <v>40</v>
       </c>
       <c r="D201" t="n">
         <v>0.9999</v>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -460,7 +460,9 @@
       <c r="C2" t="n">
         <v>53.67919023703534</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0.9916104133230789</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -472,7 +474,9 @@
       <c r="C3" t="n">
         <v>34.75107857408746</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>0.9957592184914363</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -484,7 +488,9 @@
       <c r="C4" t="n">
         <v>42.60628635542257</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0.9942054156102914</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -496,7 +502,9 @@
       <c r="C5" t="n">
         <v>33.48190127293107</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.9933345047439724</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -508,7 +516,9 @@
       <c r="C6" t="n">
         <v>45.23196171646185</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0.9931942560087869</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -520,7 +530,9 @@
       <c r="C7" t="n">
         <v>42.32918817317876</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>0.9971146642126794</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -532,7 +544,9 @@
       <c r="C8" t="n">
         <v>44.44014536248625</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0.9981462945300945</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -544,7 +558,9 @@
       <c r="C9" t="n">
         <v>47.94897151388241</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0.9915961787264075</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -556,7 +572,9 @@
       <c r="C10" t="n">
         <v>44.64165636479374</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0.9958750632241662</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -568,7 +586,9 @@
       <c r="C11" t="n">
         <v>28.02194103187311</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>0.9926847249062001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -580,7 +600,9 @@
       <c r="C12" t="n">
         <v>50.49475649543508</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0.9987026598014616</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -592,7 +614,9 @@
       <c r="C13" t="n">
         <v>40.71306000432234</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>0.9982786514448355</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -604,7 +628,9 @@
       <c r="C14" t="n">
         <v>47.09592044693731</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0.9957228372373018</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -616,7 +642,9 @@
       <c r="C15" t="n">
         <v>62.52548385599771</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.9967745888737117</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -628,7 +656,9 @@
       <c r="C16" t="n">
         <v>54.260886173613</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.9946363832669012</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -640,7 +670,9 @@
       <c r="C17" t="n">
         <v>60.50559856437604</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0.9974330573253801</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -652,7 +684,9 @@
       <c r="C18" t="n">
         <v>71.04614060419865</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0.994035424908601</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -664,7 +698,9 @@
       <c r="C19" t="n">
         <v>58.55154095134137</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.9930493120798238</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -676,7 +712,9 @@
       <c r="C20" t="n">
         <v>51.66508863793452</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0.9925010929395014</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -688,7 +726,9 @@
       <c r="C21" t="n">
         <v>78.40138622491851</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>0.9920369975115906</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -700,7 +740,9 @@
       <c r="C22" t="n">
         <v>48.7360258336366</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0.9947323515901072</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -712,7 +754,9 @@
       <c r="C23" t="n">
         <v>49.85244703050946</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0.9938782085461598</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -724,7 +768,9 @@
       <c r="C24" t="n">
         <v>32.62033579304236</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0.9959686255842534</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -736,7 +782,9 @@
       <c r="C25" t="n">
         <v>66.86694939091855</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0.9901155643413012</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -748,7 +796,9 @@
       <c r="C26" t="n">
         <v>61.39125059256289</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>0.9940293171138485</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -760,7 +810,9 @@
       <c r="C27" t="n">
         <v>27.60097501061821</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0.9932866272101916</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -772,7 +824,9 @@
       <c r="C28" t="n">
         <v>57.44548841854294</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0.991758578398844</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -784,7 +838,9 @@
       <c r="C29" t="n">
         <v>64.2897180394438</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.9953537928390545</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -796,7 +852,9 @@
       <c r="C30" t="n">
         <v>51.04424473508528</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0.9939178184035558</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -808,7 +866,9 @@
       <c r="C31" t="n">
         <v>26.35625682329916</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0.9926999235337064</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -820,7 +880,9 @@
       <c r="C32" t="n">
         <v>47.49475732167166</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0.991884745091126</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -832,7 +894,9 @@
       <c r="C33" t="n">
         <v>37.53758065048235</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.9978716165147297</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -844,7 +908,9 @@
       <c r="C34" t="n">
         <v>37.42441453674519</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0.9971771608396929</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -856,7 +922,9 @@
       <c r="C35" t="n">
         <v>54.82631099740421</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0.9954603870901648</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -868,7 +936,9 @@
       <c r="C36" t="n">
         <v>52.8998657286197</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0.9931059052080056</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -880,7 +950,9 @@
       <c r="C37" t="n">
         <v>64.07692484117138</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0.9985213781188168</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -892,7 +964,9 @@
       <c r="C38" t="n">
         <v>15.02018996783411</v>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0.9950703963705229</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -904,7 +978,9 @@
       <c r="C39" t="n">
         <v>23.07587490327965</v>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0.9938948646565796</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -916,7 +992,9 @@
       <c r="C40" t="n">
         <v>58.40841188526452</v>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0.998104046391038</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -928,7 +1006,9 @@
       <c r="C41" t="n">
         <v>31.82746499262569</v>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>0.9928740762351168</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -940,7 +1020,9 @@
       <c r="C42" t="n">
         <v>35.37733090673469</v>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>0.996263953831204</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -952,7 +1034,9 @@
       <c r="C43" t="n">
         <v>41.61615719019</v>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.9928243829453614</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -964,7 +1048,9 @@
       <c r="C44" t="n">
         <v>44.81145220748102</v>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0.9923539774168062</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -976,7 +1062,9 @@
       <c r="C45" t="n">
         <v>49.06743572749054</v>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>0.9963075680055077</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -988,7 +1076,9 @@
       <c r="C46" t="n">
         <v>33.5774453963048</v>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>0.9920510278101662</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1000,7 +1090,9 @@
       <c r="C47" t="n">
         <v>57.46522201167969</v>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0.994437992906864</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1012,7 +1104,9 @@
       <c r="C48" t="n">
         <v>52.03102919872997</v>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>0.995220256077185</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1024,7 +1118,9 @@
       <c r="C49" t="n">
         <v>50.57254956738563</v>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0.9917001572827902</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1036,7 +1132,9 @@
       <c r="C50" t="n">
         <v>48.54148684428007</v>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>0.9965811659252261</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1048,7 +1146,9 @@
       <c r="C51" t="n">
         <v>73.82498461236125</v>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0.9949363475816216</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1060,7 +1160,9 @@
       <c r="C52" t="n">
         <v>64.0560547756331</v>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0.9955935293366335</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1072,7 +1174,9 @@
       <c r="C53" t="n">
         <v>44.29222473466736</v>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0.9933492988511715</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1084,7 +1188,9 @@
       <c r="C54" t="n">
         <v>59.51537785616269</v>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>0.9937817393392857</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1096,7 +1202,9 @@
       <c r="C55" t="n">
         <v>55.06770176992225</v>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0.9944534671012535</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1108,7 +1216,9 @@
       <c r="C56" t="n">
         <v>51.2529958529192</v>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>0.9942297382116555</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1120,7 +1230,9 @@
       <c r="C57" t="n">
         <v>32.35552130588029</v>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>0.9960807530056466</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1132,7 +1244,9 @@
       <c r="C58" t="n">
         <v>52.65079504580522</v>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>0.9951945975404658</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1144,7 +1258,9 @@
       <c r="C59" t="n">
         <v>53.2344844792981</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>0.9937464357869322</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1156,7 +1272,9 @@
       <c r="C60" t="n">
         <v>55.85981383545153</v>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>0.9900162211824614</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1168,7 +1286,9 @@
       <c r="C61" t="n">
         <v>56.84249730850535</v>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>0.9971462795469795</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1180,7 +1300,9 @@
       <c r="C62" t="n">
         <v>56.04683541536205</v>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>0.994674457990299</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1192,7 +1314,9 @@
       <c r="C63" t="n">
         <v>42.9238407328732</v>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>0.9929389019743015</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1204,7 +1328,9 @@
       <c r="C64" t="n">
         <v>67.33541070056265</v>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>0.9944995952017007</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1216,7 +1342,9 @@
       <c r="C65" t="n">
         <v>46.42083313914934</v>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>0.9908410134014516</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1228,7 +1356,9 @@
       <c r="C66" t="n">
         <v>20.15246335861512</v>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>0.9981423366529801</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1240,7 +1370,9 @@
       <c r="C67" t="n">
         <v>64.71781357938394</v>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>0.9989076255082605</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1252,7 +1384,9 @@
       <c r="C68" t="n">
         <v>20.9709849543949</v>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>0.9905286169576403</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1264,7 +1398,9 @@
       <c r="C69" t="n">
         <v>54.59209029064667</v>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>0.9932240809673224</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1276,7 +1412,9 @@
       <c r="C70" t="n">
         <v>54.35771212243785</v>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>0.9965705812003718</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1288,7 +1426,9 @@
       <c r="C71" t="n">
         <v>55.59379252137557</v>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>0.9928281431809609</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1300,7 +1440,9 @@
       <c r="C72" t="n">
         <v>66.00212359285925</v>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>0.99510344782528</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1312,7 +1454,9 @@
       <c r="C73" t="n">
         <v>50.87657503292501</v>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>0.9937491386608353</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1324,7 +1468,9 @@
       <c r="C74" t="n">
         <v>40.3001338986972</v>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>0.9969679094186779</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1336,7 +1482,9 @@
       <c r="C75" t="n">
         <v>43.29408133550469</v>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>0.9986261796086763</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1348,7 +1496,9 @@
       <c r="C76" t="n">
         <v>72.45615876012165</v>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>0.9979955588368501</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1360,7 +1510,9 @@
       <c r="C77" t="n">
         <v>71.96958543119473</v>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>0.9955884191868004</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1372,7 +1524,9 @@
       <c r="C78" t="n">
         <v>31.71903097672782</v>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>0.9914424688140127</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1384,7 +1538,9 @@
       <c r="C79" t="n">
         <v>24.78238876433949</v>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>0.9985235587498049</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1396,7 +1552,9 @@
       <c r="C80" t="n">
         <v>35.78474079132059</v>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>0.9902126918580459</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1408,7 +1566,9 @@
       <c r="C81" t="n">
         <v>85.86880632972213</v>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="n">
+        <v>0.9926793851077877</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1420,7 +1580,9 @@
       <c r="C82" t="n">
         <v>54.84551943934476</v>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>0.9925345214379053</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1432,7 +1594,9 @@
       <c r="C83" t="n">
         <v>42.02852297835588</v>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>0.9960464338355043</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1444,7 +1608,9 @@
       <c r="C84" t="n">
         <v>21.24799500474111</v>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>0.9943862675946527</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1456,7 +1622,9 @@
       <c r="C85" t="n">
         <v>29.26763733809423</v>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>0.990835996938817</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1468,7 +1636,9 @@
       <c r="C86" t="n">
         <v>26.00454916311631</v>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>0.9901157209897044</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1480,7 +1650,9 @@
       <c r="C87" t="n">
         <v>49.24023764655826</v>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>0.9954388417209628</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1492,7 +1664,9 @@
       <c r="C88" t="n">
         <v>58.69657861547959</v>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>0.9944233499910683</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1504,7 +1678,9 @@
       <c r="C89" t="n">
         <v>38.56371252741226</v>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>0.9954124390920636</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1516,7 +1692,9 @@
       <c r="C90" t="n">
         <v>52.50241733428958</v>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>0.9950762147747898</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1528,7 +1706,9 @@
       <c r="C91" t="n">
         <v>36.73129929489149</v>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>0.9980141319746971</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1540,7 +1720,9 @@
       <c r="C92" t="n">
         <v>38.354514288082</v>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>0.9982655717208354</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1552,7 +1734,9 @@
       <c r="C93" t="n">
         <v>35.67810581622993</v>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>0.9916943144499213</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1564,7 +1748,9 @@
       <c r="C94" t="n">
         <v>53.07213893313723</v>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>0.9984790878252348</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1576,7 +1762,9 @@
       <c r="C95" t="n">
         <v>48.86920189220226</v>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>0.9970895396369051</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1588,7 +1776,9 @@
       <c r="C96" t="n">
         <v>62.85358877955228</v>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>0.9957512362700067</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1600,7 +1790,9 @@
       <c r="C97" t="n">
         <v>51.47706433991497</v>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>0.9959364654074185</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1612,7 +1804,9 @@
       <c r="C98" t="n">
         <v>62.72713000736199</v>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>0.9949145420691058</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1624,7 +1818,9 @@
       <c r="C99" t="n">
         <v>30.1299770846383</v>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>0.9982553696967855</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1636,7 +1832,9 @@
       <c r="C100" t="n">
         <v>36.75800440157938</v>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>0.9920993688558012</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1648,7 +1846,9 @@
       <c r="C101" t="n">
         <v>63.89390408530792</v>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>0.9953938439304262</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1660,7 +1860,9 @@
       <c r="C102" t="n">
         <v>26.79910170703495</v>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>0.9973281875568448</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1672,7 +1874,9 @@
       <c r="C103" t="n">
         <v>60.78466344124584</v>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>0.9912128530645902</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1684,7 +1888,9 @@
       <c r="C104" t="n">
         <v>50.48567520359704</v>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="n">
+        <v>0.9955395744692298</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1696,7 +1902,9 @@
       <c r="C105" t="n">
         <v>41.35935978814719</v>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>0.9936255012797661</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1708,7 +1916,9 @@
       <c r="C106" t="n">
         <v>42.82388935866014</v>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="n">
+        <v>0.9968943270731966</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1720,7 +1930,9 @@
       <c r="C107" t="n">
         <v>68.23917794835043</v>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="n">
+        <v>0.9906094292455848</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1732,7 +1944,9 @@
       <c r="C108" t="n">
         <v>59.83732978424243</v>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="n">
+        <v>0.9954613294293079</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1744,7 +1958,9 @@
       <c r="C109" t="n">
         <v>74.63434472715409</v>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="n">
+        <v>0.9977137082098798</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1756,7 +1972,9 @@
       <c r="C110" t="n">
         <v>43.8272972250524</v>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>0.9956551307612678</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1768,7 +1986,9 @@
       <c r="C111" t="n">
         <v>38.43265364638556</v>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>0.9928920392590816</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1780,7 +2000,9 @@
       <c r="C112" t="n">
         <v>43.35818692272822</v>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>0.995902164503297</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -1792,7 +2014,9 @@
       <c r="C113" t="n">
         <v>38.24494164978585</v>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="n">
+        <v>0.9930433755846241</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -1804,7 +2028,9 @@
       <c r="C114" t="n">
         <v>63.72798095751364</v>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0.9960173350956908</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -1816,7 +2042,9 @@
       <c r="C115" t="n">
         <v>67.53649305633806</v>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>0.9911550996129784</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -1828,7 +2056,9 @@
       <c r="C116" t="n">
         <v>32.72351644182054</v>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>0.992519925697763</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -1840,7 +2070,9 @@
       <c r="C117" t="n">
         <v>61.59257328408566</v>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>0.9902944654037722</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -1852,7 +2084,9 @@
       <c r="C118" t="n">
         <v>25.38818198523678</v>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="n">
+        <v>0.9907551845006642</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -1864,7 +2098,9 @@
       <c r="C119" t="n">
         <v>45.79677033582375</v>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="n">
+        <v>0.9949929265783486</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -1876,7 +2112,9 @@
       <c r="C120" t="n">
         <v>37.48719016337304</v>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="n">
+        <v>0.9920852839925307</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -1888,7 +2126,9 @@
       <c r="C121" t="n">
         <v>32.63044854100505</v>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="n">
+        <v>0.9946447432887395</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -1900,7 +2140,9 @@
       <c r="C122" t="n">
         <v>68.28707584039341</v>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="n">
+        <v>0.9959361257976556</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -1912,7 +2154,9 @@
       <c r="C123" t="n">
         <v>33.24305624591818</v>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>0.9979306756141457</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -1924,7 +2168,9 @@
       <c r="C124" t="n">
         <v>44.03556352239427</v>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>0.9931955491312968</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -1936,7 +2182,9 @@
       <c r="C125" t="n">
         <v>42.74363943603997</v>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="n">
+        <v>0.9928681106979487</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -1948,7 +2196,9 @@
       <c r="C126" t="n">
         <v>58.85095317494391</v>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="n">
+        <v>0.9928230006740743</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -1960,7 +2210,9 @@
       <c r="C127" t="n">
         <v>16.17394847958799</v>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="n">
+        <v>0.9910606468007196</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -1972,7 +2224,9 @@
       <c r="C128" t="n">
         <v>33.87766682607845</v>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="n">
+        <v>0.9959686502819154</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -1984,7 +2238,9 @@
       <c r="C129" t="n">
         <v>47.00209216877489</v>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="n">
+        <v>0.9973768912329349</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -1996,7 +2252,9 @@
       <c r="C130" t="n">
         <v>21.82843164035993</v>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="n">
+        <v>0.9942570437477669</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2008,7 +2266,9 @@
       <c r="C131" t="n">
         <v>60.99389115413728</v>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="n">
+        <v>0.9950246765725369</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2020,7 +2280,9 @@
       <c r="C132" t="n">
         <v>56.44673584598896</v>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="n">
+        <v>0.9986263210232605</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2032,7 +2294,9 @@
       <c r="C133" t="n">
         <v>69.7668412155984</v>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="n">
+        <v>0.9962902365448724</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2044,7 +2308,9 @@
       <c r="C134" t="n">
         <v>61.90100495581607</v>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>0.9967053139798289</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2056,7 +2322,9 @@
       <c r="C135" t="n">
         <v>67.47581972462075</v>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>0.9980054852157407</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2068,7 +2336,9 @@
       <c r="C136" t="n">
         <v>56.0214981912111</v>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="n">
+        <v>0.9919421151847571</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2080,7 +2350,9 @@
       <c r="C137" t="n">
         <v>50.95247214583335</v>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="n">
+        <v>0.9958514945248862</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2092,7 +2364,9 @@
       <c r="C138" t="n">
         <v>53.57551639207747</v>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="n">
+        <v>0.9964565505479376</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2104,7 +2378,9 @@
       <c r="C139" t="n">
         <v>50.14878729140165</v>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="n">
+        <v>0.9975800513675117</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2116,7 +2392,9 @@
       <c r="C140" t="n">
         <v>39.11919311989337</v>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="n">
+        <v>0.9930940699140171</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2128,7 +2406,9 @@
       <c r="C141" t="n">
         <v>57.67393992818478</v>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="n">
+        <v>0.9961991523514174</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2140,7 +2420,9 @@
       <c r="C142" t="n">
         <v>59.98976470976152</v>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="n">
+        <v>0.9954396054522234</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2152,7 +2434,9 @@
       <c r="C143" t="n">
         <v>61.29403023760543</v>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="n">
+        <v>0.993684249304404</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2164,7 +2448,9 @@
       <c r="C144" t="n">
         <v>41.06339365608342</v>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>0.9909151718137394</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2176,7 +2462,9 @@
       <c r="C145" t="n">
         <v>71.71488219151669</v>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>0.9931774359040483</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2188,7 +2476,9 @@
       <c r="C146" t="n">
         <v>33.21788065693907</v>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="n">
+        <v>0.9986713627330843</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2200,7 +2490,9 @@
       <c r="C147" t="n">
         <v>35.76532379625473</v>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="n">
+        <v>0.9919487115145151</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2212,7 +2504,9 @@
       <c r="C148" t="n">
         <v>50.30715431918719</v>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="n">
+        <v>0.9910227419422936</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2224,7 +2518,9 @@
       <c r="C149" t="n">
         <v>41.70098183161208</v>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="n">
+        <v>0.9933091148226331</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2236,7 +2532,9 @@
       <c r="C150" t="n">
         <v>25.71370826456232</v>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="n">
+        <v>0.9909088271289538</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2248,7 +2546,9 @@
       <c r="C151" t="n">
         <v>26.49052869939182</v>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="n">
+        <v>0.9924047903865264</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2260,7 +2560,9 @@
       <c r="C152" t="n">
         <v>63.90692432390129</v>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="n">
+        <v>0.9982301050989263</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2272,7 +2574,9 @@
       <c r="C153" t="n">
         <v>63.37928648737845</v>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="n">
+        <v>0.9928690387330102</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2284,7 +2588,9 @@
       <c r="C154" t="n">
         <v>25.12029222292051</v>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="n">
+        <v>0.9952730056309215</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2296,7 +2602,9 @@
       <c r="C155" t="n">
         <v>39.60329258760133</v>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="n">
+        <v>0.9921487030159946</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2308,7 +2616,9 @@
       <c r="C156" t="n">
         <v>12.21263075110782</v>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="n">
+        <v>0.9960118193195865</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2320,7 +2630,9 @@
       <c r="C157" t="n">
         <v>30.54834043508056</v>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="n">
+        <v>0.991148907488984</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2332,7 +2644,9 @@
       <c r="C158" t="n">
         <v>50.03149339688316</v>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="n">
+        <v>0.9971082844494795</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2344,7 +2658,9 @@
       <c r="C159" t="n">
         <v>47.94394853399143</v>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>0.9938065144029443</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2356,7 +2672,9 @@
       <c r="C160" t="n">
         <v>69.92956674357832</v>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="n">
+        <v>0.9916529434838228</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2368,7 +2686,9 @@
       <c r="C161" t="n">
         <v>31.9704602093228</v>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="n">
+        <v>0.9968242460908364</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2380,7 +2700,9 @@
       <c r="C162" t="n">
         <v>38.96577069630239</v>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>0.9949885428512451</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2392,7 +2714,9 @@
       <c r="C163" t="n">
         <v>39.39751136993004</v>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="n">
+        <v>0.9939433050929787</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2404,7 +2728,9 @@
       <c r="C164" t="n">
         <v>70.84264618277928</v>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="n">
+        <v>0.992165634376324</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2416,7 +2742,9 @@
       <c r="C165" t="n">
         <v>33.99966038162763</v>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="n">
+        <v>0.9970322930387524</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2428,7 +2756,9 @@
       <c r="C166" t="n">
         <v>56.52139609313584</v>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="n">
+        <v>0.9932875655103311</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2440,7 +2770,9 @@
       <c r="C167" t="n">
         <v>51.63354419283532</v>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="n">
+        <v>0.9903878162157114</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2452,7 +2784,9 @@
       <c r="C168" t="n">
         <v>47.10708506835977</v>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="n">
+        <v>0.9986883234286021</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2464,7 +2798,9 @@
       <c r="C169" t="n">
         <v>55.25408342657246</v>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="n">
+        <v>0.990274183273124</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2476,7 +2812,9 @@
       <c r="C170" t="n">
         <v>60.65846113009473</v>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="n">
+        <v>0.9910842216986149</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2488,7 +2826,9 @@
       <c r="C171" t="n">
         <v>89.11758782502773</v>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="n">
+        <v>0.9941923127789584</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2500,7 +2840,9 @@
       <c r="C172" t="n">
         <v>34.15141111167516</v>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="n">
+        <v>0.9918706944741474</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2512,7 +2854,9 @@
       <c r="C173" t="n">
         <v>81.70343159249632</v>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="n">
+        <v>0.9930162153382749</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2524,7 +2868,9 @@
       <c r="C174" t="n">
         <v>66.67672188427332</v>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="n">
+        <v>0.9951080871774001</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2536,7 +2882,9 @@
       <c r="C175" t="n">
         <v>55.87154050616485</v>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="n">
+        <v>0.9986205775703306</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2548,7 +2896,9 @@
       <c r="C176" t="n">
         <v>38.00322570895611</v>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="n">
+        <v>0.9984268100183206</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2560,7 +2910,9 @@
       <c r="C177" t="n">
         <v>29.69824828000953</v>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="n">
+        <v>0.9906650637826071</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2572,7 +2924,9 @@
       <c r="C178" t="n">
         <v>51.10642431092796</v>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="n">
+        <v>0.9976798229063399</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2584,7 +2938,9 @@
       <c r="C179" t="n">
         <v>58.24256654083357</v>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="n">
+        <v>0.9915104128961902</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2596,7 +2952,9 @@
       <c r="C180" t="n">
         <v>57.90753875284465</v>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="n">
+        <v>0.9973028958525291</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2608,7 +2966,9 @@
       <c r="C181" t="n">
         <v>37.82288482564915</v>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="n">
+        <v>0.9926671249606338</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2620,7 +2980,9 @@
       <c r="C182" t="n">
         <v>59.72710216882905</v>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="n">
+        <v>0.9964605092155461</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2632,7 +2994,9 @@
       <c r="C183" t="n">
         <v>30.0882005832016</v>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>0.9964691388452478</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2644,7 +3008,9 @@
       <c r="C184" t="n">
         <v>50.0340207885088</v>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="n">
+        <v>0.9976549613378072</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -2656,7 +3022,9 @@
       <c r="C185" t="n">
         <v>22.99356530034146</v>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="n">
+        <v>0.9988166326396635</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -2668,7 +3036,9 @@
       <c r="C186" t="n">
         <v>70.53643160720347</v>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="n">
+        <v>0.992479327675767</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -2680,7 +3050,9 @@
       <c r="C187" t="n">
         <v>69.30669020013021</v>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="n">
+        <v>0.9956547761280695</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -2692,7 +3064,9 @@
       <c r="C188" t="n">
         <v>53.28708600267237</v>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="n">
+        <v>0.9966533471607333</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -2704,7 +3078,9 @@
       <c r="C189" t="n">
         <v>58.33525434379268</v>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="n">
+        <v>0.9907166640381805</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -2716,7 +3092,9 @@
       <c r="C190" t="n">
         <v>52.21783588359124</v>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="n">
+        <v>0.9959666520399196</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -2728,7 +3106,9 @@
       <c r="C191" t="n">
         <v>73.04385275833977</v>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="n">
+        <v>0.9928936396377742</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -2740,7 +3120,9 @@
       <c r="C192" t="n">
         <v>47.88198415669979</v>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="n">
+        <v>0.9914532213839485</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -2752,7 +3134,9 @@
       <c r="C193" t="n">
         <v>31.82557362505747</v>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="n">
+        <v>0.9949452440205129</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -2764,7 +3148,9 @@
       <c r="C194" t="n">
         <v>7.703496491937528</v>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="n">
+        <v>0.9941569523736981</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -2776,7 +3162,9 @@
       <c r="C195" t="n">
         <v>57.38510043723399</v>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="n">
+        <v>0.9951937184966392</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -2788,7 +3176,9 @@
       <c r="C196" t="n">
         <v>21.07210778365031</v>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="n">
+        <v>0.9957772583136302</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -2800,7 +3190,9 @@
       <c r="C197" t="n">
         <v>50.77438967751996</v>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="n">
+        <v>0.9944880197521365</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -2812,7 +3204,9 @@
       <c r="C198" t="n">
         <v>59.94433851813749</v>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="n">
+        <v>0.9981463563669523</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -2824,7 +3218,9 @@
       <c r="C199" t="n">
         <v>18.08351560802339</v>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="n">
+        <v>0.9916012277855191</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -2836,7 +3232,9 @@
       <c r="C200" t="n">
         <v>48.88290551241017</v>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="n">
+        <v>0.9925991248410848</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -2848,7 +3246,9 @@
       <c r="C201" t="n">
         <v>60.19400006076078</v>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="n">
+        <v>0.9932059947706208</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -461,7 +461,7 @@
         <v>53.67919023703534</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9916104133230789</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>34.75107857408746</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9957592184914363</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>42.60628635542257</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9942054156102914</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>33.48190127293107</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9933345047439724</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>45.23196171646185</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9931942560087869</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>42.32918817317876</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9971146642126794</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>44.44014536248625</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9981462945300945</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +559,7 @@
         <v>47.94897151388241</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9915961787264075</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         <v>44.64165636479374</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9958750632241662</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         <v>28.02194103187311</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9926847249062001</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         <v>50.49475649543508</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9987026598014616</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>40.71306000432234</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9982786514448355</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         <v>47.09592044693731</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9957228372373018</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +643,7 @@
         <v>62.52548385599771</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9967745888737117</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -657,7 +657,7 @@
         <v>54.260886173613</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9946363832669012</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         <v>60.50559856437604</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9974330573253801</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         <v>71.04614060419865</v>
       </c>
       <c r="D18" t="n">
-        <v>0.994035424908601</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>58.55154095134137</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9930493120798238</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20">
@@ -713,7 +713,7 @@
         <v>51.66508863793452</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9925010929395014</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>78.40138622491851</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9920369975115906</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>48.7360258336366</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9947323515901072</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -755,7 +755,7 @@
         <v>49.85244703050946</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9938782085461598</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         <v>32.62033579304236</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9959686255842534</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="25">
@@ -783,7 +783,7 @@
         <v>66.86694939091855</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9901155643413012</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +797,7 @@
         <v>61.39125059256289</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9940293171138485</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="27">
@@ -811,7 +811,7 @@
         <v>27.60097501061821</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9932866272101916</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>57.44548841854294</v>
       </c>
       <c r="D28" t="n">
-        <v>0.991758578398844</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="29">
@@ -839,7 +839,7 @@
         <v>64.2897180394438</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9953537928390545</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +853,7 @@
         <v>51.04424473508528</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9939178184035558</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +867,7 @@
         <v>26.35625682329916</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9926999235337064</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="32">
@@ -881,7 +881,7 @@
         <v>47.49475732167166</v>
       </c>
       <c r="D32" t="n">
-        <v>0.991884745091126</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="33">
@@ -895,7 +895,7 @@
         <v>37.53758065048235</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9978716165147297</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="34">
@@ -909,7 +909,7 @@
         <v>37.42441453674519</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9971771608396929</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="35">
@@ -923,7 +923,7 @@
         <v>54.82631099740421</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9954603870901648</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="36">
@@ -937,7 +937,7 @@
         <v>52.8998657286197</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9931059052080056</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="37">
@@ -951,7 +951,7 @@
         <v>64.07692484117138</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9985213781188168</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="38">
@@ -965,7 +965,7 @@
         <v>15.02018996783411</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9950703963705229</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="39">
@@ -979,7 +979,7 @@
         <v>23.07587490327965</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9938948646565796</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="40">
@@ -993,7 +993,7 @@
         <v>58.40841188526452</v>
       </c>
       <c r="D40" t="n">
-        <v>0.998104046391038</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="41">
@@ -1007,7 +1007,7 @@
         <v>31.82746499262569</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9928740762351168</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="42">
@@ -1021,7 +1021,7 @@
         <v>35.37733090673469</v>
       </c>
       <c r="D42" t="n">
-        <v>0.996263953831204</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="43">
@@ -1035,7 +1035,7 @@
         <v>41.61615719019</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9928243829453614</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="44">
@@ -1049,7 +1049,7 @@
         <v>44.81145220748102</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9923539774168062</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="45">
@@ -1063,7 +1063,7 @@
         <v>49.06743572749054</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9963075680055077</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="46">
@@ -1077,7 +1077,7 @@
         <v>33.5774453963048</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9920510278101662</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -1091,7 +1091,7 @@
         <v>57.46522201167969</v>
       </c>
       <c r="D47" t="n">
-        <v>0.994437992906864</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="48">
@@ -1105,7 +1105,7 @@
         <v>52.03102919872997</v>
       </c>
       <c r="D48" t="n">
-        <v>0.995220256077185</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -1119,7 +1119,7 @@
         <v>50.57254956738563</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9917001572827902</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="50">
@@ -1133,7 +1133,7 @@
         <v>48.54148684428007</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9965811659252261</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="51">
@@ -1147,7 +1147,7 @@
         <v>73.82498461236125</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9949363475816216</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="52">
@@ -1161,7 +1161,7 @@
         <v>64.0560547756331</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9955935293366335</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="53">
@@ -1175,7 +1175,7 @@
         <v>44.29222473466736</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9933492988511715</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="54">
@@ -1189,7 +1189,7 @@
         <v>59.51537785616269</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9937817393392857</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="55">
@@ -1203,7 +1203,7 @@
         <v>55.06770176992225</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9944534671012535</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="56">
@@ -1217,7 +1217,7 @@
         <v>51.2529958529192</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9942297382116555</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="57">
@@ -1231,7 +1231,7 @@
         <v>32.35552130588029</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9960807530056466</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="58">
@@ -1245,7 +1245,7 @@
         <v>52.65079504580522</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9951945975404658</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="59">
@@ -1259,7 +1259,7 @@
         <v>53.2344844792981</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9937464357869322</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="60">
@@ -1273,7 +1273,7 @@
         <v>55.85981383545153</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9900162211824614</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="61">
@@ -1287,7 +1287,7 @@
         <v>56.84249730850535</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9971462795469795</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="62">
@@ -1301,7 +1301,7 @@
         <v>56.04683541536205</v>
       </c>
       <c r="D62" t="n">
-        <v>0.994674457990299</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="63">
@@ -1315,7 +1315,7 @@
         <v>42.9238407328732</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9929389019743015</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="64">
@@ -1329,7 +1329,7 @@
         <v>67.33541070056265</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9944995952017007</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="65">
@@ -1343,7 +1343,7 @@
         <v>46.42083313914934</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9908410134014516</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="66">
@@ -1357,7 +1357,7 @@
         <v>20.15246335861512</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9981423366529801</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="67">
@@ -1371,7 +1371,7 @@
         <v>64.71781357938394</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9989076255082605</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="68">
@@ -1385,7 +1385,7 @@
         <v>20.9709849543949</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9905286169576403</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="69">
@@ -1399,7 +1399,7 @@
         <v>54.59209029064667</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9932240809673224</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="70">
@@ -1413,7 +1413,7 @@
         <v>54.35771212243785</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9965705812003718</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="71">
@@ -1427,7 +1427,7 @@
         <v>55.59379252137557</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9928281431809609</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="72">
@@ -1441,7 +1441,7 @@
         <v>66.00212359285925</v>
       </c>
       <c r="D72" t="n">
-        <v>0.99510344782528</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="73">
@@ -1455,7 +1455,7 @@
         <v>50.87657503292501</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9937491386608353</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="74">
@@ -1469,7 +1469,7 @@
         <v>40.3001338986972</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9969679094186779</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="75">
@@ -1483,7 +1483,7 @@
         <v>43.29408133550469</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9986261796086763</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="76">
@@ -1497,7 +1497,7 @@
         <v>72.45615876012165</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9979955588368501</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="77">
@@ -1511,7 +1511,7 @@
         <v>71.96958543119473</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9955884191868004</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="78">
@@ -1525,7 +1525,7 @@
         <v>31.71903097672782</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9914424688140127</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="79">
@@ -1539,7 +1539,7 @@
         <v>24.78238876433949</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9985235587498049</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="80">
@@ -1553,7 +1553,7 @@
         <v>35.78474079132059</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9902126918580459</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="81">
@@ -1567,7 +1567,7 @@
         <v>85.86880632972213</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9926793851077877</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="82">
@@ -1581,7 +1581,7 @@
         <v>54.84551943934476</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9925345214379053</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="83">
@@ -1595,7 +1595,7 @@
         <v>42.02852297835588</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9960464338355043</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="84">
@@ -1609,7 +1609,7 @@
         <v>21.24799500474111</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9943862675946527</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="85">
@@ -1623,7 +1623,7 @@
         <v>29.26763733809423</v>
       </c>
       <c r="D85" t="n">
-        <v>0.990835996938817</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="86">
@@ -1637,7 +1637,7 @@
         <v>26.00454916311631</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9901157209897044</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="87">
@@ -1651,7 +1651,7 @@
         <v>49.24023764655826</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9954388417209628</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="88">
@@ -1665,7 +1665,7 @@
         <v>58.69657861547959</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9944233499910683</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="89">
@@ -1679,7 +1679,7 @@
         <v>38.56371252741226</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9954124390920636</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="90">
@@ -1693,7 +1693,7 @@
         <v>52.50241733428958</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9950762147747898</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="91">
@@ -1707,7 +1707,7 @@
         <v>36.73129929489149</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9980141319746971</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="92">
@@ -1721,7 +1721,7 @@
         <v>38.354514288082</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9982655717208354</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="93">
@@ -1735,7 +1735,7 @@
         <v>35.67810581622993</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9916943144499213</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="94">
@@ -1749,7 +1749,7 @@
         <v>53.07213893313723</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9984790878252348</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="95">
@@ -1763,7 +1763,7 @@
         <v>48.86920189220226</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9970895396369051</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="96">
@@ -1777,7 +1777,7 @@
         <v>62.85358877955228</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9957512362700067</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="97">
@@ -1791,7 +1791,7 @@
         <v>51.47706433991497</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9959364654074185</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="98">
@@ -1805,7 +1805,7 @@
         <v>62.72713000736199</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9949145420691058</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="99">
@@ -1819,7 +1819,7 @@
         <v>30.1299770846383</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9982553696967855</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="100">
@@ -1833,7 +1833,7 @@
         <v>36.75800440157938</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9920993688558012</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="101">
@@ -1847,7 +1847,7 @@
         <v>63.89390408530792</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9953938439304262</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="102">
@@ -1861,7 +1861,7 @@
         <v>26.79910170703495</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9973281875568448</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="103">
@@ -1875,7 +1875,7 @@
         <v>60.78466344124584</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9912128530645902</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="104">
@@ -1889,7 +1889,7 @@
         <v>50.48567520359704</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9955395744692298</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="105">
@@ -1903,7 +1903,7 @@
         <v>41.35935978814719</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9936255012797661</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="106">
@@ -1917,7 +1917,7 @@
         <v>42.82388935866014</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9968943270731966</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="107">
@@ -1931,7 +1931,7 @@
         <v>68.23917794835043</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9906094292455848</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="108">
@@ -1945,7 +1945,7 @@
         <v>59.83732978424243</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9954613294293079</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="109">
@@ -1959,7 +1959,7 @@
         <v>74.63434472715409</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9977137082098798</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="110">
@@ -1973,7 +1973,7 @@
         <v>43.8272972250524</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9956551307612678</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="111">
@@ -1987,7 +1987,7 @@
         <v>38.43265364638556</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9928920392590816</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="112">
@@ -2001,7 +2001,7 @@
         <v>43.35818692272822</v>
       </c>
       <c r="D112" t="n">
-        <v>0.995902164503297</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="113">
@@ -2015,7 +2015,7 @@
         <v>38.24494164978585</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9930433755846241</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="114">
@@ -2029,7 +2029,7 @@
         <v>63.72798095751364</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9960173350956908</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="115">
@@ -2043,7 +2043,7 @@
         <v>67.53649305633806</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9911550996129784</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="116">
@@ -2057,7 +2057,7 @@
         <v>32.72351644182054</v>
       </c>
       <c r="D116" t="n">
-        <v>0.992519925697763</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="117">
@@ -2071,7 +2071,7 @@
         <v>61.59257328408566</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9902944654037722</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="118">
@@ -2085,7 +2085,7 @@
         <v>25.38818198523678</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9907551845006642</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="119">
@@ -2099,7 +2099,7 @@
         <v>45.79677033582375</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9949929265783486</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="120">
@@ -2113,7 +2113,7 @@
         <v>37.48719016337304</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9920852839925307</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="121">
@@ -2127,7 +2127,7 @@
         <v>32.63044854100505</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9946447432887395</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="122">
@@ -2141,7 +2141,7 @@
         <v>68.28707584039341</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9959361257976556</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="123">
@@ -2155,7 +2155,7 @@
         <v>33.24305624591818</v>
       </c>
       <c r="D123" t="n">
-        <v>0.9979306756141457</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="124">
@@ -2169,7 +2169,7 @@
         <v>44.03556352239427</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9931955491312968</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="125">
@@ -2183,7 +2183,7 @@
         <v>42.74363943603997</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9928681106979487</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="126">
@@ -2197,7 +2197,7 @@
         <v>58.85095317494391</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9928230006740743</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="127">
@@ -2211,7 +2211,7 @@
         <v>16.17394847958799</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9910606468007196</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="128">
@@ -2225,7 +2225,7 @@
         <v>33.87766682607845</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9959686502819154</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="129">
@@ -2239,7 +2239,7 @@
         <v>47.00209216877489</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9973768912329349</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="130">
@@ -2253,7 +2253,7 @@
         <v>21.82843164035993</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9942570437477669</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="131">
@@ -2267,7 +2267,7 @@
         <v>60.99389115413728</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9950246765725369</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="132">
@@ -2281,7 +2281,7 @@
         <v>56.44673584598896</v>
       </c>
       <c r="D132" t="n">
-        <v>0.9986263210232605</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="133">
@@ -2295,7 +2295,7 @@
         <v>69.7668412155984</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9962902365448724</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="134">
@@ -2309,7 +2309,7 @@
         <v>61.90100495581607</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9967053139798289</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="135">
@@ -2323,7 +2323,7 @@
         <v>67.47581972462075</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9980054852157407</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="136">
@@ -2337,7 +2337,7 @@
         <v>56.0214981912111</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9919421151847571</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="137">
@@ -2351,7 +2351,7 @@
         <v>50.95247214583335</v>
       </c>
       <c r="D137" t="n">
-        <v>0.9958514945248862</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="138">
@@ -2365,7 +2365,7 @@
         <v>53.57551639207747</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9964565505479376</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="139">
@@ -2379,7 +2379,7 @@
         <v>50.14878729140165</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9975800513675117</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="140">
@@ -2393,7 +2393,7 @@
         <v>39.11919311989337</v>
       </c>
       <c r="D140" t="n">
-        <v>0.9930940699140171</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="141">
@@ -2407,7 +2407,7 @@
         <v>57.67393992818478</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9961991523514174</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="142">
@@ -2421,7 +2421,7 @@
         <v>59.98976470976152</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9954396054522234</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="143">
@@ -2435,7 +2435,7 @@
         <v>61.29403023760543</v>
       </c>
       <c r="D143" t="n">
-        <v>0.993684249304404</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="144">
@@ -2449,7 +2449,7 @@
         <v>41.06339365608342</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9909151718137394</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="145">
@@ -2463,7 +2463,7 @@
         <v>71.71488219151669</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9931774359040483</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="146">
@@ -2477,7 +2477,7 @@
         <v>33.21788065693907</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9986713627330843</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="147">
@@ -2491,7 +2491,7 @@
         <v>35.76532379625473</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9919487115145151</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="148">
@@ -2505,7 +2505,7 @@
         <v>50.30715431918719</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9910227419422936</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="149">
@@ -2519,7 +2519,7 @@
         <v>41.70098183161208</v>
       </c>
       <c r="D149" t="n">
-        <v>0.9933091148226331</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="150">
@@ -2533,7 +2533,7 @@
         <v>25.71370826456232</v>
       </c>
       <c r="D150" t="n">
-        <v>0.9909088271289538</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="151">
@@ -2547,7 +2547,7 @@
         <v>26.49052869939182</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9924047903865264</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="152">
@@ -2561,7 +2561,7 @@
         <v>63.90692432390129</v>
       </c>
       <c r="D152" t="n">
-        <v>0.9982301050989263</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="153">
@@ -2575,7 +2575,7 @@
         <v>63.37928648737845</v>
       </c>
       <c r="D153" t="n">
-        <v>0.9928690387330102</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="154">
@@ -2589,7 +2589,7 @@
         <v>25.12029222292051</v>
       </c>
       <c r="D154" t="n">
-        <v>0.9952730056309215</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="155">
@@ -2603,7 +2603,7 @@
         <v>39.60329258760133</v>
       </c>
       <c r="D155" t="n">
-        <v>0.9921487030159946</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="156">
@@ -2617,7 +2617,7 @@
         <v>12.21263075110782</v>
       </c>
       <c r="D156" t="n">
-        <v>0.9960118193195865</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="157">
@@ -2631,7 +2631,7 @@
         <v>30.54834043508056</v>
       </c>
       <c r="D157" t="n">
-        <v>0.991148907488984</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="158">
@@ -2645,7 +2645,7 @@
         <v>50.03149339688316</v>
       </c>
       <c r="D158" t="n">
-        <v>0.9971082844494795</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="159">
@@ -2659,7 +2659,7 @@
         <v>47.94394853399143</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9938065144029443</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="160">
@@ -2673,7 +2673,7 @@
         <v>69.92956674357832</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9916529434838228</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="161">
@@ -2687,7 +2687,7 @@
         <v>31.9704602093228</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9968242460908364</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="162">
@@ -2701,7 +2701,7 @@
         <v>38.96577069630239</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9949885428512451</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="163">
@@ -2715,7 +2715,7 @@
         <v>39.39751136993004</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9939433050929787</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="164">
@@ -2729,7 +2729,7 @@
         <v>70.84264618277928</v>
       </c>
       <c r="D164" t="n">
-        <v>0.992165634376324</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="165">
@@ -2743,7 +2743,7 @@
         <v>33.99966038162763</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9970322930387524</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="166">
@@ -2757,7 +2757,7 @@
         <v>56.52139609313584</v>
       </c>
       <c r="D166" t="n">
-        <v>0.9932875655103311</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="167">
@@ -2771,7 +2771,7 @@
         <v>51.63354419283532</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9903878162157114</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="168">
@@ -2785,7 +2785,7 @@
         <v>47.10708506835977</v>
       </c>
       <c r="D168" t="n">
-        <v>0.9986883234286021</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="169">
@@ -2799,7 +2799,7 @@
         <v>55.25408342657246</v>
       </c>
       <c r="D169" t="n">
-        <v>0.990274183273124</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="170">
@@ -2813,7 +2813,7 @@
         <v>60.65846113009473</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9910842216986149</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="171">
@@ -2827,7 +2827,7 @@
         <v>89.11758782502773</v>
       </c>
       <c r="D171" t="n">
-        <v>0.9941923127789584</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="172">
@@ -2841,7 +2841,7 @@
         <v>34.15141111167516</v>
       </c>
       <c r="D172" t="n">
-        <v>0.9918706944741474</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="173">
@@ -2855,7 +2855,7 @@
         <v>81.70343159249632</v>
       </c>
       <c r="D173" t="n">
-        <v>0.9930162153382749</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="174">
@@ -2869,7 +2869,7 @@
         <v>66.67672188427332</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9951080871774001</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="175">
@@ -2883,7 +2883,7 @@
         <v>55.87154050616485</v>
       </c>
       <c r="D175" t="n">
-        <v>0.9986205775703306</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="176">
@@ -2897,7 +2897,7 @@
         <v>38.00322570895611</v>
       </c>
       <c r="D176" t="n">
-        <v>0.9984268100183206</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="177">
@@ -2911,7 +2911,7 @@
         <v>29.69824828000953</v>
       </c>
       <c r="D177" t="n">
-        <v>0.9906650637826071</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="178">
@@ -2925,7 +2925,7 @@
         <v>51.10642431092796</v>
       </c>
       <c r="D178" t="n">
-        <v>0.9976798229063399</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="179">
@@ -2939,7 +2939,7 @@
         <v>58.24256654083357</v>
       </c>
       <c r="D179" t="n">
-        <v>0.9915104128961902</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="180">
@@ -2953,7 +2953,7 @@
         <v>57.90753875284465</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9973028958525291</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="181">
@@ -2967,7 +2967,7 @@
         <v>37.82288482564915</v>
       </c>
       <c r="D181" t="n">
-        <v>0.9926671249606338</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="182">
@@ -2981,7 +2981,7 @@
         <v>59.72710216882905</v>
       </c>
       <c r="D182" t="n">
-        <v>0.9964605092155461</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="183">
@@ -2995,7 +2995,7 @@
         <v>30.0882005832016</v>
       </c>
       <c r="D183" t="n">
-        <v>0.9964691388452478</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="184">
@@ -3009,7 +3009,7 @@
         <v>50.0340207885088</v>
       </c>
       <c r="D184" t="n">
-        <v>0.9976549613378072</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="185">
@@ -3023,7 +3023,7 @@
         <v>22.99356530034146</v>
       </c>
       <c r="D185" t="n">
-        <v>0.9988166326396635</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="186">
@@ -3037,7 +3037,7 @@
         <v>70.53643160720347</v>
       </c>
       <c r="D186" t="n">
-        <v>0.992479327675767</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="187">
@@ -3051,7 +3051,7 @@
         <v>69.30669020013021</v>
       </c>
       <c r="D187" t="n">
-        <v>0.9956547761280695</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="188">
@@ -3065,7 +3065,7 @@
         <v>53.28708600267237</v>
       </c>
       <c r="D188" t="n">
-        <v>0.9966533471607333</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="189">
@@ -3079,7 +3079,7 @@
         <v>58.33525434379268</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9907166640381805</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="190">
@@ -3093,7 +3093,7 @@
         <v>52.21783588359124</v>
       </c>
       <c r="D190" t="n">
-        <v>0.9959666520399196</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="191">
@@ -3107,7 +3107,7 @@
         <v>73.04385275833977</v>
       </c>
       <c r="D191" t="n">
-        <v>0.9928936396377742</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="192">
@@ -3121,7 +3121,7 @@
         <v>47.88198415669979</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9914532213839485</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="193">
@@ -3135,7 +3135,7 @@
         <v>31.82557362505747</v>
       </c>
       <c r="D193" t="n">
-        <v>0.9949452440205129</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="194">
@@ -3149,7 +3149,7 @@
         <v>7.703496491937528</v>
       </c>
       <c r="D194" t="n">
-        <v>0.9941569523736981</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="195">
@@ -3163,7 +3163,7 @@
         <v>57.38510043723399</v>
       </c>
       <c r="D195" t="n">
-        <v>0.9951937184966392</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="196">
@@ -3177,7 +3177,7 @@
         <v>21.07210778365031</v>
       </c>
       <c r="D196" t="n">
-        <v>0.9957772583136302</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="197">
@@ -3191,7 +3191,7 @@
         <v>50.77438967751996</v>
       </c>
       <c r="D197" t="n">
-        <v>0.9944880197521365</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="198">
@@ -3205,7 +3205,7 @@
         <v>59.94433851813749</v>
       </c>
       <c r="D198" t="n">
-        <v>0.9981463563669523</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="199">
@@ -3219,7 +3219,7 @@
         <v>18.08351560802339</v>
       </c>
       <c r="D199" t="n">
-        <v>0.9916012277855191</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="200">
@@ -3233,7 +3233,7 @@
         <v>48.88290551241017</v>
       </c>
       <c r="D200" t="n">
-        <v>0.9925991248410848</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="201">
@@ -3247,7 +3247,7 @@
         <v>60.19400006076078</v>
       </c>
       <c r="D201" t="n">
-        <v>0.9932059947706208</v>
+        <v>0.9999</v>
       </c>
     </row>
   </sheetData>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>53.67919023703534</v>
+        <v>41.18660072296451</v>
       </c>
       <c r="D2" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>34.75107857408746</v>
+        <v>52.49893749629924</v>
       </c>
       <c r="D3" t="n">
         <v>0.99</v>
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60628635542257</v>
+        <v>38.4524359711053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>33.48190127293107</v>
+        <v>37.46952456002418</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>45.23196171646185</v>
+        <v>35.89237509210422</v>
       </c>
       <c r="D6" t="n">
         <v>0.999</v>
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>42.32918817317876</v>
+        <v>56.80470161257504</v>
       </c>
       <c r="D7" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>44.44014536248625</v>
+        <v>35.17874630885516</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="9">
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>47.94897151388241</v>
+        <v>34.58005024902967</v>
       </c>
       <c r="D9" t="n">
         <v>0.9999</v>
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C10" t="n">
-        <v>44.64165636479374</v>
+        <v>31.09847929715623</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>28.02194103187311</v>
+        <v>47.29836019196955</v>
       </c>
       <c r="D11" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="12">
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C12" t="n">
-        <v>50.49475649543508</v>
+        <v>61.67268359677115</v>
       </c>
       <c r="D12" t="n">
         <v>0.9999</v>
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>40.71306000432234</v>
+        <v>74.97898034473121</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C14" t="n">
-        <v>47.09592044693731</v>
+        <v>53.39769823120358</v>
       </c>
       <c r="D14" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>62.52548385599771</v>
+        <v>31.52700383387826</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>54.260886173613</v>
+        <v>37.42323827165436</v>
       </c>
       <c r="D16" t="n">
         <v>0.999</v>
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C17" t="n">
-        <v>60.50559856437604</v>
+        <v>43.03833860806844</v>
       </c>
       <c r="D17" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C18" t="n">
-        <v>71.04614060419865</v>
+        <v>36.13914194349104</v>
       </c>
       <c r="D18" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>58.55154095134137</v>
+        <v>69.05633539980356</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="20">
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C20" t="n">
-        <v>51.66508863793452</v>
+        <v>93.70223274952224</v>
       </c>
       <c r="D20" t="n">
         <v>0.9</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C21" t="n">
-        <v>78.40138622491851</v>
+        <v>58.42561777988465</v>
       </c>
       <c r="D21" t="n">
         <v>0.9999</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C22" t="n">
-        <v>48.7360258336366</v>
+        <v>82.66761935917904</v>
       </c>
       <c r="D22" t="n">
         <v>0.9</v>
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="n">
-        <v>49.85244703050946</v>
+        <v>41.70852559551759</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C24" t="n">
-        <v>32.62033579304236</v>
+        <v>58.72350280538402</v>
       </c>
       <c r="D24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C25" t="n">
-        <v>66.86694939091855</v>
+        <v>65.08432168456005</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C26" t="n">
-        <v>61.39125059256289</v>
+        <v>29.89909932766966</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="C27" t="n">
-        <v>27.60097501061821</v>
+        <v>61.24886902276679</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C28" t="n">
-        <v>57.44548841854294</v>
+        <v>7.618577231622631</v>
       </c>
       <c r="D28" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C29" t="n">
-        <v>64.2897180394438</v>
+        <v>54.16090387643604</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="30">
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C30" t="n">
-        <v>51.04424473508528</v>
+        <v>56.93875585040984</v>
       </c>
       <c r="D30" t="n">
         <v>0.99</v>
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C31" t="n">
-        <v>26.35625682329916</v>
+        <v>56.1587731842232</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32">
@@ -875,13 +875,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C32" t="n">
-        <v>47.49475732167166</v>
+        <v>30.41183834938715</v>
       </c>
       <c r="D32" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="33">
@@ -889,13 +889,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>37.53758065048235</v>
+        <v>23.54143680572582</v>
       </c>
       <c r="D33" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="34">
@@ -903,13 +903,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>37.42441453674519</v>
+        <v>49.80369741361291</v>
       </c>
       <c r="D34" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="35">
@@ -917,13 +917,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C35" t="n">
-        <v>54.82631099740421</v>
+        <v>36.63867223316725</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="36">
@@ -931,13 +931,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C36" t="n">
-        <v>52.8998657286197</v>
+        <v>58.11820636548175</v>
       </c>
       <c r="D36" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="37">
@@ -945,13 +945,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C37" t="n">
-        <v>64.07692484117138</v>
+        <v>40.22751856744325</v>
       </c>
       <c r="D37" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="38">
@@ -959,10 +959,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C38" t="n">
-        <v>15.02018996783411</v>
+        <v>43.09314145828443</v>
       </c>
       <c r="D38" t="n">
         <v>0.999</v>
@@ -973,13 +973,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="C39" t="n">
-        <v>23.07587490327965</v>
+        <v>35.92630785767798</v>
       </c>
       <c r="D39" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="40">
@@ -987,13 +987,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C40" t="n">
-        <v>58.40841188526452</v>
+        <v>71.57438942494069</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="41">
@@ -1001,10 +1001,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C41" t="n">
-        <v>31.82746499262569</v>
+        <v>60.48771917205494</v>
       </c>
       <c r="D41" t="n">
         <v>0.9</v>
@@ -1015,10 +1015,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C42" t="n">
-        <v>35.37733090673469</v>
+        <v>68.88254121078265</v>
       </c>
       <c r="D42" t="n">
         <v>0.999</v>
@@ -1029,10 +1029,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>41.61615719019</v>
+        <v>30.7162765035165</v>
       </c>
       <c r="D43" t="n">
         <v>0.99</v>
@@ -1043,13 +1043,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="C44" t="n">
-        <v>44.81145220748102</v>
+        <v>51.74544586972218</v>
       </c>
       <c r="D44" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="45">
@@ -1057,13 +1057,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C45" t="n">
-        <v>49.06743572749054</v>
+        <v>60.37964170327503</v>
       </c>
       <c r="D45" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="46">
@@ -1071,10 +1071,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="C46" t="n">
-        <v>33.5774453963048</v>
+        <v>48.34006272225907</v>
       </c>
       <c r="D46" t="n">
         <v>0.9</v>
@@ -1085,13 +1085,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C47" t="n">
-        <v>57.46522201167969</v>
+        <v>54.98922155860479</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="48">
@@ -1099,13 +1099,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C48" t="n">
-        <v>52.03102919872997</v>
+        <v>57.9849148603933</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="49">
@@ -1113,10 +1113,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C49" t="n">
-        <v>50.57254956738563</v>
+        <v>36.90852090884079</v>
       </c>
       <c r="D49" t="n">
         <v>0.999</v>
@@ -1127,13 +1127,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C50" t="n">
-        <v>48.54148684428007</v>
+        <v>77.82169179675695</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="51">
@@ -1141,13 +1141,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C51" t="n">
-        <v>73.82498461236125</v>
+        <v>38.84398113564195</v>
       </c>
       <c r="D51" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="52">
@@ -1155,13 +1155,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="C52" t="n">
-        <v>64.0560547756331</v>
+        <v>45.18055483659527</v>
       </c>
       <c r="D52" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="53">
@@ -1169,13 +1169,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>44.29222473466736</v>
+        <v>60.69736733515805</v>
       </c>
       <c r="D53" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="54">
@@ -1183,13 +1183,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C54" t="n">
-        <v>59.51537785616269</v>
+        <v>44.93599810598114</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="55">
@@ -1197,10 +1197,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C55" t="n">
-        <v>55.06770176992225</v>
+        <v>58.09709982370419</v>
       </c>
       <c r="D55" t="n">
         <v>0.999</v>
@@ -1214,10 +1214,10 @@
         <v>20</v>
       </c>
       <c r="C56" t="n">
-        <v>51.2529958529192</v>
+        <v>35.92094115466597</v>
       </c>
       <c r="D56" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="57">
@@ -1225,13 +1225,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C57" t="n">
-        <v>32.35552130588029</v>
+        <v>38.07572159742486</v>
       </c>
       <c r="D57" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="58">
@@ -1239,10 +1239,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C58" t="n">
-        <v>52.65079504580522</v>
+        <v>74.36347994907064</v>
       </c>
       <c r="D58" t="n">
         <v>0.99</v>
@@ -1253,13 +1253,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C59" t="n">
-        <v>53.2344844792981</v>
+        <v>49.9565575271561</v>
       </c>
       <c r="D59" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="60">
@@ -1267,10 +1267,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>55.85981383545153</v>
+        <v>32.0112827209538</v>
       </c>
       <c r="D60" t="n">
         <v>0.9</v>
@@ -1281,10 +1281,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C61" t="n">
-        <v>56.84249730850535</v>
+        <v>54.89734505811601</v>
       </c>
       <c r="D61" t="n">
         <v>0.999</v>
@@ -1295,13 +1295,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>56.04683541536205</v>
+        <v>64.51122042621715</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="63">
@@ -1309,13 +1309,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C63" t="n">
-        <v>42.9238407328732</v>
+        <v>54.49276986088906</v>
       </c>
       <c r="D63" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="64">
@@ -1323,13 +1323,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>67.33541070056265</v>
+        <v>43.54518328195375</v>
       </c>
       <c r="D64" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="65">
@@ -1337,13 +1337,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="C65" t="n">
-        <v>46.42083313914934</v>
+        <v>26.46595227451997</v>
       </c>
       <c r="D65" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="66">
@@ -1351,13 +1351,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="C66" t="n">
-        <v>20.15246335861512</v>
+        <v>49.73613305814442</v>
       </c>
       <c r="D66" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="67">
@@ -1365,13 +1365,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C67" t="n">
-        <v>64.71781357938394</v>
+        <v>58.56362920852447</v>
       </c>
       <c r="D67" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="68">
@@ -1379,13 +1379,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="C68" t="n">
-        <v>20.9709849543949</v>
+        <v>67.2347419802137</v>
       </c>
       <c r="D68" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="69">
@@ -1393,13 +1393,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="C69" t="n">
-        <v>54.59209029064667</v>
+        <v>11.97211002813287</v>
       </c>
       <c r="D69" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="70">
@@ -1407,13 +1407,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C70" t="n">
-        <v>54.35771212243785</v>
+        <v>69.88321307864339</v>
       </c>
       <c r="D70" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="71">
@@ -1421,13 +1421,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C71" t="n">
-        <v>55.59379252137557</v>
+        <v>65.52480961623445</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="72">
@@ -1435,13 +1435,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C72" t="n">
-        <v>66.00212359285925</v>
+        <v>94.10776738862424</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="73">
@@ -1449,13 +1449,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C73" t="n">
-        <v>50.87657503292501</v>
+        <v>34.3146829850063</v>
       </c>
       <c r="D73" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="74">
@@ -1463,13 +1463,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C74" t="n">
-        <v>40.3001338986972</v>
+        <v>43.66557986655914</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="75">
@@ -1477,13 +1477,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>43.29408133550469</v>
+        <v>23.22991551603931</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="76">
@@ -1491,10 +1491,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C76" t="n">
-        <v>72.45615876012165</v>
+        <v>51.54008678567424</v>
       </c>
       <c r="D76" t="n">
         <v>0.999</v>
@@ -1505,10 +1505,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="C77" t="n">
-        <v>71.96958543119473</v>
+        <v>48.86374401612555</v>
       </c>
       <c r="D77" t="n">
         <v>0.9999</v>
@@ -1519,13 +1519,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="C78" t="n">
-        <v>31.71903097672782</v>
+        <v>42.39688034884901</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="79">
@@ -1533,13 +1533,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="C79" t="n">
-        <v>24.78238876433949</v>
+        <v>53.27300922066683</v>
       </c>
       <c r="D79" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="80">
@@ -1547,13 +1547,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C80" t="n">
-        <v>35.78474079132059</v>
+        <v>67.89788227108647</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="81">
@@ -1561,10 +1561,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C81" t="n">
-        <v>85.86880632972213</v>
+        <v>37.56300422461504</v>
       </c>
       <c r="D81" t="n">
         <v>0.9999</v>
@@ -1575,10 +1575,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C82" t="n">
-        <v>54.84551943934476</v>
+        <v>35.01610453939815</v>
       </c>
       <c r="D82" t="n">
         <v>0.99</v>
@@ -1589,13 +1589,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C83" t="n">
-        <v>42.02852297835588</v>
+        <v>72.88885847789385</v>
       </c>
       <c r="D83" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="84">
@@ -1603,13 +1603,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C84" t="n">
-        <v>21.24799500474111</v>
+        <v>78.19701091701387</v>
       </c>
       <c r="D84" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="85">
@@ -1617,13 +1617,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="C85" t="n">
-        <v>29.26763733809423</v>
+        <v>47.94075382571584</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="86">
@@ -1631,13 +1631,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="C86" t="n">
-        <v>26.00454916311631</v>
+        <v>41.73936825484108</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="87">
@@ -1645,13 +1645,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C87" t="n">
-        <v>49.24023764655826</v>
+        <v>45.23541136621797</v>
       </c>
       <c r="D87" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="88">
@@ -1659,13 +1659,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C88" t="n">
-        <v>58.69657861547959</v>
+        <v>27.01222092464516</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="89">
@@ -1673,13 +1673,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C89" t="n">
-        <v>38.56371252741226</v>
+        <v>50.42855760179366</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="90">
@@ -1687,10 +1687,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C90" t="n">
-        <v>52.50241733428958</v>
+        <v>50.70537992598002</v>
       </c>
       <c r="D90" t="n">
         <v>0.9999</v>
@@ -1701,13 +1701,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="C91" t="n">
-        <v>36.73129929489149</v>
+        <v>24.95083805225507</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="92">
@@ -1715,13 +1715,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C92" t="n">
-        <v>38.354514288082</v>
+        <v>15.26379097441664</v>
       </c>
       <c r="D92" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="93">
@@ -1729,13 +1729,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C93" t="n">
-        <v>35.67810581622993</v>
+        <v>61.26663730927602</v>
       </c>
       <c r="D93" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="94">
@@ -1743,10 +1743,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C94" t="n">
-        <v>53.07213893313723</v>
+        <v>48.35952024052171</v>
       </c>
       <c r="D94" t="n">
         <v>0.999</v>
@@ -1757,13 +1757,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="C95" t="n">
-        <v>48.86920189220226</v>
+        <v>69.89267692845807</v>
       </c>
       <c r="D95" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="96">
@@ -1771,13 +1771,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C96" t="n">
-        <v>62.85358877955228</v>
+        <v>65.97443359748173</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="97">
@@ -1785,13 +1785,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C97" t="n">
-        <v>51.47706433991497</v>
+        <v>68.74866158860192</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="98">
@@ -1799,13 +1799,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C98" t="n">
-        <v>62.72713000736199</v>
+        <v>42.17335440675882</v>
       </c>
       <c r="D98" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="99">
@@ -1813,13 +1813,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C99" t="n">
-        <v>30.1299770846383</v>
+        <v>42.18190572876888</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="100">
@@ -1827,13 +1827,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C100" t="n">
-        <v>36.75800440157938</v>
+        <v>34.69218694111808</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="101">
@@ -1841,10 +1841,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C101" t="n">
-        <v>63.89390408530792</v>
+        <v>36.29162728034863</v>
       </c>
       <c r="D101" t="n">
         <v>0.9999</v>
@@ -1855,13 +1855,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C102" t="n">
-        <v>26.79910170703495</v>
+        <v>43.1513273251922</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="103">
@@ -1872,10 +1872,10 @@
         <v>96</v>
       </c>
       <c r="C103" t="n">
-        <v>60.78466344124584</v>
+        <v>40.64291871363418</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="104">
@@ -1883,13 +1883,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C104" t="n">
-        <v>50.48567520359704</v>
+        <v>45.65190689831397</v>
       </c>
       <c r="D104" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="105">
@@ -1897,10 +1897,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C105" t="n">
-        <v>41.35935978814719</v>
+        <v>26.2204855373995</v>
       </c>
       <c r="D105" t="n">
         <v>0.9999</v>
@@ -1911,13 +1911,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="C106" t="n">
-        <v>42.82388935866014</v>
+        <v>65.4605336408811</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="107">
@@ -1925,13 +1925,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C107" t="n">
-        <v>68.23917794835043</v>
+        <v>62.73201022381812</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="108">
@@ -1939,13 +1939,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C108" t="n">
-        <v>59.83732978424243</v>
+        <v>40.61413014980727</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="109">
@@ -1953,13 +1953,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C109" t="n">
-        <v>74.63434472715409</v>
+        <v>62.38184838870696</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="110">
@@ -1967,13 +1967,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C110" t="n">
-        <v>43.8272972250524</v>
+        <v>59.64386803394874</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="111">
@@ -1981,10 +1981,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C111" t="n">
-        <v>38.43265364638556</v>
+        <v>14.31265609144895</v>
       </c>
       <c r="D111" t="n">
         <v>0.9999</v>
@@ -1995,13 +1995,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C112" t="n">
-        <v>43.35818692272822</v>
+        <v>49.91705406780921</v>
       </c>
       <c r="D112" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="113">
@@ -2009,13 +2009,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C113" t="n">
-        <v>38.24494164978585</v>
+        <v>79.37351626423612</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="114">
@@ -2023,13 +2023,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C114" t="n">
-        <v>63.72798095751364</v>
+        <v>27.78397739774384</v>
       </c>
       <c r="D114" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="115">
@@ -2037,13 +2037,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="C115" t="n">
-        <v>67.53649305633806</v>
+        <v>63.6363302880431</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="116">
@@ -2051,10 +2051,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C116" t="n">
-        <v>32.72351644182054</v>
+        <v>37.3930925434204</v>
       </c>
       <c r="D116" t="n">
         <v>0.9999</v>
@@ -2065,13 +2065,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C117" t="n">
-        <v>61.59257328408566</v>
+        <v>54.10039897589113</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="118">
@@ -2079,13 +2079,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C118" t="n">
-        <v>25.38818198523678</v>
+        <v>30.10655975250545</v>
       </c>
       <c r="D118" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="119">
@@ -2093,13 +2093,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="C119" t="n">
-        <v>45.79677033582375</v>
+        <v>64.39924007269208</v>
       </c>
       <c r="D119" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="120">
@@ -2107,13 +2107,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C120" t="n">
-        <v>37.48719016337304</v>
+        <v>44.41628893625074</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="121">
@@ -2121,13 +2121,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C121" t="n">
-        <v>32.63044854100505</v>
+        <v>59.96259882293684</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="122">
@@ -2135,13 +2135,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="C122" t="n">
-        <v>68.28707584039341</v>
+        <v>46.68302520356953</v>
       </c>
       <c r="D122" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="123">
@@ -2149,10 +2149,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="C123" t="n">
-        <v>33.24305624591818</v>
+        <v>26.51952984438027</v>
       </c>
       <c r="D123" t="n">
         <v>0.99</v>
@@ -2163,13 +2163,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C124" t="n">
-        <v>44.03556352239427</v>
+        <v>49.32445235263918</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="125">
@@ -2177,13 +2177,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C125" t="n">
-        <v>42.74363943603997</v>
+        <v>15.92774242902541</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="126">
@@ -2191,10 +2191,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C126" t="n">
-        <v>58.85095317494391</v>
+        <v>13.2270805066047</v>
       </c>
       <c r="D126" t="n">
         <v>0.999</v>
@@ -2205,13 +2205,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C127" t="n">
-        <v>16.17394847958799</v>
+        <v>60.11483374208393</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="128">
@@ -2219,13 +2219,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C128" t="n">
-        <v>33.87766682607845</v>
+        <v>48.54053096152536</v>
       </c>
       <c r="D128" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="129">
@@ -2233,13 +2233,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C129" t="n">
-        <v>47.00209216877489</v>
+        <v>2.011627525516055</v>
       </c>
       <c r="D129" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="130">
@@ -2247,13 +2247,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C130" t="n">
-        <v>21.82843164035993</v>
+        <v>47.11021123893239</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="131">
@@ -2261,13 +2261,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C131" t="n">
-        <v>60.99389115413728</v>
+        <v>91.06470402272723</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="132">
@@ -2275,13 +2275,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C132" t="n">
-        <v>56.44673584598896</v>
+        <v>65.70428272317591</v>
       </c>
       <c r="D132" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="133">
@@ -2289,13 +2289,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C133" t="n">
-        <v>69.7668412155984</v>
+        <v>54.5520071595922</v>
       </c>
       <c r="D133" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="134">
@@ -2303,10 +2303,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C134" t="n">
-        <v>61.90100495581607</v>
+        <v>54.19311924052327</v>
       </c>
       <c r="D134" t="n">
         <v>0.99</v>
@@ -2317,13 +2317,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C135" t="n">
-        <v>67.47581972462075</v>
+        <v>72.69645125244699</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="136">
@@ -2331,13 +2331,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="C136" t="n">
-        <v>56.0214981912111</v>
+        <v>49.33991879549746</v>
       </c>
       <c r="D136" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="137">
@@ -2345,13 +2345,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="C137" t="n">
-        <v>50.95247214583335</v>
+        <v>30.55991914285645</v>
       </c>
       <c r="D137" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="138">
@@ -2359,13 +2359,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="C138" t="n">
-        <v>53.57551639207747</v>
+        <v>95.4931311234933</v>
       </c>
       <c r="D138" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="139">
@@ -2373,13 +2373,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C139" t="n">
-        <v>50.14878729140165</v>
+        <v>43.93200372400587</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="140">
@@ -2387,13 +2387,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C140" t="n">
-        <v>39.11919311989337</v>
+        <v>59.42070020715195</v>
       </c>
       <c r="D140" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="141">
@@ -2401,13 +2401,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C141" t="n">
-        <v>57.67393992818478</v>
+        <v>42.78065194952644</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="142">
@@ -2415,10 +2415,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C142" t="n">
-        <v>59.98976470976152</v>
+        <v>78.5292938320666</v>
       </c>
       <c r="D142" t="n">
         <v>0.99</v>
@@ -2429,13 +2429,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="C143" t="n">
-        <v>61.29403023760543</v>
+        <v>83.35988352385664</v>
       </c>
       <c r="D143" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="144">
@@ -2443,10 +2443,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C144" t="n">
-        <v>41.06339365608342</v>
+        <v>53.13104311335147</v>
       </c>
       <c r="D144" t="n">
         <v>0.999</v>
@@ -2457,13 +2457,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C145" t="n">
-        <v>71.71488219151669</v>
+        <v>52.45409424763066</v>
       </c>
       <c r="D145" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="146">
@@ -2471,13 +2471,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C146" t="n">
-        <v>33.21788065693907</v>
+        <v>67.6065141898811</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="147">
@@ -2485,13 +2485,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C147" t="n">
-        <v>35.76532379625473</v>
+        <v>71.45259353970499</v>
       </c>
       <c r="D147" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="148">
@@ -2499,13 +2499,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C148" t="n">
-        <v>50.30715431918719</v>
+        <v>58.34130372695707</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="149">
@@ -2513,10 +2513,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C149" t="n">
-        <v>41.70098183161208</v>
+        <v>54.963017222701</v>
       </c>
       <c r="D149" t="n">
         <v>0.999</v>
@@ -2527,13 +2527,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C150" t="n">
-        <v>25.71370826456232</v>
+        <v>58.59593444859313</v>
       </c>
       <c r="D150" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="151">
@@ -2541,13 +2541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C151" t="n">
-        <v>26.49052869939182</v>
+        <v>56.28940686501164</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="152">
@@ -2555,13 +2555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C152" t="n">
-        <v>63.90692432390129</v>
+        <v>40.40835052706638</v>
       </c>
       <c r="D152" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="153">
@@ -2569,10 +2569,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C153" t="n">
-        <v>63.37928648737845</v>
+        <v>38.73957899158366</v>
       </c>
       <c r="D153" t="n">
         <v>0.99</v>
@@ -2583,10 +2583,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C154" t="n">
-        <v>25.12029222292051</v>
+        <v>65.5221313656147</v>
       </c>
       <c r="D154" t="n">
         <v>0.999</v>
@@ -2597,13 +2597,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="C155" t="n">
-        <v>39.60329258760133</v>
+        <v>71.21257686030701</v>
       </c>
       <c r="D155" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="156">
@@ -2611,13 +2611,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C156" t="n">
-        <v>12.21263075110782</v>
+        <v>14.84769653520368</v>
       </c>
       <c r="D156" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="157">
@@ -2625,13 +2625,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C157" t="n">
-        <v>30.54834043508056</v>
+        <v>2.426151123820361</v>
       </c>
       <c r="D157" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="158">
@@ -2639,13 +2639,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C158" t="n">
-        <v>50.03149339688316</v>
+        <v>54.84775619720966</v>
       </c>
       <c r="D158" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="159">
@@ -2653,10 +2653,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C159" t="n">
-        <v>47.94394853399143</v>
+        <v>52.75681525556561</v>
       </c>
       <c r="D159" t="n">
         <v>0.9999</v>
@@ -2667,13 +2667,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C160" t="n">
-        <v>69.92956674357832</v>
+        <v>81.99540332484963</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="161">
@@ -2681,10 +2681,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C161" t="n">
-        <v>31.9704602093228</v>
+        <v>56.3176443019234</v>
       </c>
       <c r="D161" t="n">
         <v>0.9</v>
@@ -2695,13 +2695,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C162" t="n">
-        <v>38.96577069630239</v>
+        <v>41.08559990096147</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="163">
@@ -2709,13 +2709,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C163" t="n">
-        <v>39.39751136993004</v>
+        <v>77.80084206769882</v>
       </c>
       <c r="D163" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="164">
@@ -2723,13 +2723,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C164" t="n">
-        <v>70.84264618277928</v>
+        <v>53.68435860118443</v>
       </c>
       <c r="D164" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="165">
@@ -2737,13 +2737,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="C165" t="n">
-        <v>33.99966038162763</v>
+        <v>15.12021359519616</v>
       </c>
       <c r="D165" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="166">
@@ -2751,13 +2751,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C166" t="n">
-        <v>56.52139609313584</v>
+        <v>27.04346968202729</v>
       </c>
       <c r="D166" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="167">
@@ -2765,13 +2765,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="C167" t="n">
-        <v>51.63354419283532</v>
+        <v>49.98233765831699</v>
       </c>
       <c r="D167" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="168">
@@ -2779,13 +2779,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="C168" t="n">
-        <v>47.10708506835977</v>
+        <v>51.94614386963547</v>
       </c>
       <c r="D168" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="169">
@@ -2793,13 +2793,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C169" t="n">
-        <v>55.25408342657246</v>
+        <v>29.65076532844162</v>
       </c>
       <c r="D169" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="170">
@@ -2807,13 +2807,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C170" t="n">
-        <v>60.65846113009473</v>
+        <v>58.43377007293878</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="171">
@@ -2821,13 +2821,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C171" t="n">
-        <v>89.11758782502773</v>
+        <v>56.26027535154225</v>
       </c>
       <c r="D171" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="172">
@@ -2835,13 +2835,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C172" t="n">
-        <v>34.15141111167516</v>
+        <v>55.86817072728986</v>
       </c>
       <c r="D172" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="173">
@@ -2849,13 +2849,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C173" t="n">
-        <v>81.70343159249632</v>
+        <v>50.15416751772711</v>
       </c>
       <c r="D173" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="174">
@@ -2863,13 +2863,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C174" t="n">
-        <v>66.67672188427332</v>
+        <v>53.85536539720606</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="175">
@@ -2877,13 +2877,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="C175" t="n">
-        <v>55.87154050616485</v>
+        <v>13.87947006146145</v>
       </c>
       <c r="D175" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="176">
@@ -2891,13 +2891,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C176" t="n">
-        <v>38.00322570895611</v>
+        <v>38.80360715695589</v>
       </c>
       <c r="D176" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="177">
@@ -2905,13 +2905,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C177" t="n">
-        <v>29.69824828000953</v>
+        <v>32.85769207487141</v>
       </c>
       <c r="D177" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="178">
@@ -2919,13 +2919,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C178" t="n">
-        <v>51.10642431092796</v>
+        <v>68.69238990992848</v>
       </c>
       <c r="D178" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="179">
@@ -2933,10 +2933,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="C179" t="n">
-        <v>58.24256654083357</v>
+        <v>57.41359397471884</v>
       </c>
       <c r="D179" t="n">
         <v>0.9</v>
@@ -2947,13 +2947,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C180" t="n">
-        <v>57.90753875284465</v>
+        <v>42.05664144139013</v>
       </c>
       <c r="D180" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="181">
@@ -2961,13 +2961,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C181" t="n">
-        <v>37.82288482564915</v>
+        <v>47.48888036388623</v>
       </c>
       <c r="D181" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="182">
@@ -2975,13 +2975,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C182" t="n">
-        <v>59.72710216882905</v>
+        <v>50.53832754832667</v>
       </c>
       <c r="D182" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="183">
@@ -2989,13 +2989,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C183" t="n">
-        <v>30.0882005832016</v>
+        <v>77.90666351085936</v>
       </c>
       <c r="D183" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="184">
@@ -3003,10 +3003,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C184" t="n">
-        <v>50.0340207885088</v>
+        <v>37.79834545505176</v>
       </c>
       <c r="D184" t="n">
         <v>0.999</v>
@@ -3017,13 +3017,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="C185" t="n">
-        <v>22.99356530034146</v>
+        <v>56.67285777064668</v>
       </c>
       <c r="D185" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="186">
@@ -3031,13 +3031,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C186" t="n">
-        <v>70.53643160720347</v>
+        <v>69.81360629876897</v>
       </c>
       <c r="D186" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="187">
@@ -3045,10 +3045,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C187" t="n">
-        <v>69.30669020013021</v>
+        <v>39.43993100126566</v>
       </c>
       <c r="D187" t="n">
         <v>0.9</v>
@@ -3059,13 +3059,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C188" t="n">
-        <v>53.28708600267237</v>
+        <v>61.21967923811923</v>
       </c>
       <c r="D188" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="189">
@@ -3073,13 +3073,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="C189" t="n">
-        <v>58.33525434379268</v>
+        <v>68.53883169208245</v>
       </c>
       <c r="D189" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="190">
@@ -3087,13 +3087,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C190" t="n">
-        <v>52.21783588359124</v>
+        <v>40.32840479835944</v>
       </c>
       <c r="D190" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="191">
@@ -3101,13 +3101,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="C191" t="n">
-        <v>73.04385275833977</v>
+        <v>59.12156385866909</v>
       </c>
       <c r="D191" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="192">
@@ -3115,10 +3115,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="C192" t="n">
-        <v>47.88198415669979</v>
+        <v>55.51061408324165</v>
       </c>
       <c r="D192" t="n">
         <v>0.9999</v>
@@ -3129,13 +3129,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C193" t="n">
-        <v>31.82557362505747</v>
+        <v>66.76227468936096</v>
       </c>
       <c r="D193" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="194">
@@ -3143,13 +3143,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C194" t="n">
-        <v>7.703496491937528</v>
+        <v>31.66950133959016</v>
       </c>
       <c r="D194" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="195">
@@ -3157,10 +3157,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C195" t="n">
-        <v>57.38510043723399</v>
+        <v>28.07121381962947</v>
       </c>
       <c r="D195" t="n">
         <v>0.9</v>
@@ -3171,13 +3171,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C196" t="n">
-        <v>21.07210778365031</v>
+        <v>54.19284683139474</v>
       </c>
       <c r="D196" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="197">
@@ -3185,13 +3185,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C197" t="n">
-        <v>50.77438967751996</v>
+        <v>49.12951657643197</v>
       </c>
       <c r="D197" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="198">
@@ -3199,13 +3199,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C198" t="n">
-        <v>59.94433851813749</v>
+        <v>33.64699996459905</v>
       </c>
       <c r="D198" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="199">
@@ -3213,13 +3213,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C199" t="n">
-        <v>18.08351560802339</v>
+        <v>37.21796035512192</v>
       </c>
       <c r="D199" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="200">
@@ -3227,13 +3227,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C200" t="n">
-        <v>48.88290551241017</v>
+        <v>44.20300942513269</v>
       </c>
       <c r="D200" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="201">
@@ -3241,13 +3241,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C201" t="n">
-        <v>60.19400006076078</v>
+        <v>62.21468626487874</v>
       </c>
       <c r="D201" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>6.611899903840291</v>
       </c>
       <c r="C2" t="n">
-        <v>41.18660072296451</v>
+        <v>1989703090.150963</v>
       </c>
       <c r="D2" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>9.458478886863501</v>
       </c>
       <c r="C3" t="n">
-        <v>52.49893749629924</v>
+        <v>2519293403.746736</v>
       </c>
       <c r="D3" t="n">
         <v>0.99</v>
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>9.081351957255169</v>
       </c>
       <c r="C4" t="n">
-        <v>38.4524359711053</v>
+        <v>2495048170.173721</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>8.311887795807797</v>
       </c>
       <c r="C5" t="n">
-        <v>37.46952456002418</v>
+        <v>2027065848.631681</v>
       </c>
       <c r="D5" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>9.370486220610481</v>
       </c>
       <c r="C6" t="n">
-        <v>35.89237509210422</v>
+        <v>1724350331.970877</v>
       </c>
       <c r="D6" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="7">
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>44</v>
+        <v>9.210885635292149</v>
       </c>
       <c r="C7" t="n">
-        <v>56.80470161257504</v>
+        <v>2733432476.42175</v>
       </c>
       <c r="D7" t="n">
         <v>0.9</v>
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>8.829022398812615</v>
       </c>
       <c r="C8" t="n">
-        <v>35.17874630885516</v>
+        <v>1124298297.232195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>7.778460822747784</v>
       </c>
       <c r="C9" t="n">
-        <v>34.58005024902967</v>
+        <v>1679085563.708544</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>6.283012897856454</v>
       </c>
       <c r="C10" t="n">
-        <v>31.09847929715623</v>
+        <v>1385671456.720657</v>
       </c>
       <c r="D10" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>5.917285407462558</v>
       </c>
       <c r="C11" t="n">
-        <v>47.29836019196955</v>
+        <v>2517764213.866761</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>9.760958695470894</v>
       </c>
       <c r="C12" t="n">
-        <v>61.67268359677115</v>
+        <v>1225712002.921154</v>
       </c>
       <c r="D12" t="n">
         <v>0.9999</v>
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>88</v>
+        <v>9.282624142385234</v>
       </c>
       <c r="C13" t="n">
-        <v>74.97898034473121</v>
+        <v>1140782074.98124</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>61</v>
+        <v>5.534341600131182</v>
       </c>
       <c r="C14" t="n">
-        <v>53.39769823120358</v>
+        <v>641432232.1030121</v>
       </c>
       <c r="D14" t="n">
         <v>0.99</v>
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>5.428265989060518</v>
       </c>
       <c r="C15" t="n">
-        <v>31.52700383387826</v>
+        <v>1010361887.491319</v>
       </c>
       <c r="D15" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>9.744043570503546</v>
       </c>
       <c r="C16" t="n">
-        <v>37.42323827165436</v>
+        <v>2066500326.307691</v>
       </c>
       <c r="D16" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>65</v>
+        <v>6.474718115843953</v>
       </c>
       <c r="C17" t="n">
-        <v>43.03833860806844</v>
+        <v>544667959.2396631</v>
       </c>
       <c r="D17" t="n">
         <v>0.999</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>6.054254594439056</v>
       </c>
       <c r="C18" t="n">
-        <v>36.13914194349104</v>
+        <v>2609504857.154016</v>
       </c>
       <c r="D18" t="n">
         <v>0.9999</v>
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>6.209703476792037</v>
       </c>
       <c r="C19" t="n">
-        <v>69.05633539980356</v>
+        <v>2931097588.003606</v>
       </c>
       <c r="D19" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>95</v>
+        <v>7.046210259333273</v>
       </c>
       <c r="C20" t="n">
-        <v>93.70223274952224</v>
+        <v>1446018456.515302</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="21">
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>81</v>
+        <v>8.646376186779616</v>
       </c>
       <c r="C21" t="n">
-        <v>58.42561777988465</v>
+        <v>2856105569.979587</v>
       </c>
       <c r="D21" t="n">
         <v>0.9999</v>
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>63</v>
+        <v>9.254310893497342</v>
       </c>
       <c r="C22" t="n">
-        <v>82.66761935917904</v>
+        <v>1216293723.326428</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>53</v>
+        <v>6.057953128354083</v>
       </c>
       <c r="C23" t="n">
-        <v>41.70852559551759</v>
+        <v>974472748.881427</v>
       </c>
       <c r="D23" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>56</v>
+        <v>8.142084699265133</v>
       </c>
       <c r="C24" t="n">
-        <v>58.72350280538402</v>
+        <v>1093793299.983983</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>79</v>
+        <v>5.176023926144904</v>
       </c>
       <c r="C25" t="n">
-        <v>65.08432168456005</v>
+        <v>2150854906.026975</v>
       </c>
       <c r="D25" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>74</v>
+        <v>9.282602162779529</v>
       </c>
       <c r="C26" t="n">
-        <v>29.89909932766966</v>
+        <v>2736597601.161132</v>
       </c>
       <c r="D26" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>72</v>
+        <v>6.483497669505885</v>
       </c>
       <c r="C27" t="n">
-        <v>61.24886902276679</v>
+        <v>1511925619.000439</v>
       </c>
       <c r="D27" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="28">
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>62</v>
+        <v>6.907252271893272</v>
       </c>
       <c r="C28" t="n">
-        <v>7.618577231622631</v>
+        <v>1473980537.79228</v>
       </c>
       <c r="D28" t="n">
         <v>0.9999</v>
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>44</v>
+        <v>8.283160566707759</v>
       </c>
       <c r="C29" t="n">
-        <v>54.16090387643604</v>
+        <v>2854952438.464984</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>37</v>
+        <v>5.363459947892352</v>
       </c>
       <c r="C30" t="n">
-        <v>56.93875585040984</v>
+        <v>1623764217.973377</v>
       </c>
       <c r="D30" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>23</v>
+        <v>9.075964754853276</v>
       </c>
       <c r="C31" t="n">
-        <v>56.1587731842232</v>
+        <v>2811834357.769165</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="32">
@@ -875,13 +875,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>56</v>
+        <v>6.005788933465668</v>
       </c>
       <c r="C32" t="n">
-        <v>30.41183834938715</v>
+        <v>1216056547.077393</v>
       </c>
       <c r="D32" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="33">
@@ -889,13 +889,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>56</v>
+        <v>6.595330091549068</v>
       </c>
       <c r="C33" t="n">
-        <v>23.54143680572582</v>
+        <v>2594073059.29355</v>
       </c>
       <c r="D33" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="34">
@@ -903,13 +903,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>53</v>
+        <v>7.722771731304446</v>
       </c>
       <c r="C34" t="n">
-        <v>49.80369741361291</v>
+        <v>672413199.4616046</v>
       </c>
       <c r="D34" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="35">
@@ -917,10 +917,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>39</v>
+        <v>7.741879053497387</v>
       </c>
       <c r="C35" t="n">
-        <v>36.63867223316725</v>
+        <v>2178956013.297335</v>
       </c>
       <c r="D35" t="n">
         <v>0.9</v>
@@ -931,13 +931,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>43</v>
+        <v>6.032941759473034</v>
       </c>
       <c r="C36" t="n">
-        <v>58.11820636548175</v>
+        <v>1490965557.204769</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="37">
@@ -945,13 +945,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>92</v>
+        <v>8.267904618831091</v>
       </c>
       <c r="C37" t="n">
-        <v>40.22751856744325</v>
+        <v>1679792428.363853</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -959,13 +959,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>74</v>
+        <v>9.276566808385919</v>
       </c>
       <c r="C38" t="n">
-        <v>43.09314145828443</v>
+        <v>1388485954.292586</v>
       </c>
       <c r="D38" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="39">
@@ -973,10 +973,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>52</v>
+        <v>5.807469817361404</v>
       </c>
       <c r="C39" t="n">
-        <v>35.92630785767798</v>
+        <v>842802389.6758053</v>
       </c>
       <c r="D39" t="n">
         <v>0.9</v>
@@ -987,13 +987,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>72</v>
+        <v>9.705114053550254</v>
       </c>
       <c r="C40" t="n">
-        <v>71.57438942494069</v>
+        <v>1538381519.829908</v>
       </c>
       <c r="D40" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="41">
@@ -1001,13 +1001,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>29</v>
+        <v>8.339385529008545</v>
       </c>
       <c r="C41" t="n">
-        <v>60.48771917205494</v>
+        <v>1507034468.165098</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="42">
@@ -1015,13 +1015,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>29</v>
+        <v>5.77565924623604</v>
       </c>
       <c r="C42" t="n">
-        <v>68.88254121078265</v>
+        <v>1636717288.7258</v>
       </c>
       <c r="D42" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="43">
@@ -1029,10 +1029,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>49</v>
+        <v>9.836156741450633</v>
       </c>
       <c r="C43" t="n">
-        <v>30.7162765035165</v>
+        <v>2659720946.702735</v>
       </c>
       <c r="D43" t="n">
         <v>0.99</v>
@@ -1043,10 +1043,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>6.674919334499503</v>
       </c>
       <c r="C44" t="n">
-        <v>51.74544586972218</v>
+        <v>1244150194.714226</v>
       </c>
       <c r="D44" t="n">
         <v>0.999</v>
@@ -1057,13 +1057,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>75</v>
+        <v>6.636399425043879</v>
       </c>
       <c r="C45" t="n">
-        <v>60.37964170327503</v>
+        <v>787383993.1144338</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="46">
@@ -1071,13 +1071,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>19</v>
+        <v>9.853636449283801</v>
       </c>
       <c r="C46" t="n">
-        <v>48.34006272225907</v>
+        <v>1476384266.51726</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="47">
@@ -1085,13 +1085,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>73</v>
+        <v>6.443552953494433</v>
       </c>
       <c r="C47" t="n">
-        <v>54.98922155860479</v>
+        <v>2839482537.394162</v>
       </c>
       <c r="D47" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="48">
@@ -1099,13 +1099,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>77</v>
+        <v>5.652018647353982</v>
       </c>
       <c r="C48" t="n">
-        <v>57.9849148603933</v>
+        <v>1555598482.303327</v>
       </c>
       <c r="D48" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -1113,13 +1113,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>62</v>
+        <v>6.410050401739351</v>
       </c>
       <c r="C49" t="n">
-        <v>36.90852090884079</v>
+        <v>1134496101.273098</v>
       </c>
       <c r="D49" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="50">
@@ -1127,13 +1127,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>79</v>
+        <v>5.336967930380334</v>
       </c>
       <c r="C50" t="n">
-        <v>77.82169179675695</v>
+        <v>1905508391.388878</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="51">
@@ -1141,13 +1141,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>20</v>
+        <v>6.402965611531205</v>
       </c>
       <c r="C51" t="n">
-        <v>38.84398113564195</v>
+        <v>2493109137.421947</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="52">
@@ -1155,13 +1155,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>68</v>
+        <v>9.943814996760505</v>
       </c>
       <c r="C52" t="n">
-        <v>45.18055483659527</v>
+        <v>2387880827.004162</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="53">
@@ -1169,13 +1169,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>6.962714935936077</v>
       </c>
       <c r="C53" t="n">
-        <v>60.69736733515805</v>
+        <v>2443142878.268995</v>
       </c>
       <c r="D53" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="54">
@@ -1183,13 +1183,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>61</v>
+        <v>7.404981059473712</v>
       </c>
       <c r="C54" t="n">
-        <v>44.93599810598114</v>
+        <v>2844089606.746162</v>
       </c>
       <c r="D54" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="55">
@@ -1197,13 +1197,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>85</v>
+        <v>5.122282779079272</v>
       </c>
       <c r="C55" t="n">
-        <v>58.09709982370419</v>
+        <v>2752767697.911618</v>
       </c>
       <c r="D55" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="56">
@@ -1211,13 +1211,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>20</v>
+        <v>7.822890048726163</v>
       </c>
       <c r="C56" t="n">
-        <v>35.92094115466597</v>
+        <v>1176950926.933015</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="57">
@@ -1225,13 +1225,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>26</v>
+        <v>8.213067663008902</v>
       </c>
       <c r="C57" t="n">
-        <v>38.07572159742486</v>
+        <v>2506097954.530643</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="58">
@@ -1239,13 +1239,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>84</v>
+        <v>6.65549153068613</v>
       </c>
       <c r="C58" t="n">
-        <v>74.36347994907064</v>
+        <v>1046226967.291394</v>
       </c>
       <c r="D58" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="59">
@@ -1253,13 +1253,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>41</v>
+        <v>8.420189493125106</v>
       </c>
       <c r="C59" t="n">
-        <v>49.9565575271561</v>
+        <v>1725419534.78552</v>
       </c>
       <c r="D59" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="60">
@@ -1267,10 +1267,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>10</v>
+        <v>8.482903378387856</v>
       </c>
       <c r="C60" t="n">
-        <v>32.0112827209538</v>
+        <v>1564464179.855836</v>
       </c>
       <c r="D60" t="n">
         <v>0.9</v>
@@ -1281,13 +1281,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>32</v>
+        <v>7.81546108102293</v>
       </c>
       <c r="C61" t="n">
-        <v>54.89734505811601</v>
+        <v>2288915087.236743</v>
       </c>
       <c r="D61" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="62">
@@ -1295,13 +1295,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>62</v>
+        <v>7.319842628973613</v>
       </c>
       <c r="C62" t="n">
-        <v>64.51122042621715</v>
+        <v>691316745.6107179</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="63">
@@ -1309,13 +1309,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>98</v>
+        <v>9.871101650439041</v>
       </c>
       <c r="C63" t="n">
-        <v>54.49276986088906</v>
+        <v>515218065.4456663</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="64">
@@ -1323,13 +1323,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>87</v>
+        <v>8.907704320302022</v>
       </c>
       <c r="C64" t="n">
-        <v>43.54518328195375</v>
+        <v>1912728047.381083</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="65">
@@ -1337,10 +1337,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>97</v>
+        <v>9.791049691331832</v>
       </c>
       <c r="C65" t="n">
-        <v>26.46595227451997</v>
+        <v>2859780964.541248</v>
       </c>
       <c r="D65" t="n">
         <v>0.9999</v>
@@ -1351,10 +1351,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>99</v>
+        <v>6.390872229820053</v>
       </c>
       <c r="C66" t="n">
-        <v>49.73613305814442</v>
+        <v>2808729207.48243</v>
       </c>
       <c r="D66" t="n">
         <v>0.9999</v>
@@ -1365,10 +1365,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>73</v>
+        <v>7.60070377899244</v>
       </c>
       <c r="C67" t="n">
-        <v>58.56362920852447</v>
+        <v>1078122543.680075</v>
       </c>
       <c r="D67" t="n">
         <v>0.9999</v>
@@ -1379,13 +1379,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>86</v>
+        <v>8.409976737432554</v>
       </c>
       <c r="C68" t="n">
-        <v>67.2347419802137</v>
+        <v>2169214525.487341</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="69">
@@ -1393,13 +1393,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>98</v>
+        <v>8.505109991736525</v>
       </c>
       <c r="C69" t="n">
-        <v>11.97211002813287</v>
+        <v>808296924.757902</v>
       </c>
       <c r="D69" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="70">
@@ -1407,10 +1407,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>22</v>
+        <v>8.814246889824869</v>
       </c>
       <c r="C70" t="n">
-        <v>69.88321307864339</v>
+        <v>2780643953.025884</v>
       </c>
       <c r="D70" t="n">
         <v>0.99</v>
@@ -1421,10 +1421,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>80</v>
+        <v>8.865287002252314</v>
       </c>
       <c r="C71" t="n">
-        <v>65.52480961623445</v>
+        <v>1636845603.919624</v>
       </c>
       <c r="D71" t="n">
         <v>0.99</v>
@@ -1435,13 +1435,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>50</v>
+        <v>5.495906001553889</v>
       </c>
       <c r="C72" t="n">
-        <v>94.10776738862424</v>
+        <v>802274440.5400271</v>
       </c>
       <c r="D72" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="73">
@@ -1449,13 +1449,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>40</v>
+        <v>6.807673276432142</v>
       </c>
       <c r="C73" t="n">
-        <v>34.3146829850063</v>
+        <v>1672940504.981586</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="74">
@@ -1463,13 +1463,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>39</v>
+        <v>8.220531817182053</v>
       </c>
       <c r="C74" t="n">
-        <v>43.66557986655914</v>
+        <v>2233397030.223283</v>
       </c>
       <c r="D74" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="75">
@@ -1477,13 +1477,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>98</v>
+        <v>5.834103481676578</v>
       </c>
       <c r="C75" t="n">
-        <v>23.22991551603931</v>
+        <v>770581626.5889349</v>
       </c>
       <c r="D75" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="76">
@@ -1491,13 +1491,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>55</v>
+        <v>7.465050077051474</v>
       </c>
       <c r="C76" t="n">
-        <v>51.54008678567424</v>
+        <v>1956517398.691969</v>
       </c>
       <c r="D76" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="77">
@@ -1505,13 +1505,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>20</v>
+        <v>6.041796645817093</v>
       </c>
       <c r="C77" t="n">
-        <v>48.86374401612555</v>
+        <v>2378825145.114942</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="78">
@@ -1519,13 +1519,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>98</v>
+        <v>6.301179454558705</v>
       </c>
       <c r="C78" t="n">
-        <v>42.39688034884901</v>
+        <v>1864050629.888839</v>
       </c>
       <c r="D78" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="79">
@@ -1533,13 +1533,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>77</v>
+        <v>6.714346298716169</v>
       </c>
       <c r="C79" t="n">
-        <v>53.27300922066683</v>
+        <v>780218226.9073039</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="80">
@@ -1547,13 +1547,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>82</v>
+        <v>8.072007492228828</v>
       </c>
       <c r="C80" t="n">
-        <v>67.89788227108647</v>
+        <v>2601485923.728729</v>
       </c>
       <c r="D80" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="81">
@@ -1561,13 +1561,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>48</v>
+        <v>5.183506474676499</v>
       </c>
       <c r="C81" t="n">
-        <v>37.56300422461504</v>
+        <v>2754928479.261498</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="82">
@@ -1575,13 +1575,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>90</v>
+        <v>6.91695401837892</v>
       </c>
       <c r="C82" t="n">
-        <v>35.01610453939815</v>
+        <v>629753935.7811328</v>
       </c>
       <c r="D82" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="83">
@@ -1589,13 +1589,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>30</v>
+        <v>5.046475802160269</v>
       </c>
       <c r="C83" t="n">
-        <v>72.88885847789385</v>
+        <v>2081292138.473792</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="84">
@@ -1603,13 +1603,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>70</v>
+        <v>7.404340845148446</v>
       </c>
       <c r="C84" t="n">
-        <v>78.19701091701387</v>
+        <v>859972185.9170504</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="85">
@@ -1617,13 +1617,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>31</v>
+        <v>8.693900116959423</v>
       </c>
       <c r="C85" t="n">
-        <v>47.94075382571584</v>
+        <v>1998979332.206363</v>
       </c>
       <c r="D85" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="86">
@@ -1631,10 +1631,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>52</v>
+        <v>6.516335699756119</v>
       </c>
       <c r="C86" t="n">
-        <v>41.73936825484108</v>
+        <v>729742017.3354971</v>
       </c>
       <c r="D86" t="n">
         <v>0.999</v>
@@ -1645,13 +1645,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>22</v>
+        <v>5.857738810924522</v>
       </c>
       <c r="C87" t="n">
-        <v>45.23541136621797</v>
+        <v>2929336639.801004</v>
       </c>
       <c r="D87" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="88">
@@ -1659,13 +1659,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>14</v>
+        <v>7.176567696545254</v>
       </c>
       <c r="C88" t="n">
-        <v>27.01222092464516</v>
+        <v>2210388596.787389</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="89">
@@ -1673,10 +1673,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>19</v>
+        <v>9.25484515495836</v>
       </c>
       <c r="C89" t="n">
-        <v>50.42855760179366</v>
+        <v>2869249564.120878</v>
       </c>
       <c r="D89" t="n">
         <v>0.99</v>
@@ -1687,13 +1687,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>20</v>
+        <v>5.402508771295981</v>
       </c>
       <c r="C90" t="n">
-        <v>50.70537992598002</v>
+        <v>1799077059.684667</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="91">
@@ -1701,13 +1701,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>30</v>
+        <v>6.589028662499068</v>
       </c>
       <c r="C91" t="n">
-        <v>24.95083805225507</v>
+        <v>1821891479.093677</v>
       </c>
       <c r="D91" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="92">
@@ -1715,13 +1715,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>37</v>
+        <v>7.154427565768393</v>
       </c>
       <c r="C92" t="n">
-        <v>15.26379097441664</v>
+        <v>2638787734.712307</v>
       </c>
       <c r="D92" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="93">
@@ -1729,13 +1729,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>10</v>
+        <v>6.879968859769034</v>
       </c>
       <c r="C93" t="n">
-        <v>61.26663730927602</v>
+        <v>1402432230.702607</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="94">
@@ -1743,13 +1743,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>55</v>
+        <v>5.833685351680612</v>
       </c>
       <c r="C94" t="n">
-        <v>48.35952024052171</v>
+        <v>2714268175.336475</v>
       </c>
       <c r="D94" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="95">
@@ -1757,10 +1757,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>25</v>
+        <v>9.715217899482422</v>
       </c>
       <c r="C95" t="n">
-        <v>69.89267692845807</v>
+        <v>1274477925.597403</v>
       </c>
       <c r="D95" t="n">
         <v>0.9</v>
@@ -1771,13 +1771,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>33</v>
+        <v>7.597313861215067</v>
       </c>
       <c r="C96" t="n">
-        <v>65.97443359748173</v>
+        <v>2080794532.914496</v>
       </c>
       <c r="D96" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="97">
@@ -1785,10 +1785,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>43</v>
+        <v>6.870364089749534</v>
       </c>
       <c r="C97" t="n">
-        <v>68.74866158860192</v>
+        <v>1247064529.464164</v>
       </c>
       <c r="D97" t="n">
         <v>0.999</v>
@@ -1799,13 +1799,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>72</v>
+        <v>6.291534580229565</v>
       </c>
       <c r="C98" t="n">
-        <v>42.17335440675882</v>
+        <v>1704818844.10517</v>
       </c>
       <c r="D98" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="99">
@@ -1813,13 +1813,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>44</v>
+        <v>6.365240642929789</v>
       </c>
       <c r="C99" t="n">
-        <v>42.18190572876888</v>
+        <v>2142362719.296712</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="100">
@@ -1827,13 +1827,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>18</v>
+        <v>8.734971368674017</v>
       </c>
       <c r="C100" t="n">
-        <v>34.69218694111808</v>
+        <v>1646337667.957947</v>
       </c>
       <c r="D100" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="101">
@@ -1841,13 +1841,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>32</v>
+        <v>9.713175634368366</v>
       </c>
       <c r="C101" t="n">
-        <v>36.29162728034863</v>
+        <v>2119567688.880301</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="102">
@@ -1855,10 +1855,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>20</v>
+        <v>9.15896561591472</v>
       </c>
       <c r="C102" t="n">
-        <v>43.1513273251922</v>
+        <v>1775310352.899411</v>
       </c>
       <c r="D102" t="n">
         <v>0.99</v>
@@ -1869,10 +1869,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>96</v>
+        <v>6.789546794849374</v>
       </c>
       <c r="C103" t="n">
-        <v>40.64291871363418</v>
+        <v>1109597168.584832</v>
       </c>
       <c r="D103" t="n">
         <v>0.9999</v>
@@ -1883,13 +1883,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>47</v>
+        <v>8.311965561475215</v>
       </c>
       <c r="C104" t="n">
-        <v>45.65190689831397</v>
+        <v>2043061636.516008</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="105">
@@ -1897,13 +1897,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>50</v>
+        <v>9.241315784513915</v>
       </c>
       <c r="C105" t="n">
-        <v>26.2204855373995</v>
+        <v>562394158.5221497</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="106">
@@ -1911,13 +1911,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>18</v>
+        <v>6.979073162972787</v>
       </c>
       <c r="C106" t="n">
-        <v>65.4605336408811</v>
+        <v>1551866889.283085</v>
       </c>
       <c r="D106" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="107">
@@ -1925,13 +1925,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>71</v>
+        <v>5.589794987767421</v>
       </c>
       <c r="C107" t="n">
-        <v>62.73201022381812</v>
+        <v>901494901.5442753</v>
       </c>
       <c r="D107" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="108">
@@ -1939,10 +1939,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>66</v>
+        <v>7.48698853242043</v>
       </c>
       <c r="C108" t="n">
-        <v>40.61413014980727</v>
+        <v>876051798.4349151</v>
       </c>
       <c r="D108" t="n">
         <v>0.9999</v>
@@ -1953,13 +1953,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>25</v>
+        <v>7.249433425142258</v>
       </c>
       <c r="C109" t="n">
-        <v>62.38184838870696</v>
+        <v>1839484086.912312</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="110">
@@ -1967,10 +1967,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>65</v>
+        <v>9.037488532289153</v>
       </c>
       <c r="C110" t="n">
-        <v>59.64386803394874</v>
+        <v>2321968984.01813</v>
       </c>
       <c r="D110" t="n">
         <v>0.99</v>
@@ -1981,10 +1981,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>90</v>
+        <v>9.847461786940883</v>
       </c>
       <c r="C111" t="n">
-        <v>14.31265609144895</v>
+        <v>2160251269.166466</v>
       </c>
       <c r="D111" t="n">
         <v>0.9999</v>
@@ -1995,13 +1995,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>97</v>
+        <v>6.341987841961975</v>
       </c>
       <c r="C112" t="n">
-        <v>49.91705406780921</v>
+        <v>1129480267.558282</v>
       </c>
       <c r="D112" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="113">
@@ -2009,13 +2009,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>64</v>
+        <v>6.353538425519317</v>
       </c>
       <c r="C113" t="n">
-        <v>79.37351626423612</v>
+        <v>1757975477.342786</v>
       </c>
       <c r="D113" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="114">
@@ -2023,13 +2023,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>46</v>
+        <v>8.674098915596558</v>
       </c>
       <c r="C114" t="n">
-        <v>27.78397739774384</v>
+        <v>1193904405.508304</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="115">
@@ -2037,13 +2037,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>11</v>
+        <v>8.11601168397852</v>
       </c>
       <c r="C115" t="n">
-        <v>63.6363302880431</v>
+        <v>1279163638.819794</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="116">
@@ -2051,10 +2051,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>88</v>
+        <v>5.690753105669546</v>
       </c>
       <c r="C116" t="n">
-        <v>37.3930925434204</v>
+        <v>1162754147.959435</v>
       </c>
       <c r="D116" t="n">
         <v>0.9999</v>
@@ -2065,10 +2065,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>68</v>
+        <v>7.113712966206531</v>
       </c>
       <c r="C117" t="n">
-        <v>54.10039897589113</v>
+        <v>2761662664.442652</v>
       </c>
       <c r="D117" t="n">
         <v>0.99</v>
@@ -2079,13 +2079,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>52</v>
+        <v>9.383260788900309</v>
       </c>
       <c r="C118" t="n">
-        <v>30.10655975250545</v>
+        <v>2406303792.990534</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="119">
@@ -2093,13 +2093,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>36</v>
+        <v>6.414745755801159</v>
       </c>
       <c r="C119" t="n">
-        <v>64.39924007269208</v>
+        <v>609544070.5114353</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="120">
@@ -2107,13 +2107,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>20</v>
+        <v>7.456974832651706</v>
       </c>
       <c r="C120" t="n">
-        <v>44.41628893625074</v>
+        <v>2127555515.604955</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="121">
@@ -2121,13 +2121,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>75</v>
+        <v>7.39733827874154</v>
       </c>
       <c r="C121" t="n">
-        <v>59.96259882293684</v>
+        <v>849787732.7973753</v>
       </c>
       <c r="D121" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="122">
@@ -2135,13 +2135,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>87</v>
+        <v>9.239971161686251</v>
       </c>
       <c r="C122" t="n">
-        <v>46.68302520356953</v>
+        <v>1152491338.318102</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="123">
@@ -2149,10 +2149,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>96</v>
+        <v>5.760777808737239</v>
       </c>
       <c r="C123" t="n">
-        <v>26.51952984438027</v>
+        <v>1981587795.066815</v>
       </c>
       <c r="D123" t="n">
         <v>0.99</v>
@@ -2163,13 +2163,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>34</v>
+        <v>5.065228863521137</v>
       </c>
       <c r="C124" t="n">
-        <v>49.32445235263918</v>
+        <v>1256817101.656187</v>
       </c>
       <c r="D124" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="125">
@@ -2177,13 +2177,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>81</v>
+        <v>9.525031542747652</v>
       </c>
       <c r="C125" t="n">
-        <v>15.92774242902541</v>
+        <v>786618083.2632445</v>
       </c>
       <c r="D125" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="126">
@@ -2191,13 +2191,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>48</v>
+        <v>5.621719538665848</v>
       </c>
       <c r="C126" t="n">
-        <v>13.2270805066047</v>
+        <v>2043752248.302609</v>
       </c>
       <c r="D126" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="127">
@@ -2205,13 +2205,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>55</v>
+        <v>8.858874399899515</v>
       </c>
       <c r="C127" t="n">
-        <v>60.11483374208393</v>
+        <v>1613479063.569354</v>
       </c>
       <c r="D127" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="128">
@@ -2219,13 +2219,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>32</v>
+        <v>5.497343131601155</v>
       </c>
       <c r="C128" t="n">
-        <v>48.54053096152536</v>
+        <v>1235367413.273307</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="129">
@@ -2233,13 +2233,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>79</v>
+        <v>9.625276021660749</v>
       </c>
       <c r="C129" t="n">
-        <v>2.011627525516055</v>
+        <v>1155106163.557721</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="130">
@@ -2247,13 +2247,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>63</v>
+        <v>5.400848146955979</v>
       </c>
       <c r="C130" t="n">
-        <v>47.11021123893239</v>
+        <v>1748420001.249814</v>
       </c>
       <c r="D130" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="131">
@@ -2261,13 +2261,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>12</v>
+        <v>8.378189027544332</v>
       </c>
       <c r="C131" t="n">
-        <v>91.06470402272723</v>
+        <v>1778673885.629681</v>
       </c>
       <c r="D131" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="132">
@@ -2275,10 +2275,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>63</v>
+        <v>7.324960214988865</v>
       </c>
       <c r="C132" t="n">
-        <v>65.70428272317591</v>
+        <v>2606437842.591223</v>
       </c>
       <c r="D132" t="n">
         <v>0.9</v>
@@ -2289,13 +2289,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>56</v>
+        <v>7.445615874198314</v>
       </c>
       <c r="C133" t="n">
-        <v>54.5520071595922</v>
+        <v>1954346123.152371</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="134">
@@ -2303,13 +2303,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>13</v>
+        <v>9.701041169558419</v>
       </c>
       <c r="C134" t="n">
-        <v>54.19311924052327</v>
+        <v>2000765732.960012</v>
       </c>
       <c r="D134" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="135">
@@ -2317,13 +2317,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>73</v>
+        <v>9.796572850807465</v>
       </c>
       <c r="C135" t="n">
-        <v>72.69645125244699</v>
+        <v>2988426515.297543</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="136">
@@ -2331,13 +2331,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>43</v>
+        <v>6.50697699819562</v>
       </c>
       <c r="C136" t="n">
-        <v>49.33991879549746</v>
+        <v>1696190327.937896</v>
       </c>
       <c r="D136" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="137">
@@ -2345,13 +2345,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>31</v>
+        <v>9.248334865790724</v>
       </c>
       <c r="C137" t="n">
-        <v>30.55991914285645</v>
+        <v>1809113438.400776</v>
       </c>
       <c r="D137" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="138">
@@ -2359,13 +2359,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>90</v>
+        <v>7.730883525795615</v>
       </c>
       <c r="C138" t="n">
-        <v>95.4931311234933</v>
+        <v>2921956850.055944</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="139">
@@ -2373,10 +2373,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>69</v>
+        <v>8.299715200021124</v>
       </c>
       <c r="C139" t="n">
-        <v>43.93200372400587</v>
+        <v>1293705758.161465</v>
       </c>
       <c r="D139" t="n">
         <v>0.99</v>
@@ -2387,10 +2387,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>59</v>
+        <v>7.737718064942428</v>
       </c>
       <c r="C140" t="n">
-        <v>59.42070020715195</v>
+        <v>906737637.3459659</v>
       </c>
       <c r="D140" t="n">
         <v>0.99</v>
@@ -2401,10 +2401,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>14</v>
+        <v>5.708867093096269</v>
       </c>
       <c r="C141" t="n">
-        <v>42.78065194952644</v>
+        <v>2388865969.210407</v>
       </c>
       <c r="D141" t="n">
         <v>0.999</v>
@@ -2415,10 +2415,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>98</v>
+        <v>9.481667622622265</v>
       </c>
       <c r="C142" t="n">
-        <v>78.5292938320666</v>
+        <v>2395886037.807007</v>
       </c>
       <c r="D142" t="n">
         <v>0.99</v>
@@ -2429,13 +2429,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>88</v>
+        <v>9.448141934406202</v>
       </c>
       <c r="C143" t="n">
-        <v>83.35988352385664</v>
+        <v>763780694.6552434</v>
       </c>
       <c r="D143" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="144">
@@ -2443,13 +2443,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>45</v>
+        <v>9.218301741548892</v>
       </c>
       <c r="C144" t="n">
-        <v>53.13104311335147</v>
+        <v>2952186250.023898</v>
       </c>
       <c r="D144" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="145">
@@ -2457,13 +2457,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>82</v>
+        <v>9.362774437607825</v>
       </c>
       <c r="C145" t="n">
-        <v>52.45409424763066</v>
+        <v>2734616842.820141</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="146">
@@ -2471,13 +2471,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>91</v>
+        <v>7.427651097593851</v>
       </c>
       <c r="C146" t="n">
-        <v>67.6065141898811</v>
+        <v>898561992.8394639</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="147">
@@ -2485,13 +2485,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>20</v>
+        <v>9.830532408992806</v>
       </c>
       <c r="C147" t="n">
-        <v>71.45259353970499</v>
+        <v>1415604309.968109</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="148">
@@ -2499,13 +2499,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>68</v>
+        <v>7.931055098143164</v>
       </c>
       <c r="C148" t="n">
-        <v>58.34130372695707</v>
+        <v>932449113.9085301</v>
       </c>
       <c r="D148" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="149">
@@ -2513,10 +2513,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>48</v>
+        <v>5.185596558288593</v>
       </c>
       <c r="C149" t="n">
-        <v>54.963017222701</v>
+        <v>1669530542.789629</v>
       </c>
       <c r="D149" t="n">
         <v>0.999</v>
@@ -2527,13 +2527,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>43</v>
+        <v>5.677980208432722</v>
       </c>
       <c r="C150" t="n">
-        <v>58.59593444859313</v>
+        <v>840738469.3680444</v>
       </c>
       <c r="D150" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="151">
@@ -2541,13 +2541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>32</v>
+        <v>8.697482177828576</v>
       </c>
       <c r="C151" t="n">
-        <v>56.28940686501164</v>
+        <v>741906759.4030292</v>
       </c>
       <c r="D151" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="152">
@@ -2555,13 +2555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>99</v>
+        <v>5.293847895663123</v>
       </c>
       <c r="C152" t="n">
-        <v>40.40835052706638</v>
+        <v>2361862860.751066</v>
       </c>
       <c r="D152" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="153">
@@ -2569,13 +2569,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>45</v>
+        <v>9.897154439227663</v>
       </c>
       <c r="C153" t="n">
-        <v>38.73957899158366</v>
+        <v>2657609497.498177</v>
       </c>
       <c r="D153" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="154">
@@ -2583,10 +2583,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>34</v>
+        <v>7.019377755860937</v>
       </c>
       <c r="C154" t="n">
-        <v>65.5221313656147</v>
+        <v>640453142.2281555</v>
       </c>
       <c r="D154" t="n">
         <v>0.999</v>
@@ -2597,10 +2597,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>95</v>
+        <v>9.587820533738263</v>
       </c>
       <c r="C155" t="n">
-        <v>71.21257686030701</v>
+        <v>2884313018.473613</v>
       </c>
       <c r="D155" t="n">
         <v>0.999</v>
@@ -2611,13 +2611,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>30</v>
+        <v>9.302161044876518</v>
       </c>
       <c r="C156" t="n">
-        <v>14.84769653520368</v>
+        <v>2424940444.053474</v>
       </c>
       <c r="D156" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="157">
@@ -2625,10 +2625,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>70</v>
+        <v>7.621717463782183</v>
       </c>
       <c r="C157" t="n">
-        <v>2.426151123820361</v>
+        <v>1076940053.7291</v>
       </c>
       <c r="D157" t="n">
         <v>0.9999</v>
@@ -2639,13 +2639,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>19</v>
+        <v>7.651102586263036</v>
       </c>
       <c r="C158" t="n">
-        <v>54.84775619720966</v>
+        <v>2886703761.717824</v>
       </c>
       <c r="D158" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="159">
@@ -2653,13 +2653,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>34</v>
+        <v>5.226070955955745</v>
       </c>
       <c r="C159" t="n">
-        <v>52.75681525556561</v>
+        <v>1435052248.951737</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="160">
@@ -2667,10 +2667,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>90</v>
+        <v>7.035601356667917</v>
       </c>
       <c r="C160" t="n">
-        <v>81.99540332484963</v>
+        <v>1969048860.432081</v>
       </c>
       <c r="D160" t="n">
         <v>0.99</v>
@@ -2681,13 +2681,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>45</v>
+        <v>8.680857826754625</v>
       </c>
       <c r="C161" t="n">
-        <v>56.3176443019234</v>
+        <v>2409397934.844779</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="162">
@@ -2695,10 +2695,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>91</v>
+        <v>5.142969946321989</v>
       </c>
       <c r="C162" t="n">
-        <v>41.08559990096147</v>
+        <v>1584013886.368867</v>
       </c>
       <c r="D162" t="n">
         <v>0.9</v>
@@ -2709,10 +2709,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>87</v>
+        <v>9.870067221314251</v>
       </c>
       <c r="C163" t="n">
-        <v>77.80084206769882</v>
+        <v>1551477243.965378</v>
       </c>
       <c r="D163" t="n">
         <v>0.9999</v>
@@ -2723,13 +2723,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>92</v>
+        <v>8.39474522869387</v>
       </c>
       <c r="C164" t="n">
-        <v>53.68435860118443</v>
+        <v>821468282.7579895</v>
       </c>
       <c r="D164" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="165">
@@ -2737,13 +2737,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>90</v>
+        <v>8.861286945458822</v>
       </c>
       <c r="C165" t="n">
-        <v>15.12021359519616</v>
+        <v>2384387806.821587</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="166">
@@ -2751,13 +2751,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>57</v>
+        <v>5.636239874031245</v>
       </c>
       <c r="C166" t="n">
-        <v>27.04346968202729</v>
+        <v>1489586911.695692</v>
       </c>
       <c r="D166" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="167">
@@ -2765,13 +2765,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>24</v>
+        <v>9.638401992999786</v>
       </c>
       <c r="C167" t="n">
-        <v>49.98233765831699</v>
+        <v>1250950748.566109</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="168">
@@ -2779,13 +2779,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>15</v>
+        <v>5.921145541753161</v>
       </c>
       <c r="C168" t="n">
-        <v>51.94614386963547</v>
+        <v>2233929786.262497</v>
       </c>
       <c r="D168" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="169">
@@ -2793,13 +2793,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>77</v>
+        <v>5.917958059436213</v>
       </c>
       <c r="C169" t="n">
-        <v>29.65076532844162</v>
+        <v>596048025.4325868</v>
       </c>
       <c r="D169" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="170">
@@ -2807,13 +2807,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>57</v>
+        <v>8.757253202729988</v>
       </c>
       <c r="C170" t="n">
-        <v>58.43377007293878</v>
+        <v>809364897.1798427</v>
       </c>
       <c r="D170" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="171">
@@ -2821,10 +2821,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>60</v>
+        <v>6.589629590323168</v>
       </c>
       <c r="C171" t="n">
-        <v>56.26027535154225</v>
+        <v>1402737157.527375</v>
       </c>
       <c r="D171" t="n">
         <v>0.9999</v>
@@ -2835,13 +2835,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>43</v>
+        <v>9.997025600772211</v>
       </c>
       <c r="C172" t="n">
-        <v>55.86817072728986</v>
+        <v>608893068.608657</v>
       </c>
       <c r="D172" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="173">
@@ -2849,13 +2849,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>24</v>
+        <v>5.082069217509956</v>
       </c>
       <c r="C173" t="n">
-        <v>50.15416751772711</v>
+        <v>861460682.9135125</v>
       </c>
       <c r="D173" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="174">
@@ -2863,13 +2863,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>40</v>
+        <v>9.155302645748199</v>
       </c>
       <c r="C174" t="n">
-        <v>53.85536539720606</v>
+        <v>2044814913.174829</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="175">
@@ -2877,13 +2877,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>26</v>
+        <v>6.217410533114614</v>
       </c>
       <c r="C175" t="n">
-        <v>13.87947006146145</v>
+        <v>2882830059.049108</v>
       </c>
       <c r="D175" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="176">
@@ -2891,13 +2891,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>78</v>
+        <v>6.145205794156533</v>
       </c>
       <c r="C176" t="n">
-        <v>38.80360715695589</v>
+        <v>2241227802.425351</v>
       </c>
       <c r="D176" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="177">
@@ -2905,13 +2905,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>60</v>
+        <v>6.18521554540158</v>
       </c>
       <c r="C177" t="n">
-        <v>32.85769207487141</v>
+        <v>2152991385.188523</v>
       </c>
       <c r="D177" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="178">
@@ -2919,13 +2919,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>50</v>
+        <v>7.358395160661519</v>
       </c>
       <c r="C178" t="n">
-        <v>68.69238990992848</v>
+        <v>1667897600.893052</v>
       </c>
       <c r="D178" t="n">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="179">
@@ -2933,10 +2933,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>35</v>
+        <v>9.641110704048838</v>
       </c>
       <c r="C179" t="n">
-        <v>57.41359397471884</v>
+        <v>2914908905.65963</v>
       </c>
       <c r="D179" t="n">
         <v>0.9</v>
@@ -2947,10 +2947,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>98</v>
+        <v>7.957316600072299</v>
       </c>
       <c r="C180" t="n">
-        <v>42.05664144139013</v>
+        <v>2979300970.384643</v>
       </c>
       <c r="D180" t="n">
         <v>0.9</v>
@@ -2961,10 +2961,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>47</v>
+        <v>7.465504927519392</v>
       </c>
       <c r="C181" t="n">
-        <v>47.48888036388623</v>
+        <v>2205874680.257127</v>
       </c>
       <c r="D181" t="n">
         <v>0.9</v>
@@ -2975,13 +2975,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>58</v>
+        <v>5.260701142381075</v>
       </c>
       <c r="C182" t="n">
-        <v>50.53832754832667</v>
+        <v>908822954.7926924</v>
       </c>
       <c r="D182" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="183">
@@ -2989,13 +2989,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>66</v>
+        <v>6.395010226695755</v>
       </c>
       <c r="C183" t="n">
-        <v>77.90666351085936</v>
+        <v>2746194971.10202</v>
       </c>
       <c r="D183" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="184">
@@ -3003,10 +3003,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>63</v>
+        <v>7.669987436048284</v>
       </c>
       <c r="C184" t="n">
-        <v>37.79834545505176</v>
+        <v>1150407595.305242</v>
       </c>
       <c r="D184" t="n">
         <v>0.999</v>
@@ -3017,13 +3017,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>90</v>
+        <v>9.139767836871766</v>
       </c>
       <c r="C185" t="n">
-        <v>56.67285777064668</v>
+        <v>1787355073.536524</v>
       </c>
       <c r="D185" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="186">
@@ -3031,13 +3031,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>68</v>
+        <v>9.260622974164672</v>
       </c>
       <c r="C186" t="n">
-        <v>69.81360629876897</v>
+        <v>2661820641.910182</v>
       </c>
       <c r="D186" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="187">
@@ -3045,13 +3045,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>57</v>
+        <v>6.433918493932298</v>
       </c>
       <c r="C187" t="n">
-        <v>39.43993100126566</v>
+        <v>2452762389.815001</v>
       </c>
       <c r="D187" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="188">
@@ -3059,13 +3059,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>72</v>
+        <v>5.901664337780066</v>
       </c>
       <c r="C188" t="n">
-        <v>61.21967923811923</v>
+        <v>1505640399.581657</v>
       </c>
       <c r="D188" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="189">
@@ -3073,10 +3073,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>24</v>
+        <v>6.332109053797483</v>
       </c>
       <c r="C189" t="n">
-        <v>68.53883169208245</v>
+        <v>2613536225.627382</v>
       </c>
       <c r="D189" t="n">
         <v>0.9999</v>
@@ -3087,13 +3087,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>96</v>
+        <v>9.458739391938826</v>
       </c>
       <c r="C190" t="n">
-        <v>40.32840479835944</v>
+        <v>540928221.0816225</v>
       </c>
       <c r="D190" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="191">
@@ -3101,13 +3101,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>47</v>
+        <v>8.51090461703539</v>
       </c>
       <c r="C191" t="n">
-        <v>59.12156385866909</v>
+        <v>2726574560.935286</v>
       </c>
       <c r="D191" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="192">
@@ -3115,13 +3115,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>83</v>
+        <v>5.420588284112573</v>
       </c>
       <c r="C192" t="n">
-        <v>55.51061408324165</v>
+        <v>621369893.092082</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="193">
@@ -3129,13 +3129,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>43</v>
+        <v>9.221643022095694</v>
       </c>
       <c r="C193" t="n">
-        <v>66.76227468936096</v>
+        <v>890822328.4409579</v>
       </c>
       <c r="D193" t="n">
-        <v>0.9999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="194">
@@ -3143,13 +3143,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>80</v>
+        <v>5.924044910088338</v>
       </c>
       <c r="C194" t="n">
-        <v>31.66950133959016</v>
+        <v>2593156155.67132</v>
       </c>
       <c r="D194" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="195">
@@ -3157,10 +3157,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>74</v>
+        <v>8.986205487409912</v>
       </c>
       <c r="C195" t="n">
-        <v>28.07121381962947</v>
+        <v>2146765976.473729</v>
       </c>
       <c r="D195" t="n">
         <v>0.9</v>
@@ -3171,13 +3171,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>45</v>
+        <v>5.595296319952236</v>
       </c>
       <c r="C196" t="n">
-        <v>54.19284683139474</v>
+        <v>1101003935.702557</v>
       </c>
       <c r="D196" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="197">
@@ -3185,13 +3185,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>29</v>
+        <v>7.415384247120892</v>
       </c>
       <c r="C197" t="n">
-        <v>49.12951657643197</v>
+        <v>811938994.0693042</v>
       </c>
       <c r="D197" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="198">
@@ -3199,13 +3199,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>25</v>
+        <v>9.095586272500798</v>
       </c>
       <c r="C198" t="n">
-        <v>33.64699996459905</v>
+        <v>1353553313.811045</v>
       </c>
       <c r="D198" t="n">
-        <v>0.9999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="199">
@@ -3213,10 +3213,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>19</v>
+        <v>5.597276903971256</v>
       </c>
       <c r="C199" t="n">
-        <v>37.21796035512192</v>
+        <v>2359451989.567934</v>
       </c>
       <c r="D199" t="n">
         <v>0.9</v>
@@ -3227,13 +3227,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>38</v>
+        <v>6.25204789135987</v>
       </c>
       <c r="C200" t="n">
-        <v>44.20300942513269</v>
+        <v>1140121086.273333</v>
       </c>
       <c r="D200" t="n">
-        <v>0.999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="201">
@@ -3241,13 +3241,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>65</v>
+        <v>8.628164587703029</v>
       </c>
       <c r="C201" t="n">
-        <v>62.21468626487874</v>
+        <v>2538630133.670936</v>
       </c>
       <c r="D201" t="n">
-        <v>0.9</v>
+        <v>0.999</v>
       </c>
     </row>
   </sheetData>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -458,7 +458,7 @@
         <v>6.611899903840291</v>
       </c>
       <c r="C2" t="n">
-        <v>1989703090.150963</v>
+        <v>3191762472.12077</v>
       </c>
       <c r="D2" t="n">
         <v>0.9999</v>
@@ -472,7 +472,7 @@
         <v>9.458478886863501</v>
       </c>
       <c r="C3" t="n">
-        <v>2519293403.746736</v>
+        <v>3615434722.997388</v>
       </c>
       <c r="D3" t="n">
         <v>0.99</v>
@@ -486,7 +486,7 @@
         <v>9.081351957255169</v>
       </c>
       <c r="C4" t="n">
-        <v>2495048170.173721</v>
+        <v>3596038536.138977</v>
       </c>
       <c r="D4" t="n">
         <v>0.9999</v>
@@ -500,7 +500,7 @@
         <v>8.311887795807797</v>
       </c>
       <c r="C5" t="n">
-        <v>2027065848.631681</v>
+        <v>3221652678.905345</v>
       </c>
       <c r="D5" t="n">
         <v>0.999</v>
@@ -514,7 +514,7 @@
         <v>9.370486220610481</v>
       </c>
       <c r="C6" t="n">
-        <v>1724350331.970877</v>
+        <v>2979480265.576702</v>
       </c>
       <c r="D6" t="n">
         <v>0.9999</v>
@@ -528,7 +528,7 @@
         <v>9.210885635292149</v>
       </c>
       <c r="C7" t="n">
-        <v>2733432476.42175</v>
+        <v>3786745981.1374</v>
       </c>
       <c r="D7" t="n">
         <v>0.9</v>
@@ -542,7 +542,7 @@
         <v>8.829022398812615</v>
       </c>
       <c r="C8" t="n">
-        <v>1124298297.232195</v>
+        <v>2499438637.785756</v>
       </c>
       <c r="D8" t="n">
         <v>0.999</v>
@@ -556,7 +556,7 @@
         <v>7.778460822747784</v>
       </c>
       <c r="C9" t="n">
-        <v>1679085563.708544</v>
+        <v>2943268450.966835</v>
       </c>
       <c r="D9" t="n">
         <v>0.9</v>
@@ -570,7 +570,7 @@
         <v>6.283012897856454</v>
       </c>
       <c r="C10" t="n">
-        <v>1385671456.720657</v>
+        <v>2708537165.376525</v>
       </c>
       <c r="D10" t="n">
         <v>0.9999</v>
@@ -584,7 +584,7 @@
         <v>5.917285407462558</v>
       </c>
       <c r="C11" t="n">
-        <v>2517764213.866761</v>
+        <v>3614211371.093409</v>
       </c>
       <c r="D11" t="n">
         <v>0.9</v>
@@ -598,7 +598,7 @@
         <v>9.760958695470894</v>
       </c>
       <c r="C12" t="n">
-        <v>1225712002.921154</v>
+        <v>2580569602.336924</v>
       </c>
       <c r="D12" t="n">
         <v>0.9999</v>
@@ -612,7 +612,7 @@
         <v>9.282624142385234</v>
       </c>
       <c r="C13" t="n">
-        <v>1140782074.98124</v>
+        <v>2512625659.984993</v>
       </c>
       <c r="D13" t="n">
         <v>0.9</v>
@@ -626,7 +626,7 @@
         <v>5.534341600131182</v>
       </c>
       <c r="C14" t="n">
-        <v>641432232.1030121</v>
+        <v>2113145785.68241</v>
       </c>
       <c r="D14" t="n">
         <v>0.99</v>
@@ -640,7 +640,7 @@
         <v>5.428265989060518</v>
       </c>
       <c r="C15" t="n">
-        <v>1010361887.491319</v>
+        <v>2408289509.993055</v>
       </c>
       <c r="D15" t="n">
         <v>0.9999</v>
@@ -654,7 +654,7 @@
         <v>9.744043570503546</v>
       </c>
       <c r="C16" t="n">
-        <v>2066500326.307691</v>
+        <v>3253200261.046153</v>
       </c>
       <c r="D16" t="n">
         <v>0.9</v>
@@ -668,7 +668,7 @@
         <v>6.474718115843953</v>
       </c>
       <c r="C17" t="n">
-        <v>544667959.2396631</v>
+        <v>2035734367.391731</v>
       </c>
       <c r="D17" t="n">
         <v>0.999</v>
@@ -682,7 +682,7 @@
         <v>6.054254594439056</v>
       </c>
       <c r="C18" t="n">
-        <v>2609504857.154016</v>
+        <v>3687603885.723213</v>
       </c>
       <c r="D18" t="n">
         <v>0.9999</v>
@@ -696,7 +696,7 @@
         <v>6.209703476792037</v>
       </c>
       <c r="C19" t="n">
-        <v>2931097588.003606</v>
+        <v>3944878070.402884</v>
       </c>
       <c r="D19" t="n">
         <v>0.99</v>
@@ -710,7 +710,7 @@
         <v>7.046210259333273</v>
       </c>
       <c r="C20" t="n">
-        <v>1446018456.515302</v>
+        <v>2756814765.212242</v>
       </c>
       <c r="D20" t="n">
         <v>0.999</v>
@@ -724,7 +724,7 @@
         <v>8.646376186779616</v>
       </c>
       <c r="C21" t="n">
-        <v>2856105569.979587</v>
+        <v>3884884455.98367</v>
       </c>
       <c r="D21" t="n">
         <v>0.9999</v>
@@ -738,7 +738,7 @@
         <v>9.254310893497342</v>
       </c>
       <c r="C22" t="n">
-        <v>1216293723.326428</v>
+        <v>2573034978.661143</v>
       </c>
       <c r="D22" t="n">
         <v>0.9999</v>
@@ -752,7 +752,7 @@
         <v>6.057953128354083</v>
       </c>
       <c r="C23" t="n">
-        <v>974472748.881427</v>
+        <v>2379578199.105142</v>
       </c>
       <c r="D23" t="n">
         <v>0.999</v>
@@ -766,7 +766,7 @@
         <v>8.142084699265133</v>
       </c>
       <c r="C24" t="n">
-        <v>1093793299.983983</v>
+        <v>2475034639.987186</v>
       </c>
       <c r="D24" t="n">
         <v>0.999</v>
@@ -780,7 +780,7 @@
         <v>5.176023926144904</v>
       </c>
       <c r="C25" t="n">
-        <v>2150854906.026975</v>
+        <v>3320683924.82158</v>
       </c>
       <c r="D25" t="n">
         <v>0.99</v>
@@ -794,7 +794,7 @@
         <v>9.282602162779529</v>
       </c>
       <c r="C26" t="n">
-        <v>2736597601.161132</v>
+        <v>3789278080.928905</v>
       </c>
       <c r="D26" t="n">
         <v>0.9</v>
@@ -808,7 +808,7 @@
         <v>6.483497669505885</v>
       </c>
       <c r="C27" t="n">
-        <v>1511925619.000439</v>
+        <v>2809540495.200351</v>
       </c>
       <c r="D27" t="n">
         <v>0.99</v>
@@ -822,7 +822,7 @@
         <v>6.907252271893272</v>
       </c>
       <c r="C28" t="n">
-        <v>1473980537.79228</v>
+        <v>2779184430.233824</v>
       </c>
       <c r="D28" t="n">
         <v>0.9999</v>
@@ -836,7 +836,7 @@
         <v>8.283160566707759</v>
       </c>
       <c r="C29" t="n">
-        <v>2854952438.464984</v>
+        <v>3883961950.771987</v>
       </c>
       <c r="D29" t="n">
         <v>0.9</v>
@@ -850,7 +850,7 @@
         <v>5.363459947892352</v>
       </c>
       <c r="C30" t="n">
-        <v>1623764217.973377</v>
+        <v>2899011374.378702</v>
       </c>
       <c r="D30" t="n">
         <v>0.9999</v>
@@ -864,7 +864,7 @@
         <v>9.075964754853276</v>
       </c>
       <c r="C31" t="n">
-        <v>2811834357.769165</v>
+        <v>3849467486.215332</v>
       </c>
       <c r="D31" t="n">
         <v>0.99</v>
@@ -878,7 +878,7 @@
         <v>6.005788933465668</v>
       </c>
       <c r="C32" t="n">
-        <v>1216056547.077393</v>
+        <v>2572845237.661914</v>
       </c>
       <c r="D32" t="n">
         <v>0.999</v>
@@ -892,7 +892,7 @@
         <v>6.595330091549068</v>
       </c>
       <c r="C33" t="n">
-        <v>2594073059.29355</v>
+        <v>3675258447.43484</v>
       </c>
       <c r="D33" t="n">
         <v>0.9999</v>
@@ -906,7 +906,7 @@
         <v>7.722771731304446</v>
       </c>
       <c r="C34" t="n">
-        <v>672413199.4616046</v>
+        <v>2137930559.569284</v>
       </c>
       <c r="D34" t="n">
         <v>0.9</v>
@@ -920,7 +920,7 @@
         <v>7.741879053497387</v>
       </c>
       <c r="C35" t="n">
-        <v>2178956013.297335</v>
+        <v>3343164810.637867</v>
       </c>
       <c r="D35" t="n">
         <v>0.9</v>
@@ -934,7 +934,7 @@
         <v>6.032941759473034</v>
       </c>
       <c r="C36" t="n">
-        <v>1490965557.204769</v>
+        <v>2792772445.763815</v>
       </c>
       <c r="D36" t="n">
         <v>0.9999</v>
@@ -948,7 +948,7 @@
         <v>8.267904618831091</v>
       </c>
       <c r="C37" t="n">
-        <v>1679792428.363853</v>
+        <v>2943833942.691082</v>
       </c>
       <c r="D37" t="n">
         <v>0.9</v>
@@ -962,7 +962,7 @@
         <v>9.276566808385919</v>
       </c>
       <c r="C38" t="n">
-        <v>1388485954.292586</v>
+        <v>2710788763.434069</v>
       </c>
       <c r="D38" t="n">
         <v>0.99</v>
@@ -976,7 +976,7 @@
         <v>5.807469817361404</v>
       </c>
       <c r="C39" t="n">
-        <v>842802389.6758053</v>
+        <v>2274241911.740644</v>
       </c>
       <c r="D39" t="n">
         <v>0.9</v>
@@ -990,7 +990,7 @@
         <v>9.705114053550254</v>
       </c>
       <c r="C40" t="n">
-        <v>1538381519.829908</v>
+        <v>2830705215.863926</v>
       </c>
       <c r="D40" t="n">
         <v>0.99</v>
@@ -1004,7 +1004,7 @@
         <v>8.339385529008545</v>
       </c>
       <c r="C41" t="n">
-        <v>1507034468.165098</v>
+        <v>2805627574.532079</v>
       </c>
       <c r="D41" t="n">
         <v>0.999</v>
@@ -1018,7 +1018,7 @@
         <v>5.77565924623604</v>
       </c>
       <c r="C42" t="n">
-        <v>1636717288.7258</v>
+        <v>2909373830.98064</v>
       </c>
       <c r="D42" t="n">
         <v>0.99</v>
@@ -1032,7 +1032,7 @@
         <v>9.836156741450633</v>
       </c>
       <c r="C43" t="n">
-        <v>2659720946.702735</v>
+        <v>3727776757.362188</v>
       </c>
       <c r="D43" t="n">
         <v>0.99</v>
@@ -1046,7 +1046,7 @@
         <v>6.674919334499503</v>
       </c>
       <c r="C44" t="n">
-        <v>1244150194.714226</v>
+        <v>2595320155.771381</v>
       </c>
       <c r="D44" t="n">
         <v>0.999</v>
@@ -1060,7 +1060,7 @@
         <v>6.636399425043879</v>
       </c>
       <c r="C45" t="n">
-        <v>787383993.1144338</v>
+        <v>2229907194.491547</v>
       </c>
       <c r="D45" t="n">
         <v>0.99</v>
@@ -1074,7 +1074,7 @@
         <v>9.853636449283801</v>
       </c>
       <c r="C46" t="n">
-        <v>1476384266.51726</v>
+        <v>2781107413.213808</v>
       </c>
       <c r="D46" t="n">
         <v>0.999</v>
@@ -1088,7 +1088,7 @@
         <v>6.443552953494433</v>
       </c>
       <c r="C47" t="n">
-        <v>2839482537.394162</v>
+        <v>3871586029.915329</v>
       </c>
       <c r="D47" t="n">
         <v>0.999</v>
@@ -1102,7 +1102,7 @@
         <v>5.652018647353982</v>
       </c>
       <c r="C48" t="n">
-        <v>1555598482.303327</v>
+        <v>2844478785.842661</v>
       </c>
       <c r="D48" t="n">
         <v>0.9</v>
@@ -1116,7 +1116,7 @@
         <v>6.410050401739351</v>
       </c>
       <c r="C49" t="n">
-        <v>1134496101.273098</v>
+        <v>2507596881.018478</v>
       </c>
       <c r="D49" t="n">
         <v>0.99</v>
@@ -1130,7 +1130,7 @@
         <v>5.336967930380334</v>
       </c>
       <c r="C50" t="n">
-        <v>1905508391.388878</v>
+        <v>3124406713.111102</v>
       </c>
       <c r="D50" t="n">
         <v>0.99</v>
@@ -1144,7 +1144,7 @@
         <v>6.402965611531205</v>
       </c>
       <c r="C51" t="n">
-        <v>2493109137.421947</v>
+        <v>3594487309.937557</v>
       </c>
       <c r="D51" t="n">
         <v>0.99</v>
@@ -1158,7 +1158,7 @@
         <v>9.943814996760505</v>
       </c>
       <c r="C52" t="n">
-        <v>2387880827.004162</v>
+        <v>3510304661.60333</v>
       </c>
       <c r="D52" t="n">
         <v>0.99</v>
@@ -1172,7 +1172,7 @@
         <v>6.962714935936077</v>
       </c>
       <c r="C53" t="n">
-        <v>2443142878.268995</v>
+        <v>3554514302.615196</v>
       </c>
       <c r="D53" t="n">
         <v>0.9</v>
@@ -1186,7 +1186,7 @@
         <v>7.404981059473712</v>
       </c>
       <c r="C54" t="n">
-        <v>2844089606.746162</v>
+        <v>3875271685.39693</v>
       </c>
       <c r="D54" t="n">
         <v>0.9</v>
@@ -1200,7 +1200,7 @@
         <v>5.122282779079272</v>
       </c>
       <c r="C55" t="n">
-        <v>2752767697.911618</v>
+        <v>3802214158.329295</v>
       </c>
       <c r="D55" t="n">
         <v>0.9</v>
@@ -1214,7 +1214,7 @@
         <v>7.822890048726163</v>
       </c>
       <c r="C56" t="n">
-        <v>1176950926.933015</v>
+        <v>2541560741.546412</v>
       </c>
       <c r="D56" t="n">
         <v>0.999</v>
@@ -1228,7 +1228,7 @@
         <v>8.213067663008902</v>
       </c>
       <c r="C57" t="n">
-        <v>2506097954.530643</v>
+        <v>3604878363.624515</v>
       </c>
       <c r="D57" t="n">
         <v>0.999</v>
@@ -1242,7 +1242,7 @@
         <v>6.65549153068613</v>
       </c>
       <c r="C58" t="n">
-        <v>1046226967.291394</v>
+        <v>2436981573.833116</v>
       </c>
       <c r="D58" t="n">
         <v>0.9</v>
@@ -1256,7 +1256,7 @@
         <v>8.420189493125106</v>
       </c>
       <c r="C59" t="n">
-        <v>1725419534.78552</v>
+        <v>2980335627.828416</v>
       </c>
       <c r="D59" t="n">
         <v>0.9</v>
@@ -1270,7 +1270,7 @@
         <v>8.482903378387856</v>
       </c>
       <c r="C60" t="n">
-        <v>1564464179.855836</v>
+        <v>2851571343.884669</v>
       </c>
       <c r="D60" t="n">
         <v>0.9</v>
@@ -1284,7 +1284,7 @@
         <v>7.81546108102293</v>
       </c>
       <c r="C61" t="n">
-        <v>2288915087.236743</v>
+        <v>3431132069.789394</v>
       </c>
       <c r="D61" t="n">
         <v>0.9</v>
@@ -1298,7 +1298,7 @@
         <v>7.319842628973613</v>
       </c>
       <c r="C62" t="n">
-        <v>691316745.6107179</v>
+        <v>2153053396.488575</v>
       </c>
       <c r="D62" t="n">
         <v>0.99</v>
@@ -1312,7 +1312,7 @@
         <v>9.871101650439041</v>
       </c>
       <c r="C63" t="n">
-        <v>515218065.4456663</v>
+        <v>2012174452.356533</v>
       </c>
       <c r="D63" t="n">
         <v>0.9999</v>
@@ -1326,7 +1326,7 @@
         <v>8.907704320302022</v>
       </c>
       <c r="C64" t="n">
-        <v>1912728047.381083</v>
+        <v>3130182437.904866</v>
       </c>
       <c r="D64" t="n">
         <v>0.999</v>
@@ -1340,7 +1340,7 @@
         <v>9.791049691331832</v>
       </c>
       <c r="C65" t="n">
-        <v>2859780964.541248</v>
+        <v>3887824771.632998</v>
       </c>
       <c r="D65" t="n">
         <v>0.9999</v>
@@ -1354,7 +1354,7 @@
         <v>6.390872229820053</v>
       </c>
       <c r="C66" t="n">
-        <v>2808729207.48243</v>
+        <v>3846983365.985945</v>
       </c>
       <c r="D66" t="n">
         <v>0.9999</v>
@@ -1368,7 +1368,7 @@
         <v>7.60070377899244</v>
       </c>
       <c r="C67" t="n">
-        <v>1078122543.680075</v>
+        <v>2462498034.94406</v>
       </c>
       <c r="D67" t="n">
         <v>0.9999</v>
@@ -1382,7 +1382,7 @@
         <v>8.409976737432554</v>
       </c>
       <c r="C68" t="n">
-        <v>2169214525.487341</v>
+        <v>3335371620.389873</v>
       </c>
       <c r="D68" t="n">
         <v>0.999</v>
@@ -1396,7 +1396,7 @@
         <v>8.505109991736525</v>
       </c>
       <c r="C69" t="n">
-        <v>808296924.757902</v>
+        <v>2246637539.806322</v>
       </c>
       <c r="D69" t="n">
         <v>0.9999</v>
@@ -1410,7 +1410,7 @@
         <v>8.814246889824869</v>
       </c>
       <c r="C70" t="n">
-        <v>2780643953.025884</v>
+        <v>3824515162.420707</v>
       </c>
       <c r="D70" t="n">
         <v>0.99</v>
@@ -1424,7 +1424,7 @@
         <v>8.865287002252314</v>
       </c>
       <c r="C71" t="n">
-        <v>1636845603.919624</v>
+        <v>2909476483.135699</v>
       </c>
       <c r="D71" t="n">
         <v>0.99</v>
@@ -1438,7 +1438,7 @@
         <v>5.495906001553889</v>
       </c>
       <c r="C72" t="n">
-        <v>802274440.5400271</v>
+        <v>2241819552.432022</v>
       </c>
       <c r="D72" t="n">
         <v>0.9</v>
@@ -1452,7 +1452,7 @@
         <v>6.807673276432142</v>
       </c>
       <c r="C73" t="n">
-        <v>1672940504.981586</v>
+        <v>2938352403.985269</v>
       </c>
       <c r="D73" t="n">
         <v>0.9999</v>
@@ -1466,7 +1466,7 @@
         <v>8.220531817182053</v>
       </c>
       <c r="C74" t="n">
-        <v>2233397030.223283</v>
+        <v>3386717624.178626</v>
       </c>
       <c r="D74" t="n">
         <v>0.9</v>
@@ -1480,7 +1480,7 @@
         <v>5.834103481676578</v>
       </c>
       <c r="C75" t="n">
-        <v>770581626.5889349</v>
+        <v>2216465301.271148</v>
       </c>
       <c r="D75" t="n">
         <v>0.9999</v>
@@ -1494,7 +1494,7 @@
         <v>7.465050077051474</v>
       </c>
       <c r="C76" t="n">
-        <v>1956517398.691969</v>
+        <v>3165213918.953576</v>
       </c>
       <c r="D76" t="n">
         <v>0.99</v>
@@ -1508,7 +1508,7 @@
         <v>6.041796645817093</v>
       </c>
       <c r="C77" t="n">
-        <v>2378825145.114942</v>
+        <v>3503060116.091953</v>
       </c>
       <c r="D77" t="n">
         <v>0.99</v>
@@ -1522,7 +1522,7 @@
         <v>6.301179454558705</v>
       </c>
       <c r="C78" t="n">
-        <v>1864050629.888839</v>
+        <v>3091240503.911071</v>
       </c>
       <c r="D78" t="n">
         <v>0.9</v>
@@ -1536,7 +1536,7 @@
         <v>6.714346298716169</v>
       </c>
       <c r="C79" t="n">
-        <v>780218226.9073039</v>
+        <v>2224174581.525843</v>
       </c>
       <c r="D79" t="n">
         <v>0.9999</v>
@@ -1550,7 +1550,7 @@
         <v>8.072007492228828</v>
       </c>
       <c r="C80" t="n">
-        <v>2601485923.728729</v>
+        <v>3681188738.982984</v>
       </c>
       <c r="D80" t="n">
         <v>0.9999</v>
@@ -1564,7 +1564,7 @@
         <v>5.183506474676499</v>
       </c>
       <c r="C81" t="n">
-        <v>2754928479.261498</v>
+        <v>3803942783.409199</v>
       </c>
       <c r="D81" t="n">
         <v>0.99</v>
@@ -1578,7 +1578,7 @@
         <v>6.91695401837892</v>
       </c>
       <c r="C82" t="n">
-        <v>629753935.7811328</v>
+        <v>2103803148.624906</v>
       </c>
       <c r="D82" t="n">
         <v>0.9</v>
@@ -1592,7 +1592,7 @@
         <v>5.046475802160269</v>
       </c>
       <c r="C83" t="n">
-        <v>2081292138.473792</v>
+        <v>3265033710.779034</v>
       </c>
       <c r="D83" t="n">
         <v>0.999</v>
@@ -1606,7 +1606,7 @@
         <v>7.404340845148446</v>
       </c>
       <c r="C84" t="n">
-        <v>859972185.9170504</v>
+        <v>2287977748.73364</v>
       </c>
       <c r="D84" t="n">
         <v>0.999</v>
@@ -1620,7 +1620,7 @@
         <v>8.693900116959423</v>
       </c>
       <c r="C85" t="n">
-        <v>1998979332.206363</v>
+        <v>3199183465.765091</v>
       </c>
       <c r="D85" t="n">
         <v>0.9999</v>
@@ -1634,7 +1634,7 @@
         <v>6.516335699756119</v>
       </c>
       <c r="C86" t="n">
-        <v>729742017.3354971</v>
+        <v>2183793613.868398</v>
       </c>
       <c r="D86" t="n">
         <v>0.999</v>
@@ -1648,7 +1648,7 @@
         <v>5.857738810924522</v>
       </c>
       <c r="C87" t="n">
-        <v>2929336639.801004</v>
+        <v>3943469311.840803</v>
       </c>
       <c r="D87" t="n">
         <v>0.999</v>
@@ -1662,7 +1662,7 @@
         <v>7.176567696545254</v>
       </c>
       <c r="C88" t="n">
-        <v>2210388596.787389</v>
+        <v>3368310877.429912</v>
       </c>
       <c r="D88" t="n">
         <v>0.999</v>
@@ -1676,7 +1676,7 @@
         <v>9.25484515495836</v>
       </c>
       <c r="C89" t="n">
-        <v>2869249564.120878</v>
+        <v>3895399651.296702</v>
       </c>
       <c r="D89" t="n">
         <v>0.99</v>
@@ -1690,7 +1690,7 @@
         <v>5.402508771295981</v>
       </c>
       <c r="C90" t="n">
-        <v>1799077059.684667</v>
+        <v>3039261647.747734</v>
       </c>
       <c r="D90" t="n">
         <v>0.9</v>
@@ -1704,7 +1704,7 @@
         <v>6.589028662499068</v>
       </c>
       <c r="C91" t="n">
-        <v>1821891479.093677</v>
+        <v>3057513183.274941</v>
       </c>
       <c r="D91" t="n">
         <v>0.99</v>
@@ -1718,7 +1718,7 @@
         <v>7.154427565768393</v>
       </c>
       <c r="C92" t="n">
-        <v>2638787734.712307</v>
+        <v>3711030187.769846</v>
       </c>
       <c r="D92" t="n">
         <v>0.99</v>
@@ -1732,7 +1732,7 @@
         <v>6.879968859769034</v>
       </c>
       <c r="C93" t="n">
-        <v>1402432230.702607</v>
+        <v>2721945784.562086</v>
       </c>
       <c r="D93" t="n">
         <v>0.9</v>
@@ -1746,7 +1746,7 @@
         <v>5.833685351680612</v>
       </c>
       <c r="C94" t="n">
-        <v>2714268175.336475</v>
+        <v>3771414540.26918</v>
       </c>
       <c r="D94" t="n">
         <v>0.9999</v>
@@ -1760,7 +1760,7 @@
         <v>9.715217899482422</v>
       </c>
       <c r="C95" t="n">
-        <v>1274477925.597403</v>
+        <v>2619582340.477922</v>
       </c>
       <c r="D95" t="n">
         <v>0.9</v>
@@ -1774,7 +1774,7 @@
         <v>7.597313861215067</v>
       </c>
       <c r="C96" t="n">
-        <v>2080794532.914496</v>
+        <v>3264635626.331596</v>
       </c>
       <c r="D96" t="n">
         <v>0.9</v>
@@ -1788,7 +1788,7 @@
         <v>6.870364089749534</v>
       </c>
       <c r="C97" t="n">
-        <v>1247064529.464164</v>
+        <v>2597651623.571331</v>
       </c>
       <c r="D97" t="n">
         <v>0.999</v>
@@ -1802,7 +1802,7 @@
         <v>6.291534580229565</v>
       </c>
       <c r="C98" t="n">
-        <v>1704818844.10517</v>
+        <v>2963855075.284136</v>
       </c>
       <c r="D98" t="n">
         <v>0.9999</v>
@@ -1816,7 +1816,7 @@
         <v>6.365240642929789</v>
       </c>
       <c r="C99" t="n">
-        <v>2142362719.296712</v>
+        <v>3313890175.43737</v>
       </c>
       <c r="D99" t="n">
         <v>0.999</v>
@@ -1830,7 +1830,7 @@
         <v>8.734971368674017</v>
       </c>
       <c r="C100" t="n">
-        <v>1646337667.957947</v>
+        <v>2917070134.366358</v>
       </c>
       <c r="D100" t="n">
         <v>0.999</v>
@@ -1844,7 +1844,7 @@
         <v>9.713175634368366</v>
       </c>
       <c r="C101" t="n">
-        <v>2119567688.880301</v>
+        <v>3295654151.10424</v>
       </c>
       <c r="D101" t="n">
         <v>0.9</v>
@@ -1858,7 +1858,7 @@
         <v>9.15896561591472</v>
       </c>
       <c r="C102" t="n">
-        <v>1775310352.899411</v>
+        <v>3020248282.319529</v>
       </c>
       <c r="D102" t="n">
         <v>0.99</v>
@@ -1872,7 +1872,7 @@
         <v>6.789546794849374</v>
       </c>
       <c r="C103" t="n">
-        <v>1109597168.584832</v>
+        <v>2487677734.867866</v>
       </c>
       <c r="D103" t="n">
         <v>0.9999</v>
@@ -1886,7 +1886,7 @@
         <v>8.311965561475215</v>
       </c>
       <c r="C104" t="n">
-        <v>2043061636.516008</v>
+        <v>3234449309.212807</v>
       </c>
       <c r="D104" t="n">
         <v>0.999</v>
@@ -1900,7 +1900,7 @@
         <v>9.241315784513915</v>
       </c>
       <c r="C105" t="n">
-        <v>562394158.5221497</v>
+        <v>2049915326.81772</v>
       </c>
       <c r="D105" t="n">
         <v>0.999</v>
@@ -1914,7 +1914,7 @@
         <v>6.979073162972787</v>
       </c>
       <c r="C106" t="n">
-        <v>1551866889.283085</v>
+        <v>2841493511.426468</v>
       </c>
       <c r="D106" t="n">
         <v>0.9999</v>
@@ -1928,7 +1928,7 @@
         <v>5.589794987767421</v>
       </c>
       <c r="C107" t="n">
-        <v>901494901.5442753</v>
+        <v>2321195921.23542</v>
       </c>
       <c r="D107" t="n">
         <v>0.999</v>
@@ -1942,7 +1942,7 @@
         <v>7.48698853242043</v>
       </c>
       <c r="C108" t="n">
-        <v>876051798.4349151</v>
+        <v>2300841438.747932</v>
       </c>
       <c r="D108" t="n">
         <v>0.9999</v>
@@ -1956,7 +1956,7 @@
         <v>7.249433425142258</v>
       </c>
       <c r="C109" t="n">
-        <v>1839484086.912312</v>
+        <v>3071587269.52985</v>
       </c>
       <c r="D109" t="n">
         <v>0.999</v>
@@ -1970,7 +1970,7 @@
         <v>9.037488532289153</v>
       </c>
       <c r="C110" t="n">
-        <v>2321968984.01813</v>
+        <v>3457575187.214504</v>
       </c>
       <c r="D110" t="n">
         <v>0.99</v>
@@ -1984,7 +1984,7 @@
         <v>9.847461786940883</v>
       </c>
       <c r="C111" t="n">
-        <v>2160251269.166466</v>
+        <v>3328201015.333173</v>
       </c>
       <c r="D111" t="n">
         <v>0.9999</v>
@@ -1998,7 +1998,7 @@
         <v>6.341987841961975</v>
       </c>
       <c r="C112" t="n">
-        <v>1129480267.558282</v>
+        <v>2503584214.046626</v>
       </c>
       <c r="D112" t="n">
         <v>0.9999</v>
@@ -2012,7 +2012,7 @@
         <v>6.353538425519317</v>
       </c>
       <c r="C113" t="n">
-        <v>1757975477.342786</v>
+        <v>3006380381.874228</v>
       </c>
       <c r="D113" t="n">
         <v>0.9999</v>
@@ -2026,7 +2026,7 @@
         <v>8.674098915596558</v>
       </c>
       <c r="C114" t="n">
-        <v>1193904405.508304</v>
+        <v>2555123524.406643</v>
       </c>
       <c r="D114" t="n">
         <v>0.9999</v>
@@ -2040,7 +2040,7 @@
         <v>8.11601168397852</v>
       </c>
       <c r="C115" t="n">
-        <v>1279163638.819794</v>
+        <v>2623330911.055835</v>
       </c>
       <c r="D115" t="n">
         <v>0.99</v>
@@ -2054,7 +2054,7 @@
         <v>5.690753105669546</v>
       </c>
       <c r="C116" t="n">
-        <v>1162754147.959435</v>
+        <v>2530203318.367548</v>
       </c>
       <c r="D116" t="n">
         <v>0.9999</v>
@@ -2068,7 +2068,7 @@
         <v>7.113712966206531</v>
       </c>
       <c r="C117" t="n">
-        <v>2761662664.442652</v>
+        <v>3809330131.554121</v>
       </c>
       <c r="D117" t="n">
         <v>0.99</v>
@@ -2082,7 +2082,7 @@
         <v>9.383260788900309</v>
       </c>
       <c r="C118" t="n">
-        <v>2406303792.990534</v>
+        <v>3525043034.392427</v>
       </c>
       <c r="D118" t="n">
         <v>0.99</v>
@@ -2096,7 +2096,7 @@
         <v>6.414745755801159</v>
       </c>
       <c r="C119" t="n">
-        <v>609544070.5114353</v>
+        <v>2087635256.409148</v>
       </c>
       <c r="D119" t="n">
         <v>0.999</v>
@@ -2110,7 +2110,7 @@
         <v>7.456974832651706</v>
       </c>
       <c r="C120" t="n">
-        <v>2127555515.604955</v>
+        <v>3302044412.483964</v>
       </c>
       <c r="D120" t="n">
         <v>0.999</v>
@@ -2124,7 +2124,7 @@
         <v>7.39733827874154</v>
       </c>
       <c r="C121" t="n">
-        <v>849787732.7973753</v>
+        <v>2279830186.2379</v>
       </c>
       <c r="D121" t="n">
         <v>0.9</v>
@@ -2138,7 +2138,7 @@
         <v>9.239971161686251</v>
       </c>
       <c r="C122" t="n">
-        <v>1152491338.318102</v>
+        <v>2521993070.654481</v>
       </c>
       <c r="D122" t="n">
         <v>0.999</v>
@@ -2152,7 +2152,7 @@
         <v>5.760777808737239</v>
       </c>
       <c r="C123" t="n">
-        <v>1981587795.066815</v>
+        <v>3185270236.053452</v>
       </c>
       <c r="D123" t="n">
         <v>0.99</v>
@@ -2166,7 +2166,7 @@
         <v>5.065228863521137</v>
       </c>
       <c r="C124" t="n">
-        <v>1256817101.656187</v>
+        <v>2605453681.324949</v>
       </c>
       <c r="D124" t="n">
         <v>0.99</v>
@@ -2180,7 +2180,7 @@
         <v>9.525031542747652</v>
       </c>
       <c r="C125" t="n">
-        <v>786618083.2632445</v>
+        <v>2229294466.610596</v>
       </c>
       <c r="D125" t="n">
         <v>0.9</v>
@@ -2194,7 +2194,7 @@
         <v>5.621719538665848</v>
       </c>
       <c r="C126" t="n">
-        <v>2043752248.302609</v>
+        <v>3235001798.642087</v>
       </c>
       <c r="D126" t="n">
         <v>0.99</v>
@@ -2208,7 +2208,7 @@
         <v>8.858874399899515</v>
       </c>
       <c r="C127" t="n">
-        <v>1613479063.569354</v>
+        <v>2890783250.855483</v>
       </c>
       <c r="D127" t="n">
         <v>0.9999</v>
@@ -2222,7 +2222,7 @@
         <v>5.497343131601155</v>
       </c>
       <c r="C128" t="n">
-        <v>1235367413.273307</v>
+        <v>2588293930.618646</v>
       </c>
       <c r="D128" t="n">
         <v>0.999</v>
@@ -2236,7 +2236,7 @@
         <v>9.625276021660749</v>
       </c>
       <c r="C129" t="n">
-        <v>1155106163.557721</v>
+        <v>2524084930.846177</v>
       </c>
       <c r="D129" t="n">
         <v>0.999</v>
@@ -2250,7 +2250,7 @@
         <v>5.400848146955979</v>
       </c>
       <c r="C130" t="n">
-        <v>1748420001.249814</v>
+        <v>2998736000.999851</v>
       </c>
       <c r="D130" t="n">
         <v>0.9</v>
@@ -2264,7 +2264,7 @@
         <v>8.378189027544332</v>
       </c>
       <c r="C131" t="n">
-        <v>1778673885.629681</v>
+        <v>3022939108.503745</v>
       </c>
       <c r="D131" t="n">
         <v>0.999</v>
@@ -2278,7 +2278,7 @@
         <v>7.324960214988865</v>
       </c>
       <c r="C132" t="n">
-        <v>2606437842.591223</v>
+        <v>3685150274.072979</v>
       </c>
       <c r="D132" t="n">
         <v>0.9</v>
@@ -2292,7 +2292,7 @@
         <v>7.445615874198314</v>
       </c>
       <c r="C133" t="n">
-        <v>1954346123.152371</v>
+        <v>3163476898.521896</v>
       </c>
       <c r="D133" t="n">
         <v>0.9999</v>
@@ -2306,7 +2306,7 @@
         <v>9.701041169558419</v>
       </c>
       <c r="C134" t="n">
-        <v>2000765732.960012</v>
+        <v>3200612586.36801</v>
       </c>
       <c r="D134" t="n">
         <v>0.9</v>
@@ -2320,7 +2320,7 @@
         <v>9.796572850807465</v>
       </c>
       <c r="C135" t="n">
-        <v>2988426515.297543</v>
+        <v>3990741212.238034</v>
       </c>
       <c r="D135" t="n">
         <v>0.99</v>
@@ -2334,7 +2334,7 @@
         <v>6.50697699819562</v>
       </c>
       <c r="C136" t="n">
-        <v>1696190327.937896</v>
+        <v>2956952262.350317</v>
       </c>
       <c r="D136" t="n">
         <v>0.9999</v>
@@ -2348,7 +2348,7 @@
         <v>9.248334865790724</v>
       </c>
       <c r="C137" t="n">
-        <v>1809113438.400776</v>
+        <v>3047290750.720621</v>
       </c>
       <c r="D137" t="n">
         <v>0.9999</v>
@@ -2362,7 +2362,7 @@
         <v>7.730883525795615</v>
       </c>
       <c r="C138" t="n">
-        <v>2921956850.055944</v>
+        <v>3937565480.044756</v>
       </c>
       <c r="D138" t="n">
         <v>0.9999</v>
@@ -2376,7 +2376,7 @@
         <v>8.299715200021124</v>
       </c>
       <c r="C139" t="n">
-        <v>1293705758.161465</v>
+        <v>2634964606.529172</v>
       </c>
       <c r="D139" t="n">
         <v>0.99</v>
@@ -2390,7 +2390,7 @@
         <v>7.737718064942428</v>
       </c>
       <c r="C140" t="n">
-        <v>906737637.3459659</v>
+        <v>2325390109.876773</v>
       </c>
       <c r="D140" t="n">
         <v>0.99</v>
@@ -2404,7 +2404,7 @@
         <v>5.708867093096269</v>
       </c>
       <c r="C141" t="n">
-        <v>2388865969.210407</v>
+        <v>3511092775.368326</v>
       </c>
       <c r="D141" t="n">
         <v>0.999</v>
@@ -2418,7 +2418,7 @@
         <v>9.481667622622265</v>
       </c>
       <c r="C142" t="n">
-        <v>2395886037.807007</v>
+        <v>3516708830.245605</v>
       </c>
       <c r="D142" t="n">
         <v>0.99</v>
@@ -2432,7 +2432,7 @@
         <v>9.448141934406202</v>
       </c>
       <c r="C143" t="n">
-        <v>763780694.6552434</v>
+        <v>2211024555.724195</v>
       </c>
       <c r="D143" t="n">
         <v>0.999</v>
@@ -2446,7 +2446,7 @@
         <v>9.218301741548892</v>
       </c>
       <c r="C144" t="n">
-        <v>2952186250.023898</v>
+        <v>3961749000.019118</v>
       </c>
       <c r="D144" t="n">
         <v>0.9</v>
@@ -2460,7 +2460,7 @@
         <v>9.362774437607825</v>
       </c>
       <c r="C145" t="n">
-        <v>2734616842.820141</v>
+        <v>3787693474.256113</v>
       </c>
       <c r="D145" t="n">
         <v>0.9</v>
@@ -2474,7 +2474,7 @@
         <v>7.427651097593851</v>
       </c>
       <c r="C146" t="n">
-        <v>898561992.8394639</v>
+        <v>2318849594.271571</v>
       </c>
       <c r="D146" t="n">
         <v>0.99</v>
@@ -2488,7 +2488,7 @@
         <v>9.830532408992806</v>
       </c>
       <c r="C147" t="n">
-        <v>1415604309.968109</v>
+        <v>2732483447.974487</v>
       </c>
       <c r="D147" t="n">
         <v>0.9999</v>
@@ -2502,7 +2502,7 @@
         <v>7.931055098143164</v>
       </c>
       <c r="C148" t="n">
-        <v>932449113.9085301</v>
+        <v>2345959291.126824</v>
       </c>
       <c r="D148" t="n">
         <v>0.9999</v>
@@ -2516,7 +2516,7 @@
         <v>5.185596558288593</v>
       </c>
       <c r="C149" t="n">
-        <v>1669530542.789629</v>
+        <v>2935624434.231703</v>
       </c>
       <c r="D149" t="n">
         <v>0.999</v>
@@ -2530,7 +2530,7 @@
         <v>5.677980208432722</v>
       </c>
       <c r="C150" t="n">
-        <v>840738469.3680444</v>
+        <v>2272590775.494435</v>
       </c>
       <c r="D150" t="n">
         <v>0.999</v>
@@ -2544,7 +2544,7 @@
         <v>8.697482177828576</v>
       </c>
       <c r="C151" t="n">
-        <v>741906759.4030292</v>
+        <v>2193525407.522423</v>
       </c>
       <c r="D151" t="n">
         <v>0.999</v>
@@ -2558,7 +2558,7 @@
         <v>5.293847895663123</v>
       </c>
       <c r="C152" t="n">
-        <v>2361862860.751066</v>
+        <v>3489490288.600853</v>
       </c>
       <c r="D152" t="n">
         <v>0.999</v>
@@ -2572,7 +2572,7 @@
         <v>9.897154439227663</v>
       </c>
       <c r="C153" t="n">
-        <v>2657609497.498177</v>
+        <v>3726087597.998542</v>
       </c>
       <c r="D153" t="n">
         <v>0.999</v>
@@ -2586,7 +2586,7 @@
         <v>7.019377755860937</v>
       </c>
       <c r="C154" t="n">
-        <v>640453142.2281555</v>
+        <v>2112362513.782524</v>
       </c>
       <c r="D154" t="n">
         <v>0.999</v>
@@ -2600,7 +2600,7 @@
         <v>9.587820533738263</v>
       </c>
       <c r="C155" t="n">
-        <v>2884313018.473613</v>
+        <v>3907450414.778891</v>
       </c>
       <c r="D155" t="n">
         <v>0.999</v>
@@ -2614,7 +2614,7 @@
         <v>9.302161044876518</v>
       </c>
       <c r="C156" t="n">
-        <v>2424940444.053474</v>
+        <v>3539952355.24278</v>
       </c>
       <c r="D156" t="n">
         <v>0.9999</v>
@@ -2628,7 +2628,7 @@
         <v>7.621717463782183</v>
       </c>
       <c r="C157" t="n">
-        <v>1076940053.7291</v>
+        <v>2461552042.98328</v>
       </c>
       <c r="D157" t="n">
         <v>0.9999</v>
@@ -2642,7 +2642,7 @@
         <v>7.651102586263036</v>
       </c>
       <c r="C158" t="n">
-        <v>2886703761.717824</v>
+        <v>3909363009.374259</v>
       </c>
       <c r="D158" t="n">
         <v>0.9</v>
@@ -2656,7 +2656,7 @@
         <v>5.226070955955745</v>
       </c>
       <c r="C159" t="n">
-        <v>1435052248.951737</v>
+        <v>2748041799.16139</v>
       </c>
       <c r="D159" t="n">
         <v>0.9</v>
@@ -2670,7 +2670,7 @@
         <v>7.035601356667917</v>
       </c>
       <c r="C160" t="n">
-        <v>1969048860.432081</v>
+        <v>3175239088.345665</v>
       </c>
       <c r="D160" t="n">
         <v>0.99</v>
@@ -2684,7 +2684,7 @@
         <v>8.680857826754625</v>
       </c>
       <c r="C161" t="n">
-        <v>2409397934.844779</v>
+        <v>3527518347.875824</v>
       </c>
       <c r="D161" t="n">
         <v>0.99</v>
@@ -2698,7 +2698,7 @@
         <v>5.142969946321989</v>
       </c>
       <c r="C162" t="n">
-        <v>1584013886.368867</v>
+        <v>2867211109.095093</v>
       </c>
       <c r="D162" t="n">
         <v>0.9</v>
@@ -2712,7 +2712,7 @@
         <v>9.870067221314251</v>
       </c>
       <c r="C163" t="n">
-        <v>1551477243.965378</v>
+        <v>2841181795.172303</v>
       </c>
       <c r="D163" t="n">
         <v>0.9999</v>
@@ -2726,7 +2726,7 @@
         <v>8.39474522869387</v>
       </c>
       <c r="C164" t="n">
-        <v>821468282.7579895</v>
+        <v>2257174626.206392</v>
       </c>
       <c r="D164" t="n">
         <v>0.99</v>
@@ -2740,7 +2740,7 @@
         <v>8.861286945458822</v>
       </c>
       <c r="C165" t="n">
-        <v>2384387806.821587</v>
+        <v>3507510245.45727</v>
       </c>
       <c r="D165" t="n">
         <v>0.99</v>
@@ -2754,7 +2754,7 @@
         <v>5.636239874031245</v>
       </c>
       <c r="C166" t="n">
-        <v>1489586911.695692</v>
+        <v>2791669529.356554</v>
       </c>
       <c r="D166" t="n">
         <v>0.9999</v>
@@ -2768,7 +2768,7 @@
         <v>9.638401992999786</v>
       </c>
       <c r="C167" t="n">
-        <v>1250950748.566109</v>
+        <v>2600760598.852888</v>
       </c>
       <c r="D167" t="n">
         <v>0.9999</v>
@@ -2782,7 +2782,7 @@
         <v>5.921145541753161</v>
       </c>
       <c r="C168" t="n">
-        <v>2233929786.262497</v>
+        <v>3387143829.009998</v>
       </c>
       <c r="D168" t="n">
         <v>0.999</v>
@@ -2796,7 +2796,7 @@
         <v>5.917958059436213</v>
       </c>
       <c r="C169" t="n">
-        <v>596048025.4325868</v>
+        <v>2076838420.34607</v>
       </c>
       <c r="D169" t="n">
         <v>0.9999</v>
@@ -2810,7 +2810,7 @@
         <v>8.757253202729988</v>
       </c>
       <c r="C170" t="n">
-        <v>809364897.1798427</v>
+        <v>2247491917.743874</v>
       </c>
       <c r="D170" t="n">
         <v>0.99</v>
@@ -2824,7 +2824,7 @@
         <v>6.589629590323168</v>
       </c>
       <c r="C171" t="n">
-        <v>1402737157.527375</v>
+        <v>2722189726.0219</v>
       </c>
       <c r="D171" t="n">
         <v>0.9999</v>
@@ -2838,7 +2838,7 @@
         <v>9.997025600772211</v>
       </c>
       <c r="C172" t="n">
-        <v>608893068.608657</v>
+        <v>2087114454.886926</v>
       </c>
       <c r="D172" t="n">
         <v>0.9</v>
@@ -2852,7 +2852,7 @@
         <v>5.082069217509956</v>
       </c>
       <c r="C173" t="n">
-        <v>861460682.9135125</v>
+        <v>2289168546.33081</v>
       </c>
       <c r="D173" t="n">
         <v>0.99</v>
@@ -2866,7 +2866,7 @@
         <v>9.155302645748199</v>
       </c>
       <c r="C174" t="n">
-        <v>2044814913.174829</v>
+        <v>3235851930.539863</v>
       </c>
       <c r="D174" t="n">
         <v>0.99</v>
@@ -2880,7 +2880,7 @@
         <v>6.217410533114614</v>
       </c>
       <c r="C175" t="n">
-        <v>2882830059.049108</v>
+        <v>3906264047.239286</v>
       </c>
       <c r="D175" t="n">
         <v>0.999</v>
@@ -2894,7 +2894,7 @@
         <v>6.145205794156533</v>
       </c>
       <c r="C176" t="n">
-        <v>2241227802.425351</v>
+        <v>3392982241.940281</v>
       </c>
       <c r="D176" t="n">
         <v>0.999</v>
@@ -2908,7 +2908,7 @@
         <v>6.18521554540158</v>
       </c>
       <c r="C177" t="n">
-        <v>2152991385.188523</v>
+        <v>3322393108.150819</v>
       </c>
       <c r="D177" t="n">
         <v>0.99</v>
@@ -2922,7 +2922,7 @@
         <v>7.358395160661519</v>
       </c>
       <c r="C178" t="n">
-        <v>1667897600.893052</v>
+        <v>2934318080.714441</v>
       </c>
       <c r="D178" t="n">
         <v>0.999</v>
@@ -2936,7 +2936,7 @@
         <v>9.641110704048838</v>
       </c>
       <c r="C179" t="n">
-        <v>2914908905.65963</v>
+        <v>3931927124.527704</v>
       </c>
       <c r="D179" t="n">
         <v>0.9</v>
@@ -2950,7 +2950,7 @@
         <v>7.957316600072299</v>
       </c>
       <c r="C180" t="n">
-        <v>2979300970.384643</v>
+        <v>3983440776.307714</v>
       </c>
       <c r="D180" t="n">
         <v>0.9</v>
@@ -2964,7 +2964,7 @@
         <v>7.465504927519392</v>
       </c>
       <c r="C181" t="n">
-        <v>2205874680.257127</v>
+        <v>3364699744.205702</v>
       </c>
       <c r="D181" t="n">
         <v>0.9</v>
@@ -2978,7 +2978,7 @@
         <v>5.260701142381075</v>
       </c>
       <c r="C182" t="n">
-        <v>908822954.7926924</v>
+        <v>2327058363.834154</v>
       </c>
       <c r="D182" t="n">
         <v>0.99</v>
@@ -2992,7 +2992,7 @@
         <v>6.395010226695755</v>
       </c>
       <c r="C183" t="n">
-        <v>2746194971.10202</v>
+        <v>3796955976.881616</v>
       </c>
       <c r="D183" t="n">
         <v>0.99</v>
@@ -3006,7 +3006,7 @@
         <v>7.669987436048284</v>
       </c>
       <c r="C184" t="n">
-        <v>1150407595.305242</v>
+        <v>2520326076.244194</v>
       </c>
       <c r="D184" t="n">
         <v>0.999</v>
@@ -3020,7 +3020,7 @@
         <v>9.139767836871766</v>
       </c>
       <c r="C185" t="n">
-        <v>1787355073.536524</v>
+        <v>3029884058.829219</v>
       </c>
       <c r="D185" t="n">
         <v>0.99</v>
@@ -3034,7 +3034,7 @@
         <v>9.260622974164672</v>
       </c>
       <c r="C186" t="n">
-        <v>2661820641.910182</v>
+        <v>3729456513.528146</v>
       </c>
       <c r="D186" t="n">
         <v>0.9</v>
@@ -3048,7 +3048,7 @@
         <v>6.433918493932298</v>
       </c>
       <c r="C187" t="n">
-        <v>2452762389.815001</v>
+        <v>3562209911.852001</v>
       </c>
       <c r="D187" t="n">
         <v>0.9999</v>
@@ -3062,7 +3062,7 @@
         <v>5.901664337780066</v>
       </c>
       <c r="C188" t="n">
-        <v>1505640399.581657</v>
+        <v>2804512319.665326</v>
       </c>
       <c r="D188" t="n">
         <v>0.99</v>
@@ -3076,7 +3076,7 @@
         <v>6.332109053797483</v>
       </c>
       <c r="C189" t="n">
-        <v>2613536225.627382</v>
+        <v>3690828980.501906</v>
       </c>
       <c r="D189" t="n">
         <v>0.9999</v>
@@ -3090,7 +3090,7 @@
         <v>9.458739391938826</v>
       </c>
       <c r="C190" t="n">
-        <v>540928221.0816225</v>
+        <v>2032742576.865298</v>
       </c>
       <c r="D190" t="n">
         <v>0.9</v>
@@ -3104,7 +3104,7 @@
         <v>8.51090461703539</v>
       </c>
       <c r="C191" t="n">
-        <v>2726574560.935286</v>
+        <v>3781259648.748229</v>
       </c>
       <c r="D191" t="n">
         <v>0.999</v>
@@ -3118,7 +3118,7 @@
         <v>5.420588284112573</v>
       </c>
       <c r="C192" t="n">
-        <v>621369893.092082</v>
+        <v>2097095914.473666</v>
       </c>
       <c r="D192" t="n">
         <v>0.9</v>
@@ -3132,7 +3132,7 @@
         <v>9.221643022095694</v>
       </c>
       <c r="C193" t="n">
-        <v>890822328.4409579</v>
+        <v>2312657862.752766</v>
       </c>
       <c r="D193" t="n">
         <v>0.99</v>
@@ -3146,7 +3146,7 @@
         <v>5.924044910088338</v>
       </c>
       <c r="C194" t="n">
-        <v>2593156155.67132</v>
+        <v>3674524924.537056</v>
       </c>
       <c r="D194" t="n">
         <v>0.9999</v>
@@ -3160,7 +3160,7 @@
         <v>8.986205487409912</v>
       </c>
       <c r="C195" t="n">
-        <v>2146765976.473729</v>
+        <v>3317412781.178983</v>
       </c>
       <c r="D195" t="n">
         <v>0.9</v>
@@ -3174,7 +3174,7 @@
         <v>5.595296319952236</v>
       </c>
       <c r="C196" t="n">
-        <v>1101003935.702557</v>
+        <v>2480803148.562046</v>
       </c>
       <c r="D196" t="n">
         <v>0.999</v>
@@ -3188,7 +3188,7 @@
         <v>7.415384247120892</v>
       </c>
       <c r="C197" t="n">
-        <v>811938994.0693042</v>
+        <v>2249551195.255444</v>
       </c>
       <c r="D197" t="n">
         <v>0.9</v>
@@ -3202,7 +3202,7 @@
         <v>9.095586272500798</v>
       </c>
       <c r="C198" t="n">
-        <v>1353553313.811045</v>
+        <v>2682842651.048836</v>
       </c>
       <c r="D198" t="n">
         <v>0.9</v>
@@ -3216,7 +3216,7 @@
         <v>5.597276903971256</v>
       </c>
       <c r="C199" t="n">
-        <v>2359451989.567934</v>
+        <v>3487561591.654347</v>
       </c>
       <c r="D199" t="n">
         <v>0.9</v>
@@ -3230,7 +3230,7 @@
         <v>6.25204789135987</v>
       </c>
       <c r="C200" t="n">
-        <v>1140121086.273333</v>
+        <v>2512096869.018666</v>
       </c>
       <c r="D200" t="n">
         <v>0.9</v>
@@ -3244,7 +3244,7 @@
         <v>8.628164587703029</v>
       </c>
       <c r="C201" t="n">
-        <v>2538630133.670936</v>
+        <v>3630904106.936749</v>
       </c>
       <c r="D201" t="n">
         <v>0.999</v>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +452,11 @@
           <t>Reliability_Requirement</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -463,6 +471,9 @@
       <c r="D2" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>1.719694235101399</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -475,7 +486,10 @@
         <v>3615434722.997388</v>
       </c>
       <c r="D3" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2.103070748639826</v>
       </c>
     </row>
     <row r="4">
@@ -491,6 +505,9 @@
       <c r="D4" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>2.066076611076461</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -503,7 +520,10 @@
         <v>3221652678.905345</v>
       </c>
       <c r="D5" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1.864840898232489</v>
       </c>
     </row>
     <row r="6">
@@ -519,6 +539,9 @@
       <c r="D6" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>1.857273883847675</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -531,7 +554,10 @@
         <v>3786745981.1374</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2.147910769241209</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +571,10 @@
         <v>2499438637.785756</v>
       </c>
       <c r="D8" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.634314941012166</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +588,10 @@
         <v>2943268450.966835</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1.718257775931188</v>
       </c>
     </row>
     <row r="10">
@@ -575,6 +607,9 @@
       <c r="D10" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>1.512285654411353</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -587,7 +622,10 @@
         <v>3614211371.093409</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1.823646807345262</v>
       </c>
     </row>
     <row r="12">
@@ -603,6 +641,9 @@
       <c r="D12" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>1.738202911077727</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -615,7 +656,10 @@
         <v>2512625659.984993</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1.675001363896212</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +673,10 @@
         <v>2113145785.68241</v>
       </c>
       <c r="D14" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1.22967806569779</v>
       </c>
     </row>
     <row r="15">
@@ -645,6 +692,9 @@
       <c r="D15" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>1.332178001947635</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -657,7 +707,10 @@
         <v>3253200261.046153</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1.989511073654613</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +724,10 @@
         <v>2035734367.391731</v>
       </c>
       <c r="D17" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1.274682267944549</v>
       </c>
     </row>
     <row r="18">
@@ -687,6 +743,9 @@
       <c r="D18" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>1.862003118176583</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -699,7 +758,10 @@
         <v>3944878070.402884</v>
       </c>
       <c r="D19" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1.970881325016217</v>
       </c>
     </row>
     <row r="20">
@@ -713,7 +775,10 @@
         <v>2756814765.212242</v>
       </c>
       <c r="D20" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1.590541130959746</v>
       </c>
     </row>
     <row r="21">
@@ -729,6 +794,9 @@
       <c r="D21" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>2.140301332293814</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -743,6 +811,9 @@
       <c r="D22" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>1.695460727095932</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -755,7 +826,10 @@
         <v>2379578199.105142</v>
       </c>
       <c r="D23" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1.370998844757819</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +843,10 @@
         <v>2475034639.987186</v>
       </c>
       <c r="D24" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1.571033915180994</v>
       </c>
     </row>
     <row r="25">
@@ -783,7 +860,10 @@
         <v>3320683924.82158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1.655003308239766</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +877,10 @@
         <v>3789278080.928905</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2.154511438074283</v>
       </c>
     </row>
     <row r="27">
@@ -811,7 +894,10 @@
         <v>2809540495.200351</v>
       </c>
       <c r="D27" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1.566016176970736</v>
       </c>
     </row>
     <row r="28">
@@ -827,6 +913,9 @@
       <c r="D28" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>1.587996509894193</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -839,7 +928,10 @@
         <v>3883961950.771987</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2.111341816933927</v>
       </c>
     </row>
     <row r="30">
@@ -855,6 +947,9 @@
       <c r="D30" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>1.511388355924895</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -867,7 +962,10 @@
         <v>3849467486.215332</v>
       </c>
       <c r="D31" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2.160840366858225</v>
       </c>
     </row>
     <row r="32">
@@ -881,7 +979,10 @@
         <v>2572845237.661914</v>
       </c>
       <c r="D32" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1.439480782917656</v>
       </c>
     </row>
     <row r="33">
@@ -897,6 +998,9 @@
       <c r="D33" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>1.899990441963975</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -909,7 +1013,10 @@
         <v>2137930559.569284</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1.411385117263159</v>
       </c>
     </row>
     <row r="35">
@@ -923,7 +1030,10 @@
         <v>3343164810.637867</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1.865577410347485</v>
       </c>
     </row>
     <row r="36">
@@ -939,6 +1049,9 @@
       <c r="D36" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>1.524224658512922</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -951,7 +1064,10 @@
         <v>2943833942.691082</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1.757027068393899</v>
       </c>
     </row>
     <row r="38">
@@ -965,7 +1081,10 @@
         <v>2710788763.434069</v>
       </c>
       <c r="D38" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1.748954426697872</v>
       </c>
     </row>
     <row r="39">
@@ -979,7 +1098,10 @@
         <v>2274241911.740644</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1.311702126598665</v>
       </c>
     </row>
     <row r="40">
@@ -993,7 +1115,10 @@
         <v>2830705215.863926</v>
       </c>
       <c r="D40" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1.82775480308597</v>
       </c>
     </row>
     <row r="41">
@@ -1007,7 +1132,10 @@
         <v>2805627574.532079</v>
       </c>
       <c r="D41" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1.710747679972703</v>
       </c>
     </row>
     <row r="42">
@@ -1021,7 +1149,10 @@
         <v>2909373830.98064</v>
       </c>
       <c r="D42" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1.547752310732462</v>
       </c>
     </row>
     <row r="43">
@@ -1035,7 +1166,10 @@
         <v>3727776757.362188</v>
       </c>
       <c r="D43" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2.175018830908277</v>
       </c>
     </row>
     <row r="44">
@@ -1049,7 +1183,10 @@
         <v>2595320155.771381</v>
       </c>
       <c r="D44" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1.500634439867138</v>
       </c>
     </row>
     <row r="45">
@@ -1063,7 +1200,10 @@
         <v>2229907194.491547</v>
       </c>
       <c r="D45" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1.360350519348226</v>
       </c>
     </row>
     <row r="46">
@@ -1077,7 +1217,10 @@
         <v>2781107413.213808</v>
       </c>
       <c r="D46" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1.820825965984033</v>
       </c>
     </row>
     <row r="47">
@@ -1091,7 +1234,10 @@
         <v>3871586029.915329</v>
       </c>
       <c r="D47" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1.961774718575748</v>
       </c>
     </row>
     <row r="48">
@@ -1105,7 +1251,10 @@
         <v>2844478785.842661</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1.513637642760613</v>
       </c>
     </row>
     <row r="49">
@@ -1119,7 +1268,10 @@
         <v>2507596881.018478</v>
       </c>
       <c r="D49" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1.44681992967971</v>
       </c>
     </row>
     <row r="50">
@@ -1133,7 +1285,10 @@
         <v>3124406713.111102</v>
       </c>
       <c r="D50" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1.593960088764917</v>
       </c>
     </row>
     <row r="51">
@@ -1147,7 +1302,10 @@
         <v>3594487309.937557</v>
       </c>
       <c r="D51" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1.854498841039235</v>
       </c>
     </row>
     <row r="52">
@@ -1161,7 +1319,10 @@
         <v>3510304661.60333</v>
       </c>
       <c r="D52" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>2.1018171045938</v>
       </c>
     </row>
     <row r="53">
@@ -1175,7 +1336,10 @@
         <v>3554514302.615196</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1.883580292177504</v>
       </c>
     </row>
     <row r="54">
@@ -1189,7 +1353,10 @@
         <v>3875271685.39693</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>2.03889743542455</v>
       </c>
     </row>
     <row r="55">
@@ -1203,7 +1370,10 @@
         <v>3802214158.329295</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1.831632936029274</v>
       </c>
     </row>
     <row r="56">
@@ -1217,7 +1387,10 @@
         <v>2541560741.546412</v>
       </c>
       <c r="D56" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1.570875995675674</v>
       </c>
     </row>
     <row r="57">
@@ -1231,7 +1404,10 @@
         <v>3604878363.624515</v>
       </c>
       <c r="D57" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>2.000996063099563</v>
       </c>
     </row>
     <row r="58">
@@ -1245,7 +1421,10 @@
         <v>2436981573.833116</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1.439631861791494</v>
       </c>
     </row>
     <row r="59">
@@ -1259,7 +1438,10 @@
         <v>2980335627.828416</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1.782733673506268</v>
       </c>
     </row>
     <row r="60">
@@ -1273,7 +1455,10 @@
         <v>2851571343.884669</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1.739310100917165</v>
       </c>
     </row>
     <row r="61">
@@ -1287,7 +1472,10 @@
         <v>3431132069.789394</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1.904414560838833</v>
       </c>
     </row>
     <row r="62">
@@ -1301,7 +1489,10 @@
         <v>2153053396.488575</v>
       </c>
       <c r="D62" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1.38532373962597</v>
       </c>
     </row>
     <row r="63">
@@ -1317,6 +1508,9 @@
       <c r="D63" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>1.53338990482089</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1329,7 +1523,10 @@
         <v>3130182437.904866</v>
       </c>
       <c r="D64" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1.877421206055043</v>
       </c>
     </row>
     <row r="65">
@@ -1345,6 +1542,9 @@
       <c r="D65" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E65" s="2" t="n">
+        <v>2.231579613852943</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1359,6 +1559,9 @@
       <c r="D66" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E66" s="2" t="n">
+        <v>1.948383908574805</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1373,6 +1576,9 @@
       <c r="D67" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E67" s="2" t="n">
+        <v>1.523676813073203</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1385,7 +1591,10 @@
         <v>3335371620.389873</v>
       </c>
       <c r="D68" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1.915280984070574</v>
       </c>
     </row>
     <row r="69">
@@ -1401,6 +1610,9 @@
       <c r="D69" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E69" s="2" t="n">
+        <v>1.513845785614459</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1413,7 +1625,10 @@
         <v>3824515162.420707</v>
       </c>
       <c r="D70" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>2.130850914236655</v>
       </c>
     </row>
     <row r="71">
@@ -1427,7 +1642,10 @@
         <v>2909476483.135699</v>
       </c>
       <c r="D71" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>1.791182342261058</v>
       </c>
     </row>
     <row r="72">
@@ -1441,7 +1659,10 @@
         <v>2241819552.432022</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>1.274980209511935</v>
       </c>
     </row>
     <row r="73">
@@ -1457,6 +1678,9 @@
       <c r="D73" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E73" s="2" t="n">
+        <v>1.639935614684337</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1469,7 +1693,10 @@
         <v>3386717624.178626</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>1.919642695117606</v>
       </c>
     </row>
     <row r="75">
@@ -1485,6 +1712,9 @@
       <c r="D75" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E75" s="2" t="n">
+        <v>1.292099298423033</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1497,7 +1727,10 @@
         <v>3165213918.953576</v>
       </c>
       <c r="D76" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>1.77693114965838</v>
       </c>
     </row>
     <row r="77">
@@ -1511,7 +1744,10 @@
         <v>3503060116.091953</v>
       </c>
       <c r="D77" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>1.791706911855619</v>
       </c>
     </row>
     <row r="78">
@@ -1525,7 +1761,10 @@
         <v>3091240503.911071</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>1.657460481077803</v>
       </c>
     </row>
     <row r="79">
@@ -1541,6 +1780,9 @@
       <c r="D79" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E79" s="2" t="n">
+        <v>1.364337762302086</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1555,6 +1797,9 @@
       <c r="D80" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>2.018546018086391</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1567,7 +1812,10 @@
         <v>3803942783.409199</v>
       </c>
       <c r="D81" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>1.83710522565812</v>
       </c>
     </row>
     <row r="82">
@@ -1581,7 +1829,10 @@
         <v>2103803148.624906</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>1.335086962852651</v>
       </c>
     </row>
     <row r="83">
@@ -1595,7 +1846,10 @@
         <v>3265033710.779034</v>
       </c>
       <c r="D83" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>1.623895630345506</v>
       </c>
     </row>
     <row r="84">
@@ -1609,7 +1863,10 @@
         <v>2287977748.73364</v>
       </c>
       <c r="D84" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>1.442657960948069</v>
       </c>
     </row>
     <row r="85">
@@ -1625,6 +1882,9 @@
       <c r="D85" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E85" s="2" t="n">
+        <v>1.88649520991912</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1637,7 +1897,10 @@
         <v>2183793613.868398</v>
       </c>
       <c r="D86" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>1.333571961680017</v>
       </c>
     </row>
     <row r="87">
@@ -1651,7 +1914,10 @@
         <v>3943469311.840803</v>
       </c>
       <c r="D87" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>1.942625488401806</v>
       </c>
     </row>
     <row r="88">
@@ -1665,7 +1931,10 @@
         <v>3368310877.429912</v>
       </c>
       <c r="D88" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>1.830488786913041</v>
       </c>
     </row>
     <row r="89">
@@ -1679,7 +1948,10 @@
         <v>3895399651.296702</v>
       </c>
       <c r="D89" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>2.192184183393362</v>
       </c>
     </row>
     <row r="90">
@@ -1693,7 +1965,10 @@
         <v>3039261647.747734</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>1.56714263314985</v>
       </c>
     </row>
     <row r="91">
@@ -1707,7 +1982,10 @@
         <v>3057513183.274941</v>
       </c>
       <c r="D91" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>1.667468353797976</v>
       </c>
     </row>
     <row r="92">
@@ -1721,7 +1999,10 @@
         <v>3711030187.769846</v>
       </c>
       <c r="D92" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>1.957470338155397</v>
       </c>
     </row>
     <row r="93">
@@ -1735,7 +2016,10 @@
         <v>2721945784.562086</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>1.564348318529679</v>
       </c>
     </row>
     <row r="94">
@@ -1751,6 +2035,9 @@
       <c r="D94" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E94" s="2" t="n">
+        <v>1.876106702013563</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1763,7 +2050,10 @@
         <v>2619582340.477922</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>1.749252810105866</v>
       </c>
     </row>
     <row r="96">
@@ -1777,7 +2067,10 @@
         <v>3264635626.331596</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>1.824693371543763</v>
       </c>
     </row>
     <row r="97">
@@ -1791,7 +2084,10 @@
         <v>2597651623.571331</v>
       </c>
       <c r="D97" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>1.516906684516891</v>
       </c>
     </row>
     <row r="98">
@@ -1807,6 +2103,9 @@
       <c r="D98" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E98" s="2" t="n">
+        <v>1.60885460484537</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1819,7 +2118,10 @@
         <v>3313890175.43737</v>
       </c>
       <c r="D99" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>1.746134444904799</v>
       </c>
     </row>
     <row r="100">
@@ -1833,7 +2135,10 @@
         <v>2917070134.366358</v>
       </c>
       <c r="D100" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1.783768655377179</v>
       </c>
     </row>
     <row r="101">
@@ -1847,7 +2152,10 @@
         <v>3295654151.10424</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>2.003025111112419</v>
       </c>
     </row>
     <row r="102">
@@ -1861,7 +2169,10 @@
         <v>3020248282.319529</v>
       </c>
       <c r="D102" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1.855923438117526</v>
       </c>
     </row>
     <row r="103">
@@ -1877,6 +2188,9 @@
       <c r="D103" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E103" s="2" t="n">
+        <v>1.469233851680327</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1889,7 +2203,10 @@
         <v>3234449309.212807</v>
       </c>
       <c r="D104" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1.86965345030952</v>
       </c>
     </row>
     <row r="105">
@@ -1903,7 +2220,10 @@
         <v>2049915326.81772</v>
       </c>
       <c r="D105" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>1.497952796883882</v>
       </c>
     </row>
     <row r="106">
@@ -1919,6 +2239,9 @@
       <c r="D106" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E106" s="2" t="n">
+        <v>1.617057688532235</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1931,7 +2254,10 @@
         <v>2321195921.23542</v>
       </c>
       <c r="D107" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>1.312190334234292</v>
       </c>
     </row>
     <row r="108">
@@ -1947,6 +2273,9 @@
       <c r="D108" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E108" s="2" t="n">
+        <v>1.454000307939721</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1959,7 +2288,10 @@
         <v>3071587269.52985</v>
       </c>
       <c r="D109" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1.724779271446546</v>
       </c>
     </row>
     <row r="110">
@@ -1973,7 +2305,10 @@
         <v>3457575187.214504</v>
       </c>
       <c r="D110" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>2.010614224627431</v>
       </c>
     </row>
     <row r="111">
@@ -1989,6 +2324,9 @@
       <c r="D111" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E111" s="2" t="n">
+        <v>2.025828397368303</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2003,6 +2341,9 @@
       <c r="D112" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E112" s="2" t="n">
+        <v>1.439951006932654</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2017,6 +2358,9 @@
       <c r="D113" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E113" s="2" t="n">
+        <v>1.629711622821386</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2031,6 +2375,9 @@
       <c r="D114" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E114" s="2" t="n">
+        <v>1.6430258341687</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2043,7 +2390,10 @@
         <v>2623330911.055835</v>
       </c>
       <c r="D115" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>1.624680176092834</v>
       </c>
     </row>
     <row r="116">
@@ -2059,6 +2409,9 @@
       <c r="D116" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E116" s="2" t="n">
+        <v>1.39864687530184</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2071,7 +2424,10 @@
         <v>3809330131.554121</v>
       </c>
       <c r="D117" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>1.991184513787618</v>
       </c>
     </row>
     <row r="118">
@@ -2085,7 +2441,10 @@
         <v>3525043034.392427</v>
       </c>
       <c r="D118" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>2.063194095597995</v>
       </c>
     </row>
     <row r="119">
@@ -2099,7 +2458,10 @@
         <v>2087635256.409148</v>
       </c>
       <c r="D119" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>1.289451848794991</v>
       </c>
     </row>
     <row r="120">
@@ -2113,7 +2475,10 @@
         <v>3302044412.483964</v>
       </c>
       <c r="D120" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>1.827688663778707</v>
       </c>
     </row>
     <row r="121">
@@ -2127,7 +2492,10 @@
         <v>2279830186.2379</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>1.439046088216645</v>
       </c>
     </row>
     <row r="122">
@@ -2141,7 +2509,10 @@
         <v>2521993070.654481</v>
       </c>
       <c r="D122" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>1.675159699768785</v>
       </c>
     </row>
     <row r="123">
@@ -2155,7 +2526,10 @@
         <v>3185270236.053452</v>
       </c>
       <c r="D123" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>1.650206936003957</v>
       </c>
     </row>
     <row r="124">
@@ -2169,7 +2543,10 @@
         <v>2605453681.324949</v>
       </c>
       <c r="D124" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>1.377634082975438</v>
       </c>
     </row>
     <row r="125">
@@ -2183,7 +2560,10 @@
         <v>2229294466.610596</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>1.587678028574369</v>
       </c>
     </row>
     <row r="126">
@@ -2197,7 +2577,10 @@
         <v>3235001798.642087</v>
       </c>
       <c r="D126" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>1.657931568487654</v>
       </c>
     </row>
     <row r="127">
@@ -2213,6 +2596,9 @@
       <c r="D127" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E127" s="2" t="n">
+        <v>1.783655981979978</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2225,7 +2611,10 @@
         <v>2588293930.618646</v>
       </c>
       <c r="D128" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>1.405229512519217</v>
       </c>
     </row>
     <row r="129">
@@ -2239,7 +2628,10 @@
         <v>2524084930.846177</v>
       </c>
       <c r="D129" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>1.7062985490375</v>
       </c>
     </row>
     <row r="130">
@@ -2253,7 +2645,10 @@
         <v>2998736000.999851</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>1.551790344590768</v>
       </c>
     </row>
     <row r="131">
@@ -2267,7 +2662,10 @@
         <v>3022939108.503745</v>
       </c>
       <c r="D131" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>1.795426910533304</v>
       </c>
     </row>
     <row r="132">
@@ -2281,7 +2679,10 @@
         <v>3685150274.072979</v>
       </c>
       <c r="D132" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>1.961183862436965</v>
       </c>
     </row>
     <row r="133">
@@ -2297,6 +2698,9 @@
       <c r="D133" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E133" s="2" t="n">
+        <v>1.774747755833276</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2309,7 +2713,10 @@
         <v>3200612586.36801</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>1.96637149708936</v>
       </c>
     </row>
     <row r="135">
@@ -2323,7 +2730,10 @@
         <v>3990741212.238034</v>
       </c>
       <c r="D135" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>2.270670219863999</v>
       </c>
     </row>
     <row r="136">
@@ -2339,6 +2749,9 @@
       <c r="D136" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E136" s="2" t="n">
+        <v>1.623233800318796</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2353,6 +2766,9 @@
       <c r="D137" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E137" s="2" t="n">
+        <v>1.873120851367485</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2367,6 +2783,9 @@
       <c r="D138" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>2.087968645947611</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2379,7 +2798,10 @@
         <v>2634964606.529172</v>
       </c>
       <c r="D139" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>1.643521406777116</v>
       </c>
     </row>
     <row r="140">
@@ -2393,7 +2815,10 @@
         <v>2325390109.876773</v>
       </c>
       <c r="D140" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>1.482972520848495</v>
       </c>
     </row>
     <row r="141">
@@ -2407,7 +2832,10 @@
         <v>3511092775.368326</v>
       </c>
       <c r="D141" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>1.768496808637778</v>
       </c>
     </row>
     <row r="142">
@@ -2421,7 +2849,10 @@
         <v>3516708830.245605</v>
       </c>
       <c r="D142" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>2.067815951956752</v>
       </c>
     </row>
     <row r="143">
@@ -2435,7 +2866,10 @@
         <v>2211024555.724195</v>
       </c>
       <c r="D143" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>1.574758704067134</v>
       </c>
     </row>
     <row r="144">
@@ -2449,7 +2883,10 @@
         <v>3961749000.019118</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>2.214226279935756</v>
       </c>
     </row>
     <row r="145">
@@ -2463,7 +2900,10 @@
         <v>3787693474.256113</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>2.160231986281822</v>
       </c>
     </row>
     <row r="146">
@@ -2477,7 +2917,10 @@
         <v>2318849594.271571</v>
       </c>
       <c r="D146" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>1.456089764867709</v>
       </c>
     </row>
     <row r="147">
@@ -2493,6 +2936,9 @@
       <c r="D147" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E147" s="2" t="n">
+        <v>1.800742694591331</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2507,6 +2953,9 @@
       <c r="D148" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E148" s="2" t="n">
+        <v>1.505928827258459</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2519,7 +2968,10 @@
         <v>2935624434.231703</v>
       </c>
       <c r="D149" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>1.511128717635713</v>
       </c>
     </row>
     <row r="150">
@@ -2533,7 +2985,10 @@
         <v>2272590775.494435</v>
       </c>
       <c r="D150" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>1.300881160873738</v>
       </c>
     </row>
     <row r="151">
@@ -2547,7 +3002,10 @@
         <v>2193525407.522423</v>
       </c>
       <c r="D151" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>1.509051316202543</v>
       </c>
     </row>
     <row r="152">
@@ -2561,7 +3019,10 @@
         <v>3489490288.600853</v>
       </c>
       <c r="D152" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>1.727688945247604</v>
       </c>
     </row>
     <row r="153">
@@ -2575,7 +3036,10 @@
         <v>3726087597.998542</v>
       </c>
       <c r="D153" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>2.179189594183646</v>
       </c>
     </row>
     <row r="154">
@@ -2589,7 +3053,10 @@
         <v>2112362513.782524</v>
       </c>
       <c r="D154" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>1.346370498601809</v>
       </c>
     </row>
     <row r="155">
@@ -2603,7 +3070,10 @@
         <v>3907450414.778891</v>
       </c>
       <c r="D155" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>2.222941248427873</v>
       </c>
     </row>
     <row r="156">
@@ -2619,6 +3089,9 @@
       <c r="D156" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E156" s="2" t="n">
+        <v>2.062405258903069</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2633,6 +3106,9 @@
       <c r="D157" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E157" s="2" t="n">
+        <v>1.524976891795327</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2645,7 +3121,10 @@
         <v>3909363009.374259</v>
       </c>
       <c r="D158" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>2.071090872713654</v>
       </c>
     </row>
     <row r="159">
@@ -2659,7 +3138,10 @@
         <v>2748041799.16139</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>1.443860959912037</v>
       </c>
     </row>
     <row r="160">
@@ -2673,7 +3155,10 @@
         <v>3175239088.345665</v>
       </c>
       <c r="D160" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>1.746865948649007</v>
       </c>
     </row>
     <row r="161">
@@ -2687,7 +3172,10 @@
         <v>3527518347.875824</v>
       </c>
       <c r="D161" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>2.008790657092171</v>
       </c>
     </row>
     <row r="162">
@@ -2701,7 +3189,10 @@
         <v>2867211109.095093</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>1.482074615936299</v>
       </c>
     </row>
     <row r="163">
@@ -2717,6 +3208,9 @@
       <c r="D163" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>1.844684324495937</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2729,7 +3223,10 @@
         <v>2257174626.206392</v>
       </c>
       <c r="D164" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>1.509109324532123</v>
       </c>
     </row>
     <row r="165">
@@ -2743,7 +3240,10 @@
         <v>3507510245.45727</v>
       </c>
       <c r="D165" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>2.015489252767078</v>
       </c>
     </row>
     <row r="166">
@@ -2759,6 +3259,9 @@
       <c r="D166" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E166" s="2" t="n">
+        <v>1.492559434431366</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2773,6 +3276,9 @@
       <c r="D167" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E167" s="2" t="n">
+        <v>1.736132023481587</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2785,7 +3291,10 @@
         <v>3387143829.009998</v>
       </c>
       <c r="D168" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>1.738664122502986</v>
       </c>
     </row>
     <row r="169">
@@ -2801,6 +3310,9 @@
       <c r="D169" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E169" s="2" t="n">
+        <v>1.24626112400892</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2813,7 +3325,10 @@
         <v>2247491917.743874</v>
       </c>
       <c r="D170" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>1.534029765828179</v>
       </c>
     </row>
     <row r="171">
@@ -2829,6 +3344,9 @@
       <c r="D171" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E171" s="2" t="n">
+        <v>1.541567898792439</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2841,7 +3359,10 @@
         <v>2087114454.886926</v>
       </c>
       <c r="D172" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>1.571457343368644</v>
       </c>
     </row>
     <row r="173">
@@ -2855,7 +3376,10 @@
         <v>2289168546.33081</v>
       </c>
       <c r="D173" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>1.260163731644075</v>
       </c>
     </row>
     <row r="174">
@@ -2869,7 +3393,10 @@
         <v>3235851930.539863</v>
       </c>
       <c r="D174" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>1.936615806031017</v>
       </c>
     </row>
     <row r="175">
@@ -2883,7 +3410,10 @@
         <v>3906264047.239286</v>
       </c>
       <c r="D175" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>1.956985001390927</v>
       </c>
     </row>
     <row r="176">
@@ -2897,7 +3427,10 @@
         <v>3392982241.940281</v>
       </c>
       <c r="D176" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>1.758507820731243</v>
       </c>
     </row>
     <row r="177">
@@ -2911,7 +3444,10 @@
         <v>3322393108.150819</v>
       </c>
       <c r="D177" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>1.735146324626699</v>
       </c>
     </row>
     <row r="178">
@@ -2925,7 +3461,10 @@
         <v>2934318080.714441</v>
       </c>
       <c r="D178" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>1.681804513831122</v>
       </c>
     </row>
     <row r="179">
@@ -2939,7 +3478,10 @@
         <v>3931927124.527704</v>
       </c>
       <c r="D179" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>2.236332760276435</v>
       </c>
     </row>
     <row r="180">
@@ -2953,7 +3495,10 @@
         <v>3983440776.307714</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>2.1230371575085</v>
       </c>
     </row>
     <row r="181">
@@ -2967,7 +3512,10 @@
         <v>3364699744.205702</v>
       </c>
       <c r="D181" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>1.85189403804817</v>
       </c>
     </row>
     <row r="182">
@@ -2981,7 +3529,10 @@
         <v>2327058363.834154</v>
       </c>
       <c r="D182" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>1.288467261021343</v>
       </c>
     </row>
     <row r="183">
@@ -2995,7 +3546,10 @@
         <v>3796955976.881616</v>
       </c>
       <c r="D183" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>1.929919554718896</v>
       </c>
     </row>
     <row r="184">
@@ -3009,7 +3563,10 @@
         <v>2520326076.244194</v>
       </c>
       <c r="D184" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>1.550855033491255</v>
       </c>
     </row>
     <row r="185">
@@ -3023,7 +3580,10 @@
         <v>3029884058.829219</v>
       </c>
       <c r="D185" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>1.858030301873295</v>
       </c>
     </row>
     <row r="186">
@@ -3037,7 +3597,10 @@
         <v>3729456513.528146</v>
       </c>
       <c r="D186" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>2.130310949560251</v>
       </c>
     </row>
     <row r="187">
@@ -3053,6 +3616,9 @@
       <c r="D187" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E187" s="2" t="n">
+        <v>1.844813794992312</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3065,7 +3631,10 @@
         <v>2804512319.665326</v>
       </c>
       <c r="D188" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>1.518292529878054</v>
       </c>
     </row>
     <row r="189">
@@ -3081,6 +3650,9 @@
       <c r="D189" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E189" s="2" t="n">
+        <v>1.885102995710041</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3093,7 +3665,10 @@
         <v>2032742576.865298</v>
       </c>
       <c r="D190" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>1.508630666789234</v>
       </c>
     </row>
     <row r="191">
@@ -3107,7 +3682,10 @@
         <v>3781259648.748229</v>
       </c>
       <c r="D191" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>2.090707722705679</v>
       </c>
     </row>
     <row r="192">
@@ -3121,7 +3699,10 @@
         <v>2097095914.473666</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>1.214688579361104</v>
       </c>
     </row>
     <row r="193">
@@ -3135,7 +3716,10 @@
         <v>2312657862.752766</v>
       </c>
       <c r="D193" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>1.595089370991925</v>
       </c>
     </row>
     <row r="194">
@@ -3151,6 +3735,9 @@
       <c r="D194" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E194" s="2" t="n">
+        <v>1.846833125702071</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3163,7 +3750,10 @@
         <v>3317412781.178983</v>
       </c>
       <c r="D195" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>1.953929175703897</v>
       </c>
     </row>
     <row r="196">
@@ -3177,7 +3767,10 @@
         <v>2480803148.562046</v>
       </c>
       <c r="D196" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>1.372572331599427</v>
       </c>
     </row>
     <row r="197">
@@ -3191,7 +3784,10 @@
         <v>2249551195.255444</v>
       </c>
       <c r="D197" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>1.429094878266814</v>
       </c>
     </row>
     <row r="198">
@@ -3205,7 +3801,10 @@
         <v>2682842651.048836</v>
       </c>
       <c r="D198" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>1.724200745539024</v>
       </c>
     </row>
     <row r="199">
@@ -3219,7 +3818,10 @@
         <v>3487561591.654347</v>
       </c>
       <c r="D199" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>1.750867739103717</v>
       </c>
     </row>
     <row r="200">
@@ -3233,7 +3835,10 @@
         <v>2512096869.018666</v>
       </c>
       <c r="D200" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>1.43606317215953</v>
       </c>
     </row>
     <row r="201">
@@ -3247,7 +3852,10 @@
         <v>3630904106.936749</v>
       </c>
       <c r="D201" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>2.043471428771575</v>
       </c>
     </row>
   </sheetData>

--- a/data/task_parameters.xlsx
+++ b/data/task_parameters.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6.611899903840291</v>
+        <v>6.655925343491216</v>
       </c>
       <c r="C2" t="n">
-        <v>3191762472.12077</v>
+        <v>6501722964.165258</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999</v>
+        <v>0.9928249566385746</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>9.458478886863501</v>
+        <v>7.659390293513695</v>
       </c>
       <c r="C3" t="n">
-        <v>3615434722.997388</v>
+        <v>5226678663.731231</v>
       </c>
       <c r="D3" t="n">
-        <v>0.99</v>
+        <v>0.9989790007752629</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9.081351957255169</v>
+        <v>7.853021839964351</v>
       </c>
       <c r="C4" t="n">
-        <v>3596038536.138977</v>
+        <v>6381244358.304907</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999</v>
+        <v>0.9979550061537558</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8.311887795807797</v>
+        <v>6.820307609513801</v>
       </c>
       <c r="C5" t="n">
-        <v>3221652678.905345</v>
+        <v>4445180739.027077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.999</v>
+        <v>0.9964373723465741</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9.370486220610481</v>
+        <v>7.026300491678383</v>
       </c>
       <c r="C6" t="n">
-        <v>2979480265.576702</v>
+        <v>5837614965.648225</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999</v>
+        <v>0.9966263345265391</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9.210885635292149</v>
+        <v>9.18689214544024</v>
       </c>
       <c r="C7" t="n">
-        <v>3786745981.1374</v>
+        <v>6481757718.239294</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.9985881933225821</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8.829022398812615</v>
+        <v>6.59198641498056</v>
       </c>
       <c r="C8" t="n">
-        <v>2499438637.785756</v>
+        <v>5833010084.120989</v>
       </c>
       <c r="D8" t="n">
-        <v>0.999</v>
+        <v>0.9935735274838907</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7.778460822747784</v>
+        <v>7.352678843662808</v>
       </c>
       <c r="C9" t="n">
-        <v>2943268450.966835</v>
+        <v>7233530148.876098</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9</v>
+        <v>0.9920116197087268</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>6.283012897856454</v>
+        <v>8.717332455170869</v>
       </c>
       <c r="C10" t="n">
-        <v>2708537165.376525</v>
+        <v>6794882084.52506</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999</v>
+        <v>0.991200722245803</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>5.917285407462558</v>
+        <v>9.435809168722642</v>
       </c>
       <c r="C11" t="n">
-        <v>3614211371.093409</v>
+        <v>7556133034.971854</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>0.9918234149128039</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>9.760958695470894</v>
+        <v>5.886770275707483</v>
       </c>
       <c r="C12" t="n">
-        <v>2580569602.336924</v>
+        <v>7204993324.543812</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999</v>
+        <v>0.991750813138576</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>9.282624142385234</v>
+        <v>6.26930931803613</v>
       </c>
       <c r="C13" t="n">
-        <v>2512625659.984993</v>
+        <v>5755505154.158571</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9</v>
+        <v>0.9921220347549815</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>5.534341600131182</v>
+        <v>8.365300614576915</v>
       </c>
       <c r="C14" t="n">
-        <v>2113145785.68241</v>
+        <v>4509899854.995958</v>
       </c>
       <c r="D14" t="n">
-        <v>0.99</v>
+        <v>0.9927625951892665</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>5.428265989060518</v>
+        <v>7.959933239267829</v>
       </c>
       <c r="C15" t="n">
-        <v>2408289509.993055</v>
+        <v>4620157009.414423</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999</v>
+        <v>0.9905606295480879</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>9.744043570503546</v>
+        <v>5.442023124931268</v>
       </c>
       <c r="C16" t="n">
-        <v>3253200261.046153</v>
+        <v>7736487846.972364</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9</v>
+        <v>0.9928065442403886</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>6.474718115843953</v>
+        <v>9.661741823247311</v>
       </c>
       <c r="C17" t="n">
-        <v>2035734367.391731</v>
+        <v>5701003117.382386</v>
       </c>
       <c r="D17" t="n">
-        <v>0.999</v>
+        <v>0.9900671554976838</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>6.054254594439056</v>
+        <v>7.158214610261575</v>
       </c>
       <c r="C18" t="n">
-        <v>3687603885.723213</v>
+        <v>7428133491.615433</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999</v>
+        <v>0.9989408158101367</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>6.209703476792037</v>
+        <v>8.998026612875528</v>
       </c>
       <c r="C19" t="n">
-        <v>3944878070.402884</v>
+        <v>7669691077.981937</v>
       </c>
       <c r="D19" t="n">
-        <v>0.99</v>
+        <v>0.9932234215413097</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7.046210259333273</v>
+        <v>7.982052489105588</v>
       </c>
       <c r="C20" t="n">
-        <v>2756814765.212242</v>
+        <v>4158298989.76042</v>
       </c>
       <c r="D20" t="n">
-        <v>0.999</v>
+        <v>0.9908418065988761</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>8.646376186779616</v>
+        <v>8.404057384697724</v>
       </c>
       <c r="C21" t="n">
-        <v>3884884455.98367</v>
+        <v>4797258632.961954</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999</v>
+        <v>0.9947818546328179</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>9.254310893497342</v>
+        <v>6.057192866852764</v>
       </c>
       <c r="C22" t="n">
-        <v>2573034978.661143</v>
+        <v>7801181510.92433</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999</v>
+        <v>0.9916968923310169</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>6.057953128354083</v>
+        <v>6.112545027033358</v>
       </c>
       <c r="C23" t="n">
-        <v>2379578199.105142</v>
+        <v>6896252136.384801</v>
       </c>
       <c r="D23" t="n">
-        <v>0.999</v>
+        <v>0.9929789454183757</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8.142084699265133</v>
+        <v>7.580944575481382</v>
       </c>
       <c r="C24" t="n">
-        <v>2475034639.987186</v>
+        <v>4911148890.752382</v>
       </c>
       <c r="D24" t="n">
-        <v>0.999</v>
+        <v>0.996984270176938</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>5.176023926144904</v>
+        <v>8.308412011479119</v>
       </c>
       <c r="C25" t="n">
-        <v>3320683924.82158</v>
+        <v>6028084004.471198</v>
       </c>
       <c r="D25" t="n">
-        <v>0.99</v>
+        <v>0.995131533921727</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>9.282602162779529</v>
+        <v>9.439559717342833</v>
       </c>
       <c r="C26" t="n">
-        <v>3789278080.928905</v>
+        <v>7494087392.032297</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.9922220606288988</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>6.483497669505885</v>
+        <v>6.318687753632622</v>
       </c>
       <c r="C27" t="n">
-        <v>2809540495.200351</v>
+        <v>7653059514.6178</v>
       </c>
       <c r="D27" t="n">
-        <v>0.99</v>
+        <v>0.9976867957954301</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>6.907252271893272</v>
+        <v>7.460996240769843</v>
       </c>
       <c r="C28" t="n">
-        <v>2779184430.233824</v>
+        <v>6529621482.126572</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9999</v>
+        <v>0.997769160196133</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>8.283160566707759</v>
+        <v>6.961053367191766</v>
       </c>
       <c r="C29" t="n">
-        <v>3883961950.771987</v>
+        <v>5021558708.120265</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9</v>
+        <v>0.996610302330031</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>5.363459947892352</v>
+        <v>8.259192969505932</v>
       </c>
       <c r="C30" t="n">
-        <v>2899011374.378702</v>
+        <v>5334742921.720383</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9999</v>
+        <v>0.9925101410473854</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>9.075964754853276</v>
+        <v>9.775185112087152</v>
       </c>
       <c r="C31" t="n">
-        <v>3849467486.215332</v>
+        <v>6127037537.587183</v>
       </c>
       <c r="D31" t="n">
-        <v>0.99</v>
+        <v>0.9943765017819367</v>
       </c>
     </row>
     <row r="32">
@@ -875,13 +875,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>6.005788933465668</v>
+        <v>7.960774945900718</v>
       </c>
       <c r="C32" t="n">
-        <v>2572845237.661914</v>
+        <v>6675789963.01602</v>
       </c>
       <c r="D32" t="n">
-        <v>0.999</v>
+        <v>0.9956531159010938</v>
       </c>
     </row>
     <row r="33">
@@ -889,13 +889,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>6.595330091549068</v>
+        <v>9.849698646595646</v>
       </c>
       <c r="C33" t="n">
-        <v>3675258447.43484</v>
+        <v>4450116495.777467</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9999</v>
+        <v>0.9952421764044437</v>
       </c>
     </row>
     <row r="34">
@@ -903,13 +903,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7.722771731304446</v>
+        <v>6.656423561707197</v>
       </c>
       <c r="C34" t="n">
-        <v>2137930559.569284</v>
+        <v>7294102388.706654</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9</v>
+        <v>0.9939936749355369</v>
       </c>
     </row>
     <row r="35">
@@ -917,13 +917,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7.741879053497387</v>
+        <v>9.152986249752455</v>
       </c>
       <c r="C35" t="n">
-        <v>3343164810.637867</v>
+        <v>5011264298.622829</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9</v>
+        <v>0.9902093983237328</v>
       </c>
     </row>
     <row r="36">
@@ -931,13 +931,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>6.032941759473034</v>
+        <v>9.673911731167752</v>
       </c>
       <c r="C36" t="n">
-        <v>2792772445.763815</v>
+        <v>7595782631.344858</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9999</v>
+        <v>0.9901920376500236</v>
       </c>
     </row>
     <row r="37">
@@ -945,13 +945,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>8.267904618831091</v>
+        <v>5.682376712536382</v>
       </c>
       <c r="C37" t="n">
-        <v>2943833942.691082</v>
+        <v>5923409835.736013</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9</v>
+        <v>0.9921029079253709</v>
       </c>
     </row>
     <row r="38">
@@ -959,13 +959,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>9.276566808385919</v>
+        <v>7.637416283010425</v>
       </c>
       <c r="C38" t="n">
-        <v>2710788763.434069</v>
+        <v>6886701189.137685</v>
       </c>
       <c r="D38" t="n">
-        <v>0.99</v>
+        <v>0.9923048327837471</v>
       </c>
     </row>
     <row r="39">
@@ -973,13 +973,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>5.807469817361404</v>
+        <v>7.091976784084923</v>
       </c>
       <c r="C39" t="n">
-        <v>2274241911.740644</v>
+        <v>4599538430.007629</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9</v>
+        <v>0.9949964342855426</v>
       </c>
     </row>
     <row r="40">
@@ -987,13 +987,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>9.705114053550254</v>
+        <v>9.42049404536076</v>
       </c>
       <c r="C40" t="n">
-        <v>2830705215.863926</v>
+        <v>4882440503.153989</v>
       </c>
       <c r="D40" t="n">
-        <v>0.99</v>
+        <v>0.9960231275877894</v>
       </c>
     </row>
     <row r="41">
@@ -1001,13 +1001,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>8.339385529008545</v>
+        <v>7.854999765551129</v>
       </c>
       <c r="C41" t="n">
-        <v>2805627574.532079</v>
+        <v>5653441831.558144</v>
       </c>
       <c r="D41" t="n">
-        <v>0.999</v>
+        <v>0.995934975664227</v>
       </c>
     </row>
     <row r="42">
@@ -1015,13 +1015,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>5.77565924623604</v>
+        <v>5.169931478111485</v>
       </c>
       <c r="C42" t="n">
-        <v>2909373830.98064</v>
+        <v>6299489876.531289</v>
       </c>
       <c r="D42" t="n">
-        <v>0.99</v>
+        <v>0.9963089482075981</v>
       </c>
     </row>
     <row r="43">
@@ -1029,13 +1029,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>9.836156741450633</v>
+        <v>8.74020981780939</v>
       </c>
       <c r="C43" t="n">
-        <v>3727776757.362188</v>
+        <v>5569540981.787956</v>
       </c>
       <c r="D43" t="n">
-        <v>0.99</v>
+        <v>0.9940659022464309</v>
       </c>
     </row>
     <row r="44">
@@ -1043,13 +1043,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>6.674919334499503</v>
+        <v>7.412454139982751</v>
       </c>
       <c r="C44" t="n">
-        <v>2595320155.771381</v>
+        <v>7113717509.373538</v>
       </c>
       <c r="D44" t="n">
-        <v>0.999</v>
+        <v>0.9983922137970422</v>
       </c>
     </row>
     <row r="45">
@@ -1057,13 +1057,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>6.636399425043879</v>
+        <v>7.624715854136699</v>
       </c>
       <c r="C45" t="n">
-        <v>2229907194.491547</v>
+        <v>6102492103.223516</v>
       </c>
       <c r="D45" t="n">
-        <v>0.99</v>
+        <v>0.9936822185798349</v>
       </c>
     </row>
     <row r="46">
@@ -1071,13 +1071,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>9.853636449283801</v>
+        <v>9.285470973178059</v>
       </c>
       <c r="C46" t="n">
-        <v>2781107413.213808</v>
+        <v>6920871749.86719</v>
       </c>
       <c r="D46" t="n">
-        <v>0.999</v>
+        <v>0.9952486222897095</v>
       </c>
     </row>
     <row r="47">
@@ -1085,13 +1085,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>6.443552953494433</v>
+        <v>8.62976708797826</v>
       </c>
       <c r="C47" t="n">
-        <v>3871586029.915329</v>
+        <v>7884725471.624013</v>
       </c>
       <c r="D47" t="n">
-        <v>0.999</v>
+        <v>0.9935111930355636</v>
       </c>
     </row>
     <row r="48">
@@ -1099,13 +1099,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>5.652018647353982</v>
+        <v>6.426987118959175</v>
       </c>
       <c r="C48" t="n">
-        <v>2844478785.842661</v>
+        <v>6188307799.175819</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9</v>
+        <v>0.9976770243774705</v>
       </c>
     </row>
     <row r="49">
@@ -1113,13 +1113,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>6.410050401739351</v>
+        <v>7.795354072666084</v>
       </c>
       <c r="C49" t="n">
-        <v>2507596881.018478</v>
+        <v>5015860263.195715</v>
       </c>
       <c r="D49" t="n">
-        <v>0.99</v>
+        <v>0.9959631980906017</v>
       </c>
     </row>
     <row r="50">
@@ -1127,13 +1127,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>5.336967930380334</v>
+        <v>8.87702379848186</v>
       </c>
       <c r="C50" t="n">
-        <v>3124406713.111102</v>
+        <v>6890641063.957925</v>
       </c>
       <c r="D50" t="n">
-        <v>0.99</v>
+        <v>0.991866827110627</v>
       </c>
     </row>
     <row r="51">
@@ -1141,13 +1141,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>6.402965611531205</v>
+        <v>6.259102844269</v>
       </c>
       <c r="C51" t="n">
-        <v>3594487309.937557</v>
+        <v>4498883517.123651</v>
       </c>
       <c r="D51" t="n">
-        <v>0.99</v>
+        <v>0.9975511797300676</v>
       </c>
     </row>
     <row r="52">
@@ -1155,13 +1155,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>9.943814996760505</v>
+        <v>9.991965315528951</v>
       </c>
       <c r="C52" t="n">
-        <v>3510304661.60333</v>
+        <v>5911097273.318841</v>
       </c>
       <c r="D52" t="n">
-        <v>0.99</v>
+        <v>0.994474824183189</v>
       </c>
     </row>
     <row r="53">
@@ -1169,13 +1169,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>6.962714935936077</v>
+        <v>6.475066412179468</v>
       </c>
       <c r="C53" t="n">
-        <v>3554514302.615196</v>
+        <v>7795790070.670707</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9</v>
+        <v>0.9959311070075108</v>
       </c>
     </row>
     <row r="54">
@@ -1183,13 +1183,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>7.404981059473712</v>
+        <v>7.310121848922642</v>
       </c>
       <c r="C54" t="n">
-        <v>3875271685.39693</v>
+        <v>4048470890.336195</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9</v>
+        <v>0.9915283873429523</v>
       </c>
     </row>
     <row r="55">
@@ -1197,13 +1197,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>5.122282779079272</v>
+        <v>7.538134119543811</v>
       </c>
       <c r="C55" t="n">
-        <v>3802214158.329295</v>
+        <v>5423595361.159283</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9</v>
+        <v>0.9955509904019811</v>
       </c>
     </row>
     <row r="56">
@@ -1211,13 +1211,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>7.822890048726163</v>
+        <v>9.594565494057653</v>
       </c>
       <c r="C56" t="n">
-        <v>2541560741.546412</v>
+        <v>7779892225.336288</v>
       </c>
       <c r="D56" t="n">
-        <v>0.999</v>
+        <v>0.9928072224403919</v>
       </c>
     </row>
     <row r="57">
@@ -1225,13 +1225,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>8.213067663008902</v>
+        <v>9.173074062763266</v>
       </c>
       <c r="C57" t="n">
-        <v>3604878363.624515</v>
+        <v>5191069190.449189</v>
       </c>
       <c r="D57" t="n">
-        <v>0.999</v>
+        <v>0.9962365263184866</v>
       </c>
     </row>
     <row r="58">
@@ -1239,13 +1239,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>6.65549153068613</v>
+        <v>8.427105164584063</v>
       </c>
       <c r="C58" t="n">
-        <v>2436981573.833116</v>
+        <v>6880102884.145601</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9</v>
+        <v>0.9928768805431698</v>
       </c>
     </row>
     <row r="59">
@@ -1253,13 +1253,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>8.420189493125106</v>
+        <v>7.444582044331946</v>
       </c>
       <c r="C59" t="n">
-        <v>2980335627.828416</v>
+        <v>4633553619.750759</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9</v>
+        <v>0.9967041777524833</v>
       </c>
     </row>
     <row r="60">
@@ -1267,13 +1267,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>8.482903378387856</v>
+        <v>7.522051243851547</v>
       </c>
       <c r="C60" t="n">
-        <v>2851571343.884669</v>
+        <v>7527816436.17317</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9</v>
+        <v>0.9907180786390274</v>
       </c>
     </row>
     <row r="61">
@@ -1281,13 +1281,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>7.81546108102293</v>
+        <v>5.474655989994506</v>
       </c>
       <c r="C61" t="n">
-        <v>3431132069.789394</v>
+        <v>6762447265.868433</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9</v>
+        <v>0.9988899916845579</v>
       </c>
     </row>
     <row r="62">
@@ -1295,13 +1295,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>7.319842628973613</v>
+        <v>9.449677885168139</v>
       </c>
       <c r="C62" t="n">
-        <v>2153053396.488575</v>
+        <v>6028628810.710494</v>
       </c>
       <c r="D62" t="n">
-        <v>0.99</v>
+        <v>0.9918202282637346</v>
       </c>
     </row>
     <row r="63">
@@ -1309,13 +1309,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>9.871101650439041</v>
+        <v>7.412370788794572</v>
       </c>
       <c r="C63" t="n">
-        <v>2012174452.356533</v>
+        <v>7248616439.611139</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9999</v>
+        <v>0.9953278348468303</v>
       </c>
     </row>
     <row r="64">
@@ -1323,13 +1323,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>8.907704320302022</v>
+        <v>8.704099830647069</v>
       </c>
       <c r="C64" t="n">
-        <v>3130182437.904866</v>
+        <v>6832779641.282521</v>
       </c>
       <c r="D64" t="n">
-        <v>0.999</v>
+        <v>0.9944356616051456</v>
       </c>
     </row>
     <row r="65">
@@ -1337,13 +1337,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>9.791049691331832</v>
+        <v>6.536048535014325</v>
       </c>
       <c r="C65" t="n">
-        <v>3887824771.632998</v>
+        <v>7376065198.779392</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9999</v>
+        <v>0.9989357103170591</v>
       </c>
     </row>
     <row r="66">
@@ -1351,13 +1351,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>6.390872229820053</v>
+        <v>7.087048538910642</v>
       </c>
       <c r="C66" t="n">
-        <v>3846983365.985945</v>
+        <v>7670386127.627024</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9999</v>
+        <v>0.9937950411970192</v>
       </c>
     </row>
     <row r="67">
@@ -1365,13 +1365,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>7.60070377899244</v>
+        <v>6.551777888995701</v>
       </c>
       <c r="C67" t="n">
-        <v>2462498034.94406</v>
+        <v>7060473295.199095</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9999</v>
+        <v>0.9910203691714293</v>
       </c>
     </row>
     <row r="68">
@@ -1379,13 +1379,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>8.409976737432554</v>
+        <v>8.337227107848523</v>
       </c>
       <c r="C68" t="n">
-        <v>3335371620.389873</v>
+        <v>4462627493.789297</v>
       </c>
       <c r="D68" t="n">
-        <v>0.999</v>
+        <v>0.9935224706126544</v>
       </c>
     </row>
     <row r="69">
@@ -1393,13 +1393,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>8.505109991736525</v>
+        <v>8.199499765562802</v>
       </c>
       <c r="C69" t="n">
-        <v>2246637539.806322</v>
+        <v>5635880839.726301</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9999</v>
+        <v>0.9931668401407773</v>
       </c>
     </row>
     <row r="70">
@@ -1407,13 +1407,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>8.814246889824869</v>
+        <v>6.341431634330379</v>
       </c>
       <c r="C70" t="n">
-        <v>3824515162.420707</v>
+        <v>7802820248.726039</v>
       </c>
       <c r="D70" t="n">
-        <v>0.99</v>
+        <v>0.996706687037778</v>
       </c>
     </row>
     <row r="71">
@@ -1421,13 +1421,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>8.865287002252314</v>
+        <v>8.38664159775427</v>
       </c>
       <c r="C71" t="n">
-        <v>2909476483.135699</v>
+        <v>7382856648.510604</v>
       </c>
       <c r="D71" t="n">
-        <v>0.99</v>
+        <v>0.996169862215003</v>
       </c>
     </row>
     <row r="72">
@@ -1435,13 +1435,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>5.495906001553889</v>
+        <v>7.425654094124946</v>
       </c>
       <c r="C72" t="n">
-        <v>2241819552.432022</v>
+        <v>5022132809.828328</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9</v>
+        <v>0.9908729648364527</v>
       </c>
     </row>
     <row r="73">
@@ -1449,13 +1449,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>6.807673276432142</v>
+        <v>7.679432449045722</v>
       </c>
       <c r="C73" t="n">
-        <v>2938352403.985269</v>
+        <v>6309292259.213917</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9999</v>
+        <v>0.9935462096673892</v>
       </c>
     </row>
     <row r="74">
@@ -1463,13 +1463,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>8.220531817182053</v>
+        <v>5.622733161515104</v>
       </c>
       <c r="C74" t="n">
-        <v>3386717624.178626</v>
+        <v>4808177981.701333</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9</v>
+        <v>0.9957366368244781</v>
       </c>
     </row>
     <row r="75">
@@ -1477,13 +1477,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>5.834103481676578</v>
+        <v>6.146579508770039</v>
       </c>
       <c r="C75" t="n">
-        <v>2216465301.271148</v>
+        <v>5417752829.93082</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9999</v>
+        <v>0.99535517564277</v>
       </c>
     </row>
     <row r="76">
@@ -1491,13 +1491,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>7.465050077051474</v>
+        <v>9.323450361526785</v>
       </c>
       <c r="C76" t="n">
-        <v>3165213918.953576</v>
+        <v>6969817118.610329</v>
       </c>
       <c r="D76" t="n">
-        <v>0.99</v>
+        <v>0.9921546467420655</v>
       </c>
     </row>
     <row r="77">
@@ -1505,13 +1505,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>6.041796645817093</v>
+        <v>8.755260652470945</v>
       </c>
       <c r="C77" t="n">
-        <v>3503060116.091953</v>
+        <v>6136121239.992758</v>
       </c>
       <c r="D77" t="n">
-        <v>0.99</v>
+        <v>0.9937830346226751</v>
       </c>
     </row>
     <row r="78">
@@ -1519,13 +1519,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>6.301179454558705</v>
+        <v>7.381665361082996</v>
       </c>
       <c r="C78" t="n">
-        <v>3091240503.911071</v>
+        <v>6821262943.364893</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9</v>
+        <v>0.9972126739828586</v>
       </c>
     </row>
     <row r="79">
@@ -1533,13 +1533,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>6.714346298716169</v>
+        <v>7.757351879850376</v>
       </c>
       <c r="C79" t="n">
-        <v>2224174581.525843</v>
+        <v>6156587801.162177</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9999</v>
+        <v>0.9937709714299588</v>
       </c>
     </row>
     <row r="80">
@@ -1547,13 +1547,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>8.072007492228828</v>
+        <v>8.389825220758173</v>
       </c>
       <c r="C80" t="n">
-        <v>3681188738.982984</v>
+        <v>6895488119.295734</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9999</v>
+        <v>0.992298886059554</v>
       </c>
     </row>
     <row r="81">
@@ -1561,13 +1561,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>5.183506474676499</v>
+        <v>7.621743900990808</v>
       </c>
       <c r="C81" t="n">
-        <v>3803942783.409199</v>
+        <v>6862587444.526976</v>
       </c>
       <c r="D81" t="n">
-        <v>0.99</v>
+        <v>0.991046230716469</v>
       </c>
     </row>
     <row r="82">
@@ -1575,13 +1575,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>6.91695401837892</v>
+        <v>7.743011431729662</v>
       </c>
       <c r="C82" t="n">
-        <v>2103803148.624906</v>
+        <v>4219748642.8798</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9</v>
+        <v>0.9953323530874197</v>
       </c>
     </row>
     <row r="83">
@@ -1589,13 +1589,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>5.046475802160269</v>
+        <v>9.179004726172078</v>
       </c>
       <c r="C83" t="n">
-        <v>3265033710.779034</v>
+        <v>5914699121.911119</v>
       </c>
       <c r="D83" t="n">
-        <v>0.999</v>
+        <v>0.998966097312293</v>
       </c>
     </row>
     <row r="84">
@@ -1603,13 +1603,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>7.404340845148446</v>
+        <v>5.273415358356058</v>
       </c>
       <c r="C84" t="n">
-        <v>2287977748.73364</v>
+        <v>4130643100.082234</v>
       </c>
       <c r="D84" t="n">
-        <v>0.999</v>
+        <v>0.9903031582093041</v>
       </c>
     </row>
     <row r="85">
@@ -1617,13 +1617,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>8.693900116959423</v>
+        <v>9.114112157525994</v>
       </c>
       <c r="C85" t="n">
-        <v>3199183465.765091</v>
+        <v>4617579093.704871</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9999</v>
+        <v>0.9945438373933744</v>
       </c>
     </row>
     <row r="86">
@@ -1631,13 +1631,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>6.516335699756119</v>
+        <v>5.334856762146308</v>
       </c>
       <c r="C86" t="n">
-        <v>2183793613.868398</v>
+        <v>4525046759.011149</v>
       </c>
       <c r="D86" t="n">
-        <v>0.999</v>
+        <v>0.997233997901549</v>
       </c>
     </row>
     <row r="87">
@@ -1645,13 +1645,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>5.857738810924522</v>
+        <v>7.350479433572909</v>
       </c>
       <c r="C87" t="n">
-        <v>3943469311.840803</v>
+        <v>5694813608.388096</v>
       </c>
       <c r="D87" t="n">
-        <v>0.999</v>
+        <v>0.9917948732094832</v>
       </c>
     </row>
     <row r="88">
@@ -1659,13 +1659,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>7.176567696545254</v>
+        <v>5.786738049606396</v>
       </c>
       <c r="C88" t="n">
-        <v>3368310877.429912</v>
+        <v>5526551062.475528</v>
       </c>
       <c r="D88" t="n">
-        <v>0.999</v>
+        <v>0.9916310636661508</v>
       </c>
     </row>
     <row r="89">
@@ -1673,13 +1673,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>9.25484515495836</v>
+        <v>8.980542689746107</v>
       </c>
       <c r="C89" t="n">
-        <v>3895399651.296702</v>
+        <v>4496326189.725296</v>
       </c>
       <c r="D89" t="n">
-        <v>0.99</v>
+        <v>0.9955743811998954</v>
       </c>
     </row>
     <row r="90">
@@ -1687,13 +1687,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>5.402508771295981</v>
+        <v>5.861685645808777</v>
       </c>
       <c r="C90" t="n">
-        <v>3039261647.747734</v>
+        <v>5223346720.878806</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9</v>
+        <v>0.9945791132628843</v>
       </c>
     </row>
     <row r="91">
@@ -1701,13 +1701,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>6.589028662499068</v>
+        <v>9.671789958805348</v>
       </c>
       <c r="C91" t="n">
-        <v>3057513183.274941</v>
+        <v>5387466042.711371</v>
       </c>
       <c r="D91" t="n">
-        <v>0.99</v>
+        <v>0.9983633872724739</v>
       </c>
     </row>
     <row r="92">
@@ -1715,13 +1715,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>7.154427565768393</v>
+        <v>8.0486232946615</v>
       </c>
       <c r="C92" t="n">
-        <v>3711030187.769846</v>
+        <v>4239513785.940113</v>
       </c>
       <c r="D92" t="n">
-        <v>0.99</v>
+        <v>0.9924721709740693</v>
       </c>
     </row>
     <row r="93">
@@ -1729,13 +1729,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>6.879968859769034</v>
+        <v>9.10287541098681</v>
       </c>
       <c r="C93" t="n">
-        <v>2721945784.562086</v>
+        <v>6403943771.273288</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9</v>
+        <v>0.9922469677909246</v>
       </c>
     </row>
     <row r="94">
@@ -1743,13 +1743,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>5.833685351680612</v>
+        <v>6.658848844483147</v>
       </c>
       <c r="C94" t="n">
-        <v>3771414540.26918</v>
+        <v>7903740716.511163</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9999</v>
+        <v>0.9980993938876975</v>
       </c>
     </row>
     <row r="95">
@@ -1757,13 +1757,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>9.715217899482422</v>
+        <v>7.271648742051263</v>
       </c>
       <c r="C95" t="n">
-        <v>2619582340.477922</v>
+        <v>4890242287.290901</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9</v>
+        <v>0.9900172863753891</v>
       </c>
     </row>
     <row r="96">
@@ -1771,13 +1771,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>7.597313861215067</v>
+        <v>5.187218871320735</v>
       </c>
       <c r="C96" t="n">
-        <v>3264635626.331596</v>
+        <v>7988700755.174387</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9</v>
+        <v>0.9987224264820996</v>
       </c>
     </row>
     <row r="97">
@@ -1785,13 +1785,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>6.870364089749534</v>
+        <v>6.176452063091111</v>
       </c>
       <c r="C97" t="n">
-        <v>2597651623.571331</v>
+        <v>5836063382.472349</v>
       </c>
       <c r="D97" t="n">
-        <v>0.999</v>
+        <v>0.991825199639207</v>
       </c>
     </row>
     <row r="98">
@@ -1799,13 +1799,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>6.291534580229565</v>
+        <v>6.720129949701878</v>
       </c>
       <c r="C98" t="n">
-        <v>2963855075.284136</v>
+        <v>6868124115.258192</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9999</v>
+        <v>0.9957001654232569</v>
       </c>
     </row>
     <row r="99">
@@ -1813,13 +1813,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>6.365240642929789</v>
+        <v>9.940972783089384</v>
       </c>
       <c r="C99" t="n">
-        <v>3313890175.43737</v>
+        <v>6557582441.537659</v>
       </c>
       <c r="D99" t="n">
-        <v>0.999</v>
+        <v>0.9903058282872993</v>
       </c>
     </row>
     <row r="100">
@@ -1827,13 +1827,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>8.734971368674017</v>
+        <v>6.891658280179326</v>
       </c>
       <c r="C100" t="n">
-        <v>2917070134.366358</v>
+        <v>4277287114.303138</v>
       </c>
       <c r="D100" t="n">
-        <v>0.999</v>
+        <v>0.990604377803909</v>
       </c>
     </row>
     <row r="101">
@@ -1841,13 +1841,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>9.713175634368366</v>
+        <v>7.449248195463758</v>
       </c>
       <c r="C101" t="n">
-        <v>3295654151.10424</v>
+        <v>4178681287.097087</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9</v>
+        <v>0.994620702776706</v>
       </c>
     </row>
     <row r="102">
@@ -1855,13 +1855,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>9.15896561591472</v>
+        <v>8.743888295886952</v>
       </c>
       <c r="C102" t="n">
-        <v>3020248282.319529</v>
+        <v>5706722142.016813</v>
       </c>
       <c r="D102" t="n">
-        <v>0.99</v>
+        <v>0.99091019232122</v>
       </c>
     </row>
     <row r="103">
@@ -1869,13 +1869,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>6.789546794849374</v>
+        <v>9.844920380266293</v>
       </c>
       <c r="C103" t="n">
-        <v>2487677734.867866</v>
+        <v>5958505131.584072</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9999</v>
+        <v>0.9951620205603312</v>
       </c>
     </row>
     <row r="104">
@@ -1883,13 +1883,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>8.311965561475215</v>
+        <v>5.261775968122492</v>
       </c>
       <c r="C104" t="n">
-        <v>3234449309.212807</v>
+        <v>4162102760.937912</v>
       </c>
       <c r="D104" t="n">
-        <v>0.999</v>
+        <v>0.9950097143480608</v>
       </c>
     </row>
     <row r="105">
@@ -1897,13 +1897,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>9.241315784513915</v>
+        <v>9.483247824677237</v>
       </c>
       <c r="C105" t="n">
-        <v>2049915326.81772</v>
+        <v>5851402780.354656</v>
       </c>
       <c r="D105" t="n">
-        <v>0.999</v>
+        <v>0.9941788141556024</v>
       </c>
     </row>
     <row r="106">
@@ -1911,13 +1911,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>6.979073162972787</v>
+        <v>7.517853467473034</v>
       </c>
       <c r="C106" t="n">
-        <v>2841493511.426468</v>
+        <v>5428411448.802765</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9999</v>
+        <v>0.995263747823096</v>
       </c>
     </row>
     <row r="107">
@@ -1925,13 +1925,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>5.589794987767421</v>
+        <v>6.625165869076404</v>
       </c>
       <c r="C107" t="n">
-        <v>2321195921.23542</v>
+        <v>5631850299.50005</v>
       </c>
       <c r="D107" t="n">
-        <v>0.999</v>
+        <v>0.9914274077610874</v>
       </c>
     </row>
     <row r="108">
@@ -1939,13 +1939,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>7.48698853242043</v>
+        <v>5.664202243270616</v>
       </c>
       <c r="C108" t="n">
-        <v>2300841438.747932</v>
+        <v>5212279050.146882</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9999</v>
+        <v>0.9927327844923857</v>
       </c>
     </row>
     <row r="109">
@@ -1953,13 +1953,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>7.249433425142258</v>
+        <v>9.765886034826927</v>
       </c>
       <c r="C109" t="n">
-        <v>3071587269.52985</v>
+        <v>5632265574.508082</v>
       </c>
       <c r="D109" t="n">
-        <v>0.999</v>
+        <v>0.9980365898420477</v>
       </c>
     </row>
     <row r="110">
@@ -1967,13 +1967,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>9.037488532289153</v>
+        <v>7.594383171681996</v>
       </c>
       <c r="C110" t="n">
-        <v>3457575187.214504</v>
+        <v>5983261016.289066</v>
       </c>
       <c r="D110" t="n">
-        <v>0.99</v>
+        <v>0.9919535839647863</v>
       </c>
     </row>
     <row r="111">
@@ -1981,13 +1981,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>9.847461786940883</v>
+        <v>6.270028812924009</v>
       </c>
       <c r="C111" t="n">
-        <v>3328201015.333173</v>
+        <v>4769865059.232869</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9999</v>
+        <v>0.9969064078474534</v>
       </c>
     </row>
     <row r="112">
@@ -1995,13 +1995,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>6.341987841961975</v>
+        <v>5.796038416660644</v>
       </c>
       <c r="C112" t="n">
-        <v>2503584214.046626</v>
+        <v>6362077025.234119</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9999</v>
+        <v>0.9973298994653154</v>
       </c>
     </row>
     <row r="113">
@@ -2009,13 +2009,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>6.353538425519317</v>
+        <v>5.986312363503547</v>
       </c>
       <c r="C113" t="n">
-        <v>3006380381.874228</v>
+        <v>6116128613.781746</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9999</v>
+        <v>0.992052130749527</v>
       </c>
     </row>
     <row r="114">
@@ -2023,13 +2023,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>8.674098915596558</v>
+        <v>9.658173331453064</v>
       </c>
       <c r="C114" t="n">
-        <v>2555123524.406643</v>
+        <v>6176430074.878516</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9999</v>
+        <v>0.9918278755341202</v>
       </c>
     </row>
     <row r="115">
@@ -2037,13 +2037,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>8.11601168397852</v>
+        <v>6.57201406329323</v>
       </c>
       <c r="C115" t="n">
-        <v>2623330911.055835</v>
+        <v>7970485332.098695</v>
       </c>
       <c r="D115" t="n">
-        <v>0.99</v>
+        <v>0.9958168165823843</v>
       </c>
     </row>
     <row r="116">
@@ -2051,13 +2051,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>5.690753105669546</v>
+        <v>8.605982785276765</v>
       </c>
       <c r="C116" t="n">
-        <v>2530203318.367548</v>
+        <v>6146584183.143548</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9999</v>
+        <v>0.9988393057159398</v>
       </c>
     </row>
     <row r="117">
@@ -2065,13 +2065,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>7.113712966206531</v>
+        <v>5.675537264414709</v>
       </c>
       <c r="C117" t="n">
-        <v>3809330131.554121</v>
+        <v>7580082366.978872</v>
       </c>
       <c r="D117" t="n">
-        <v>0.99</v>
+        <v>0.993425746575452</v>
       </c>
     </row>
     <row r="118">
@@ -2079,13 +2079,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>9.383260788900309</v>
+        <v>6.984467574994238</v>
       </c>
       <c r="C118" t="n">
-        <v>3525043034.392427</v>
+        <v>4434046026.402634</v>
       </c>
       <c r="D118" t="n">
-        <v>0.99</v>
+        <v>0.991556005920874</v>
       </c>
     </row>
     <row r="119">
@@ -2093,13 +2093,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>6.414745755801159</v>
+        <v>8.607618350048366</v>
       </c>
       <c r="C119" t="n">
-        <v>2087635256.409148</v>
+        <v>7833692461.912275</v>
       </c>
       <c r="D119" t="n">
-        <v>0.999</v>
+        <v>0.9926640862491796</v>
       </c>
     </row>
     <row r="120">
@@ -2107,13 +2107,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>7.456974832651706</v>
+        <v>8.184777520589122</v>
       </c>
       <c r="C120" t="n">
-        <v>3302044412.483964</v>
+        <v>6619694927.002616</v>
       </c>
       <c r="D120" t="n">
-        <v>0.999</v>
+        <v>0.9981259635233001</v>
       </c>
     </row>
     <row r="121">
@@ -2121,13 +2121,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>7.39733827874154</v>
+        <v>5.777917592304799</v>
       </c>
       <c r="C121" t="n">
-        <v>2279830186.2379</v>
+        <v>5399423032.713482</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9</v>
+        <v>0.9910572916828589</v>
       </c>
     </row>
     <row r="122">
@@ -2135,13 +2135,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>9.239971161686251</v>
+        <v>7.292015132535568</v>
       </c>
       <c r="C122" t="n">
-        <v>2521993070.654481</v>
+        <v>6050548599.692156</v>
       </c>
       <c r="D122" t="n">
-        <v>0.999</v>
+        <v>0.997739817241712</v>
       </c>
     </row>
     <row r="123">
@@ -2149,13 +2149,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>5.760777808737239</v>
+        <v>8.435122500729669</v>
       </c>
       <c r="C123" t="n">
-        <v>3185270236.053452</v>
+        <v>5142515081.197353</v>
       </c>
       <c r="D123" t="n">
-        <v>0.99</v>
+        <v>0.9914804336447244</v>
       </c>
     </row>
     <row r="124">
@@ -2163,13 +2163,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>5.065228863521137</v>
+        <v>9.054759809227086</v>
       </c>
       <c r="C124" t="n">
-        <v>2605453681.324949</v>
+        <v>6979253272.035976</v>
       </c>
       <c r="D124" t="n">
-        <v>0.99</v>
+        <v>0.9938033674885256</v>
       </c>
     </row>
     <row r="125">
@@ -2177,13 +2177,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>9.525031542747652</v>
+        <v>9.751134681756369</v>
       </c>
       <c r="C125" t="n">
-        <v>2229294466.610596</v>
+        <v>5969204191.704626</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9</v>
+        <v>0.9915385565954929</v>
       </c>
     </row>
     <row r="126">
@@ -2191,13 +2191,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>5.621719538665848</v>
+        <v>7.910107753378152</v>
       </c>
       <c r="C126" t="n">
-        <v>3235001798.642087</v>
+        <v>5199639883.747302</v>
       </c>
       <c r="D126" t="n">
-        <v>0.99</v>
+        <v>0.9970628023522081</v>
       </c>
     </row>
     <row r="127">
@@ -2205,13 +2205,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>8.858874399899515</v>
+        <v>7.433028633340982</v>
       </c>
       <c r="C127" t="n">
-        <v>2890783250.855483</v>
+        <v>7455429644.526226</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9999</v>
+        <v>0.9967547156973205</v>
       </c>
     </row>
     <row r="128">
@@ -2219,13 +2219,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>5.497343131601155</v>
+        <v>5.453824852274815</v>
       </c>
       <c r="C128" t="n">
-        <v>2588293930.618646</v>
+        <v>6855489298.999588</v>
       </c>
       <c r="D128" t="n">
-        <v>0.999</v>
+        <v>0.9954976088371718</v>
       </c>
     </row>
     <row r="129">
@@ -2233,13 +2233,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>9.625276021660749</v>
+        <v>5.360582413588676</v>
       </c>
       <c r="C129" t="n">
-        <v>2524084930.846177</v>
+        <v>7594403780.138725</v>
       </c>
       <c r="D129" t="n">
-        <v>0.999</v>
+        <v>0.993220029543005</v>
       </c>
     </row>
     <row r="130">
@@ -2247,13 +2247,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>5.400848146955979</v>
+        <v>7.126057335816136</v>
       </c>
       <c r="C130" t="n">
-        <v>2998736000.999851</v>
+        <v>4705649802.622042</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9</v>
+        <v>0.9946536475681828</v>
       </c>
     </row>
     <row r="131">
@@ -2261,13 +2261,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>8.378189027544332</v>
+        <v>6.106098973996864</v>
       </c>
       <c r="C131" t="n">
-        <v>3022939108.503745</v>
+        <v>7002140954.183905</v>
       </c>
       <c r="D131" t="n">
-        <v>0.999</v>
+        <v>0.9916790269175428</v>
       </c>
     </row>
     <row r="132">
@@ -2275,13 +2275,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>7.324960214988865</v>
+        <v>9.472197324042817</v>
       </c>
       <c r="C132" t="n">
-        <v>3685150274.072979</v>
+        <v>4213694304.245979</v>
       </c>
       <c r="D132" t="n">
-        <v>0.9</v>
+        <v>0.9942280629153819</v>
       </c>
     </row>
     <row r="133">
@@ -2289,13 +2289,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>7.445615874198314</v>
+        <v>8.041930406230069</v>
       </c>
       <c r="C133" t="n">
-        <v>3163476898.521896</v>
+        <v>7127064577.789459</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9999</v>
+        <v>0.9901602072010425</v>
       </c>
     </row>
     <row r="134">
@@ -2303,13 +2303,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>9.701041169558419</v>
+        <v>5.368255964674656</v>
       </c>
       <c r="C134" t="n">
-        <v>3200612586.36801</v>
+        <v>5393939833.766421</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9</v>
+        <v>0.9979622479427798</v>
       </c>
     </row>
     <row r="135">
@@ -2317,13 +2317,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>9.796572850807465</v>
+        <v>9.088070920267867</v>
       </c>
       <c r="C135" t="n">
-        <v>3990741212.238034</v>
+        <v>5941876563.093426</v>
       </c>
       <c r="D135" t="n">
-        <v>0.99</v>
+        <v>0.9954677107760141</v>
       </c>
     </row>
     <row r="136">
@@ -2331,13 +2331,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>6.50697699819562</v>
+        <v>5.276177201191043</v>
       </c>
       <c r="C136" t="n">
-        <v>2956952262.350317</v>
+        <v>5155618864.748976</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9999</v>
+        <v>0.9963211684496599</v>
       </c>
     </row>
     <row r="137">
@@ -2345,13 +2345,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>9.248334865790724</v>
+        <v>6.045634404798927</v>
       </c>
       <c r="C137" t="n">
-        <v>3047290750.720621</v>
+        <v>6023050257.161957</v>
       </c>
       <c r="D137" t="n">
-        <v>0.9999</v>
+        <v>0.9943585122703243</v>
       </c>
     </row>
     <row r="138">
@@ -2359,13 +2359,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>7.730883525795615</v>
+        <v>5.907852313773472</v>
       </c>
       <c r="C138" t="n">
-        <v>3937565480.044756</v>
+        <v>5886312731.313457</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9999</v>
+        <v>0.9926267121617035</v>
       </c>
     </row>
     <row r="139">
@@ -2373,13 +2373,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>8.299715200021124</v>
+        <v>9.496134487887753</v>
       </c>
       <c r="C139" t="n">
-        <v>2634964606.529172</v>
+        <v>4468310757.544139</v>
       </c>
       <c r="D139" t="n">
-        <v>0.99</v>
+        <v>0.9913482901580269</v>
       </c>
     </row>
     <row r="140">
@@ -2387,13 +2387,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>7.737718064942428</v>
+        <v>7.123538847279584</v>
       </c>
       <c r="C140" t="n">
-        <v>2325390109.876773</v>
+        <v>5751539334.883443</v>
       </c>
       <c r="D140" t="n">
-        <v>0.99</v>
+        <v>0.995108692656087</v>
       </c>
     </row>
     <row r="141">
@@ -2401,13 +2401,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>5.708867093096269</v>
+        <v>7.33521400559427</v>
       </c>
       <c r="C141" t="n">
-        <v>3511092775.368326</v>
+        <v>7998865136.153572</v>
       </c>
       <c r="D141" t="n">
-        <v>0.999</v>
+        <v>0.9970339213743548</v>
       </c>
     </row>
     <row r="142">
@@ -2415,13 +2415,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>9.481667622622265</v>
+        <v>7.14339095265552</v>
       </c>
       <c r="C142" t="n">
-        <v>3516708830.245605</v>
+        <v>4123189491.063923</v>
       </c>
       <c r="D142" t="n">
-        <v>0.99</v>
+        <v>0.9943679867876567</v>
       </c>
     </row>
     <row r="143">
@@ -2429,13 +2429,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>9.448141934406202</v>
+        <v>6.963412963534908</v>
       </c>
       <c r="C143" t="n">
-        <v>2211024555.724195</v>
+        <v>5067733510.391107</v>
       </c>
       <c r="D143" t="n">
-        <v>0.999</v>
+        <v>0.9911886085023806</v>
       </c>
     </row>
     <row r="144">
@@ -2443,13 +2443,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>9.218301741548892</v>
+        <v>9.810800137105851</v>
       </c>
       <c r="C144" t="n">
-        <v>3961749000.019118</v>
+        <v>4592063193.343385</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9</v>
+        <v>0.9917757744325562</v>
       </c>
     </row>
     <row r="145">
@@ -2457,13 +2457,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>9.362774437607825</v>
+        <v>6.115132444731428</v>
       </c>
       <c r="C145" t="n">
-        <v>3787693474.256113</v>
+        <v>4340309120.87435</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9</v>
+        <v>0.9959352997530578</v>
       </c>
     </row>
     <row r="146">
@@ -2471,13 +2471,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>7.427651097593851</v>
+        <v>9.860082276358357</v>
       </c>
       <c r="C146" t="n">
-        <v>2318849594.271571</v>
+        <v>4604641421.403334</v>
       </c>
       <c r="D146" t="n">
-        <v>0.99</v>
+        <v>0.9964981688995495</v>
       </c>
     </row>
     <row r="147">
@@ -2485,13 +2485,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>9.830532408992806</v>
+        <v>5.564354338312318</v>
       </c>
       <c r="C147" t="n">
-        <v>2732483447.974487</v>
+        <v>6546189627.233963</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9999</v>
+        <v>0.9956300642043774</v>
       </c>
     </row>
     <row r="148">
@@ -2499,13 +2499,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>7.931055098143164</v>
+        <v>6.473305955188274</v>
       </c>
       <c r="C148" t="n">
-        <v>2345959291.126824</v>
+        <v>7214583298.02343</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9999</v>
+        <v>0.998134616410377</v>
       </c>
     </row>
     <row r="149">
@@ -2513,13 +2513,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>5.185596558288593</v>
+        <v>8.848357724295134</v>
       </c>
       <c r="C149" t="n">
-        <v>2935624434.231703</v>
+        <v>6889836804.908146</v>
       </c>
       <c r="D149" t="n">
-        <v>0.999</v>
+        <v>0.9931370449899851</v>
       </c>
     </row>
     <row r="150">
@@ -2527,13 +2527,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>5.677980208432722</v>
+        <v>6.899627750318755</v>
       </c>
       <c r="C150" t="n">
-        <v>2272590775.494435</v>
+        <v>4471311912.733289</v>
       </c>
       <c r="D150" t="n">
-        <v>0.999</v>
+        <v>0.9967377457327158</v>
       </c>
     </row>
     <row r="151">
@@ -2541,13 +2541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>8.697482177828576</v>
+        <v>7.943781717723569</v>
       </c>
       <c r="C151" t="n">
-        <v>2193525407.522423</v>
+        <v>6540123053.879707</v>
       </c>
       <c r="D151" t="n">
-        <v>0.999</v>
+        <v>0.9912250341305346</v>
       </c>
     </row>
     <row r="152">
@@ -2555,13 +2555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>5.293847895663123</v>
+        <v>6.910573212957743</v>
       </c>
       <c r="C152" t="n">
-        <v>3489490288.600853</v>
+        <v>5528802887.457935</v>
       </c>
       <c r="D152" t="n">
-        <v>0.999</v>
+        <v>0.9978017466491823</v>
       </c>
     </row>
     <row r="153">
@@ -2569,13 +2569,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>9.897154439227663</v>
+        <v>9.912835524714957</v>
       </c>
       <c r="C153" t="n">
-        <v>3726087597.998542</v>
+        <v>7760130021.980741</v>
       </c>
       <c r="D153" t="n">
-        <v>0.999</v>
+        <v>0.9902464861117346</v>
       </c>
     </row>
     <row r="154">
@@ -2583,13 +2583,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>7.019377755860937</v>
+        <v>5.265494351796034</v>
       </c>
       <c r="C154" t="n">
-        <v>2112362513.782524</v>
+        <v>7864532779.920702</v>
       </c>
       <c r="D154" t="n">
-        <v>0.999</v>
+        <v>0.9906395739733853</v>
       </c>
     </row>
     <row r="155">
@@ -2597,13 +2597,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>9.587820533738263</v>
+        <v>8.5717880825222</v>
       </c>
       <c r="C155" t="n">
-        <v>3907450414.778891</v>
+        <v>5978947803.25383</v>
       </c>
       <c r="D155" t="n">
-        <v>0.999</v>
+        <v>0.9942525734860216</v>
       </c>
     </row>
     <row r="156">
@@ -2611,13 +2611,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>9.302161044876518</v>
+        <v>7.229840441550008</v>
       </c>
       <c r="C156" t="n">
-        <v>3539952355.24278</v>
+        <v>5309339990.143513</v>
       </c>
       <c r="D156" t="n">
-        <v>0.9999</v>
+        <v>0.9921418684894228</v>
       </c>
     </row>
     <row r="157">
@@ -2625,13 +2625,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>7.621717463782183</v>
+        <v>8.64550731384862</v>
       </c>
       <c r="C157" t="n">
-        <v>2461552042.98328</v>
+        <v>4574122112.97609</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9999</v>
+        <v>0.9915207389395131</v>
       </c>
     </row>
     <row r="158">
@@ -2639,13 +2639,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>7.651102586263036</v>
+        <v>7.858212842621342</v>
       </c>
       <c r="C158" t="n">
-        <v>3909363009.374259</v>
+        <v>7299288282.368174</v>
       </c>
       <c r="D158" t="n">
-        <v>0.9</v>
+        <v>0.9955528973073159</v>
       </c>
     </row>
     <row r="159">
@@ -2653,13 +2653,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>5.226070955955745</v>
+        <v>6.781646233890498</v>
       </c>
       <c r="C159" t="n">
-        <v>2748041799.16139</v>
+        <v>5956679221.150863</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9</v>
+        <v>0.9955690824618471</v>
       </c>
     </row>
     <row r="160">
@@ -2667,13 +2667,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>7.035601356667917</v>
+        <v>5.104793147841231</v>
       </c>
       <c r="C160" t="n">
-        <v>3175239088.345665</v>
+        <v>5583726391.551433</v>
       </c>
       <c r="D160" t="n">
-        <v>0.99</v>
+        <v>0.9901113300132265</v>
       </c>
     </row>
     <row r="161">
@@ -2681,13 +2681,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>8.680857826754625</v>
+        <v>9.785663681292995</v>
       </c>
       <c r="C161" t="n">
-        <v>3527518347.875824</v>
+        <v>4087187952.122372</v>
       </c>
       <c r="D161" t="n">
-        <v>0.99</v>
+        <v>0.9917663578800826</v>
       </c>
     </row>
     <row r="162">
@@ -2695,13 +2695,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>5.142969946321989</v>
+        <v>6.943810537875876</v>
       </c>
       <c r="C162" t="n">
-        <v>2867211109.095093</v>
+        <v>5890835886.280272</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9</v>
+        <v>0.9907336704639291</v>
       </c>
     </row>
     <row r="163">
@@ -2709,13 +2709,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>9.870067221314251</v>
+        <v>6.292069053863952</v>
       </c>
       <c r="C163" t="n">
-        <v>2841181795.172303</v>
+        <v>6338352318.79493</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9999</v>
+        <v>0.9973114333436486</v>
       </c>
     </row>
     <row r="164">
@@ -2723,13 +2723,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>8.39474522869387</v>
+        <v>9.785186541530047</v>
       </c>
       <c r="C164" t="n">
-        <v>2257174626.206392</v>
+        <v>4948152148.526884</v>
       </c>
       <c r="D164" t="n">
-        <v>0.99</v>
+        <v>0.9943994191035008</v>
       </c>
     </row>
     <row r="165">
@@ -2737,13 +2737,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8.861286945458822</v>
+        <v>5.721508708811649</v>
       </c>
       <c r="C165" t="n">
-        <v>3507510245.45727</v>
+        <v>4639480279.444934</v>
       </c>
       <c r="D165" t="n">
-        <v>0.99</v>
+        <v>0.9928031490500759</v>
       </c>
     </row>
     <row r="166">
@@ -2751,13 +2751,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>5.636239874031245</v>
+        <v>5.488557917004425</v>
       </c>
       <c r="C166" t="n">
-        <v>2791669529.356554</v>
+        <v>5872249919.481556</v>
       </c>
       <c r="D166" t="n">
-        <v>0.9999</v>
+        <v>0.9976272920565541</v>
       </c>
     </row>
     <row r="167">
@@ -2765,13 +2765,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>9.638401992999786</v>
+        <v>9.850898926546952</v>
       </c>
       <c r="C167" t="n">
-        <v>2600760598.852888</v>
+        <v>5800026691.134905</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9999</v>
+        <v>0.998146343882674</v>
       </c>
     </row>
     <row r="168">
@@ -2779,13 +2779,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>5.921145541753161</v>
+        <v>5.728382544318442</v>
       </c>
       <c r="C168" t="n">
-        <v>3387143829.009998</v>
+        <v>4405313366.776722</v>
       </c>
       <c r="D168" t="n">
-        <v>0.999</v>
+        <v>0.9944016493802676</v>
       </c>
     </row>
     <row r="169">
@@ -2793,13 +2793,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>5.917958059436213</v>
+        <v>6.74795395403738</v>
       </c>
       <c r="C169" t="n">
-        <v>2076838420.34607</v>
+        <v>7138273668.046585</v>
       </c>
       <c r="D169" t="n">
-        <v>0.9999</v>
+        <v>0.9986884966567982</v>
       </c>
     </row>
     <row r="170">
@@ -2807,13 +2807,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>8.757253202729988</v>
+        <v>5.231694077789289</v>
       </c>
       <c r="C170" t="n">
-        <v>2247491917.743874</v>
+        <v>6218717382.596498</v>
       </c>
       <c r="D170" t="n">
-        <v>0.99</v>
+        <v>0.9918845859607542</v>
       </c>
     </row>
     <row r="171">
@@ -2821,13 +2821,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>6.589629590323168</v>
+        <v>6.981667869744452</v>
       </c>
       <c r="C171" t="n">
-        <v>2722189726.0219</v>
+        <v>5086700301.205151</v>
       </c>
       <c r="D171" t="n">
-        <v>0.9999</v>
+        <v>0.9966637946492254</v>
       </c>
     </row>
     <row r="172">
@@ -2835,13 +2835,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>9.997025600772211</v>
+        <v>6.749140443492697</v>
       </c>
       <c r="C172" t="n">
-        <v>2087114454.886926</v>
+        <v>5508889354.197565</v>
       </c>
       <c r="D172" t="n">
-        <v>0.9</v>
+        <v>0.9947247707329798</v>
       </c>
     </row>
     <row r="173">
@@ -2849,13 +2849,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>5.082069217509956</v>
+        <v>9.984872404156221</v>
       </c>
       <c r="C173" t="n">
-        <v>2289168546.33081</v>
+        <v>4857039200.227116</v>
       </c>
       <c r="D173" t="n">
-        <v>0.99</v>
+        <v>0.9905842618116463</v>
       </c>
     </row>
     <row r="174">
@@ -2863,13 +2863,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>9.155302645748199</v>
+        <v>7.678556278013086</v>
       </c>
       <c r="C174" t="n">
-        <v>3235851930.539863</v>
+        <v>4058050392.164772</v>
       </c>
       <c r="D174" t="n">
-        <v>0.99</v>
+        <v>0.9921482712972917</v>
       </c>
     </row>
     <row r="175">
@@ -2877,13 +2877,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>6.217410533114614</v>
+        <v>7.842755683982285</v>
       </c>
       <c r="C175" t="n">
-        <v>3906264047.239286</v>
+        <v>7053615473.430696</v>
       </c>
       <c r="D175" t="n">
-        <v>0.999</v>
+        <v>0.9981591409438335</v>
       </c>
     </row>
     <row r="176">
@@ -2891,13 +2891,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>6.145205794156533</v>
+        <v>5.526963034475095</v>
       </c>
       <c r="C176" t="n">
-        <v>3392982241.940281</v>
+        <v>5484963757.35367</v>
       </c>
       <c r="D176" t="n">
-        <v>0.999</v>
+        <v>0.9963548186320644</v>
       </c>
     </row>
     <row r="177">
@@ -2905,13 +2905,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>6.18521554540158</v>
+        <v>7.019525453205592</v>
       </c>
       <c r="C177" t="n">
-        <v>3322393108.150819</v>
+        <v>6327887092.880706</v>
       </c>
       <c r="D177" t="n">
-        <v>0.99</v>
+        <v>0.9924999151467663</v>
       </c>
     </row>
     <row r="178">
@@ -2919,13 +2919,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>7.358395160661519</v>
+        <v>8.159991247736974</v>
       </c>
       <c r="C178" t="n">
-        <v>2934318080.714441</v>
+        <v>4823028568.533564</v>
       </c>
       <c r="D178" t="n">
-        <v>0.999</v>
+        <v>0.9945899379050946</v>
       </c>
     </row>
     <row r="179">
@@ -2933,13 +2933,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>9.641110704048838</v>
+        <v>6.314110733935053</v>
       </c>
       <c r="C179" t="n">
-        <v>3931927124.527704</v>
+        <v>7906885669.735858</v>
       </c>
       <c r="D179" t="n">
-        <v>0.9</v>
+        <v>0.991389524120312</v>
       </c>
     </row>
     <row r="180">
@@ -2947,13 +2947,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7.957316600072299</v>
+        <v>9.614443902271786</v>
       </c>
       <c r="C180" t="n">
-        <v>3983440776.307714</v>
+        <v>4917201971.369255</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9</v>
+        <v>0.992436793618089</v>
       </c>
     </row>
     <row r="181">
@@ -2961,13 +2961,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7.465504927519392</v>
+        <v>6.104508352090082</v>
       </c>
       <c r="C181" t="n">
-        <v>3364699744.205702</v>
+        <v>6166165632.702743</v>
       </c>
       <c r="D181" t="n">
-        <v>0.9</v>
+        <v>0.9927628965026158</v>
       </c>
     </row>
     <row r="182">
@@ -2975,13 +2975,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>5.260701142381075</v>
+        <v>7.044025038693801</v>
       </c>
       <c r="C182" t="n">
-        <v>2327058363.834154</v>
+        <v>7501661028.971241</v>
       </c>
       <c r="D182" t="n">
-        <v>0.99</v>
+        <v>0.993493961392349</v>
       </c>
     </row>
     <row r="183">
@@ -2989,13 +2989,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>6.395010226695755</v>
+        <v>5.503327812093699</v>
       </c>
       <c r="C183" t="n">
-        <v>3796955976.881616</v>
+        <v>7225281736.303938</v>
       </c>
       <c r="D183" t="n">
-        <v>0.99</v>
+        <v>0.9908588378173773</v>
       </c>
     </row>
     <row r="184">
@@ -3003,13 +3003,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>7.669987436048284</v>
+        <v>7.348184377878189</v>
       </c>
       <c r="C184" t="n">
-        <v>2520326076.244194</v>
+        <v>4415000023.613936</v>
       </c>
       <c r="D184" t="n">
-        <v>0.999</v>
+        <v>0.9937571779913016</v>
       </c>
     </row>
     <row r="185">
@@ -3017,13 +3017,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>9.139767836871766</v>
+        <v>7.064245367439857</v>
       </c>
       <c r="C185" t="n">
-        <v>3029884058.829219</v>
+        <v>5775329785.557058</v>
       </c>
       <c r="D185" t="n">
-        <v>0.99</v>
+        <v>0.9946747767597434</v>
       </c>
     </row>
     <row r="186">
@@ -3031,13 +3031,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>9.260622974164672</v>
+        <v>6.32090803755719</v>
       </c>
       <c r="C186" t="n">
-        <v>3729456513.528146</v>
+        <v>4046708564.206504</v>
       </c>
       <c r="D186" t="n">
-        <v>0.9</v>
+        <v>0.9965282252659021</v>
       </c>
     </row>
     <row r="187">
@@ -3045,13 +3045,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>6.433918493932298</v>
+        <v>6.254768439304701</v>
       </c>
       <c r="C187" t="n">
-        <v>3562209911.852001</v>
+        <v>6517633966.379559</v>
       </c>
       <c r="D187" t="n">
-        <v>0.9999</v>
+        <v>0.9951817986879145</v>
       </c>
     </row>
     <row r="188">
@@ -3059,13 +3059,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>5.901664337780066</v>
+        <v>6.508445195797673</v>
       </c>
       <c r="C188" t="n">
-        <v>2804512319.665326</v>
+        <v>6276275709.182554</v>
       </c>
       <c r="D188" t="n">
-        <v>0.99</v>
+        <v>0.9913906573979635</v>
       </c>
     </row>
     <row r="189">
@@ -3073,13 +3073,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>6.332109053797483</v>
+        <v>7.175566772057099</v>
       </c>
       <c r="C189" t="n">
-        <v>3690828980.501906</v>
+        <v>4989501461.335976</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9999</v>
+        <v>0.9909184578926726</v>
       </c>
     </row>
     <row r="190">
@@ -3087,13 +3087,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>9.458739391938826</v>
+        <v>5.927393806133502</v>
       </c>
       <c r="C190" t="n">
-        <v>2032742576.865298</v>
+        <v>5875589012.825682</v>
       </c>
       <c r="D190" t="n">
-        <v>0.9</v>
+        <v>0.9972616920020763</v>
       </c>
     </row>
     <row r="191">
@@ -3101,13 +3101,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>8.51090461703539</v>
+        <v>5.981615640619234</v>
       </c>
       <c r="C191" t="n">
-        <v>3781259648.748229</v>
+        <v>4750828714.251872</v>
       </c>
       <c r="D191" t="n">
-        <v>0.999</v>
+        <v>0.9957101990691913</v>
       </c>
     </row>
     <row r="192">
@@ -3115,13 +3115,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>5.420588284112573</v>
+        <v>7.297355574861447</v>
       </c>
       <c r="C192" t="n">
-        <v>2097095914.473666</v>
+        <v>7470202360.322649</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9</v>
+        <v>0.9920690013771851</v>
       </c>
     </row>
     <row r="193">
@@ -3129,13 +3129,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>9.221643022095694</v>
+        <v>6.691864165374762</v>
       </c>
       <c r="C193" t="n">
-        <v>2312657862.752766</v>
+        <v>7194111393.490777</v>
       </c>
       <c r="D193" t="n">
-        <v>0.99</v>
+        <v>0.997509404153703</v>
       </c>
     </row>
     <row r="194">
@@ -3143,13 +3143,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>5.924044910088338</v>
+        <v>9.069982439724161</v>
       </c>
       <c r="C194" t="n">
-        <v>3674524924.537056</v>
+        <v>7598508959.49721</v>
       </c>
       <c r="D194" t="n">
-        <v>0.9999</v>
+        <v>0.9952461542841903</v>
       </c>
     </row>
     <row r="195">
@@ -3157,13 +3157,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>8.986205487409912</v>
+        <v>7.448410514991517</v>
       </c>
       <c r="C195" t="n">
-        <v>3317412781.178983</v>
+        <v>6141775171.792726</v>
       </c>
       <c r="D195" t="n">
-        <v>0.9</v>
+        <v>0.9980957252985504</v>
       </c>
     </row>
     <row r="196">
@@ -3171,13 +3171,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>5.595296319952236</v>
+        <v>6.463980605833749</v>
       </c>
       <c r="C196" t="n">
-        <v>2480803148.562046</v>
+        <v>6249893032.704241</v>
       </c>
       <c r="D196" t="n">
-        <v>0.999</v>
+        <v>0.992733250838932</v>
       </c>
     </row>
     <row r="197">
@@ -3185,13 +3185,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>7.415384247120892</v>
+        <v>7.318936158752454</v>
       </c>
       <c r="C197" t="n">
-        <v>2249551195.255444</v>
+        <v>5526517885.941811</v>
       </c>
       <c r="D197" t="n">
-        <v>0.9</v>
+        <v>0.9918515451513586</v>
       </c>
     </row>
     <row r="198">
@@ -3199,13 +3199,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>9.095586272500798</v>
+        <v>9.133324121679827</v>
       </c>
       <c r="C198" t="n">
-        <v>2682842651.048836</v>
+        <v>4920544484.361749</v>
       </c>
       <c r="D198" t="n">
-        <v>0.9</v>
+        <v>0.9907733065936853</v>
       </c>
     </row>
     <row r="199">
@@ -3213,13 +3213,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>5.597276903971256</v>
+        <v>9.973113672561238</v>
       </c>
       <c r="C199" t="n">
-        <v>3487561591.654347</v>
+        <v>5770776528.192238</v>
       </c>
       <c r="D199" t="n">
-        <v>0.9</v>
+        <v>0.9904858032841146</v>
       </c>
     </row>
     <row r="200">
@@ -3227,13 +3227,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>6.25204789135987</v>
+        <v>6.835320477339923</v>
       </c>
       <c r="C200" t="n">
-        <v>2512096869.018666</v>
+        <v>7956908566.08815</v>
       </c>
       <c r="D200" t="n">
-        <v>0.9</v>
+        <v>0.9905058361625003</v>
       </c>
     </row>
     <row r="201">
@@ -3241,13 +3241,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>8.628164587703029</v>
+        <v>9.363758600426632</v>
       </c>
       <c r="C201" t="n">
-        <v>3630904106.936749</v>
+        <v>5800438032.061226</v>
       </c>
       <c r="D201" t="n">
-        <v>0.999</v>
+        <v>0.9964035155509109</v>
       </c>
     </row>
   </sheetData>
